--- a/Cube_finish.xlsx
+++ b/Cube_finish.xlsx
@@ -503,26 +503,18 @@
           <t>Pads Zone A / Core A</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>10/03/2022</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="E2" s="2" t="n">
+        <v>44456</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2380</v>
       </c>
       <c r="G2" t="n">
         <v>32.8</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>52.7</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>40N</t>
@@ -548,22 +540,16 @@
           <t>Pads Zone A / Core A</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>09/03/2022</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
+      <c r="E3" s="2" t="n">
+        <v>44477</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2380</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>51.0</t>
-        </is>
+      <c r="I3" t="n">
+        <v>44.2</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
@@ -591,22 +577,16 @@
           <t>Pads Zone A / Core A</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>09/03/2022</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2430</t>
-        </is>
+      <c r="E4" s="2" t="n">
+        <v>44463</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2420</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50.1</t>
-        </is>
+      <c r="I4" t="n">
+        <v>33.5</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
@@ -634,20 +614,14 @@
           <t>Pads Zone A / Core A</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>09/03/2022</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2390</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>52.7(6Days)</t>
-        </is>
+      <c r="E5" s="2" t="n">
+        <v>44456</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2340</v>
+      </c>
+      <c r="G5" t="n">
+        <v>30.2</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -677,22 +651,16 @@
           <t>Pads Zone A / Core A</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>10/03/2022</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2380</t>
-        </is>
+      <c r="E6" s="2" t="n">
+        <v>44477</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2360</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>45.5</t>
-        </is>
+      <c r="I6" t="n">
+        <v>42.2</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
@@ -720,22 +688,16 @@
           <t>Pads Zone A / Core A</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>10/03/2022</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2380</t>
-        </is>
+      <c r="E7" s="2" t="n">
+        <v>44477</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2360</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>39.3</t>
-        </is>
+      <c r="I7" t="n">
+        <v>42</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
@@ -1061,15 +1023,11 @@
           <t>Mainholes</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>10/03/2022</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="E16" s="2" t="n">
+        <v>44454</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2400</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1078,11 +1036,7 @@
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>52.7</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>40N</t>
@@ -1108,25 +1062,17 @@
           <t>Mainholes</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>09/03/2022</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
+      <c r="E17" s="2" t="n">
+        <v>44463</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2400</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>33.8</v>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>51.0</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
@@ -1153,25 +1099,17 @@
           <t>Mainholes</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>09/03/2022</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2430</t>
-        </is>
+      <c r="E18" s="2" t="n">
+        <v>44463</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2420</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>33.5</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>50.1</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
@@ -1198,21 +1136,13 @@
           <t>Mainholes</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>09/03/2022</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2390</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>52.7(6Days)</t>
-        </is>
-      </c>
+      <c r="E19" s="2" t="n">
+        <v>44491</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2420</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
@@ -17286,15 +17216,19 @@
           <t>First Floor Wall (30-45)(B-Z)</t>
         </is>
       </c>
-      <c r="E463" s="2" t="n">
-        <v>44601</v>
-      </c>
-      <c r="F463" t="n">
-        <v>2370</v>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>09/02/2022</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>2370</t>
+        </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>9 Days(33.9)</t>
+          <t>33.9(9Days)</t>
         </is>
       </c>
       <c r="H463" t="inlineStr"/>
@@ -17402,15 +17336,19 @@
           <t>Second Floor Slab - Area 1</t>
         </is>
       </c>
-      <c r="E467" s="2" t="n">
-        <v>44601</v>
-      </c>
-      <c r="F467" t="n">
-        <v>2340</v>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>09/02/2022</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>9 Days(38.4)</t>
+          <t>38.4(9Days)</t>
         </is>
       </c>
       <c r="H467" t="inlineStr"/>
@@ -17437,15 +17375,19 @@
           <t>Second Floor Slab - Area 1</t>
         </is>
       </c>
-      <c r="E468" s="2" t="n">
-        <v>44601</v>
-      </c>
-      <c r="F468" t="n">
-        <v>2340</v>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>09/02/2022</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>9 Days(37.7)</t>
+          <t>37.7(9Days)</t>
         </is>
       </c>
       <c r="H468" t="inlineStr"/>
@@ -17553,14 +17495,20 @@
           <t>First Floor Walls (31-37)(G-DD)</t>
         </is>
       </c>
-      <c r="E472" s="2" t="n">
-        <v>44601</v>
-      </c>
-      <c r="F472" t="n">
-        <v>2300</v>
-      </c>
-      <c r="G472" t="n">
-        <v>32.7</v>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>09/02/2022</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>32.7</t>
+        </is>
       </c>
       <c r="H472" t="inlineStr"/>
       <c r="I472" t="inlineStr"/>

--- a/Cube_finish.xlsx
+++ b/Cube_finish.xlsx
@@ -13519,12 +13519,24 @@
           <t>First Floor W1 (DD-KK) (8-9)</t>
         </is>
       </c>
-      <c r="D409" s="2" t="inlineStr"/>
-      <c r="E409" s="2" t="inlineStr"/>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2022</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="inlineStr">
+        <is>
+          <t>2390</t>
+        </is>
+      </c>
       <c r="F409" s="2" t="inlineStr"/>
       <c r="G409" s="2" t="inlineStr"/>
       <c r="H409" s="2" t="inlineStr"/>
-      <c r="I409" s="2" t="inlineStr"/>
+      <c r="I409" s="2" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
       <c r="J409" s="2" t="inlineStr">
         <is>
           <t>37N</t>
@@ -13634,8 +13646,10 @@
           <t>10/03/2022</t>
         </is>
       </c>
-      <c r="E413" s="2" t="n">
-        <v>2360</v>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
       </c>
       <c r="F413" s="2" t="inlineStr"/>
       <c r="G413" s="2" t="inlineStr"/>
@@ -13750,8 +13764,10 @@
           <t>11/03/2022</t>
         </is>
       </c>
-      <c r="E417" s="2" t="n">
-        <v>2350</v>
+      <c r="E417" s="2" t="inlineStr">
+        <is>
+          <t>2350</t>
+        </is>
       </c>
       <c r="F417" s="2" t="inlineStr"/>
       <c r="G417" s="2" t="inlineStr"/>
@@ -13868,8 +13884,10 @@
           <t>14/03/2022</t>
         </is>
       </c>
-      <c r="E421" s="2" t="n">
-        <v>2380</v>
+      <c r="E421" s="2" t="inlineStr">
+        <is>
+          <t>2380</t>
+        </is>
       </c>
       <c r="F421" s="2" t="inlineStr"/>
       <c r="G421" s="2" t="inlineStr"/>
@@ -13980,8 +13998,10 @@
           <t>14/03/2022</t>
         </is>
       </c>
-      <c r="E425" s="2" t="n">
-        <v>2370</v>
+      <c r="E425" s="2" t="inlineStr">
+        <is>
+          <t>2370</t>
+        </is>
       </c>
       <c r="F425" s="2" t="inlineStr"/>
       <c r="G425" s="2" t="inlineStr"/>
@@ -14182,8 +14202,10 @@
           <t>16/03/2022</t>
         </is>
       </c>
-      <c r="E432" s="2" t="n">
-        <v>2380</v>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>2380</t>
+        </is>
       </c>
       <c r="F432" s="2" t="inlineStr"/>
       <c r="G432" s="2" t="inlineStr"/>
@@ -14326,8 +14348,10 @@
           <t>17/03/2022</t>
         </is>
       </c>
-      <c r="E437" s="2" t="n">
-        <v>2360</v>
+      <c r="E437" s="2" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
       </c>
       <c r="F437" s="2" t="inlineStr"/>
       <c r="G437" s="2" t="inlineStr"/>
@@ -14358,8 +14382,10 @@
           <t>17/03/2022</t>
         </is>
       </c>
-      <c r="E438" s="2" t="n">
-        <v>2330</v>
+      <c r="E438" s="2" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
       </c>
       <c r="F438" s="2" t="inlineStr"/>
       <c r="G438" s="2" t="inlineStr"/>
@@ -14474,8 +14500,10 @@
           <t>18/03/2022</t>
         </is>
       </c>
-      <c r="E442" s="2" t="n">
-        <v>2420</v>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>2420</t>
+        </is>
       </c>
       <c r="F442" s="2" t="inlineStr"/>
       <c r="G442" s="2" t="inlineStr"/>
@@ -14592,8 +14620,10 @@
           <t>21/03/2022</t>
         </is>
       </c>
-      <c r="E446" s="2" t="n">
-        <v>2370</v>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>2370</t>
+        </is>
       </c>
       <c r="F446" s="2" t="inlineStr"/>
       <c r="G446" s="2" t="inlineStr"/>
@@ -14811,12 +14841,24 @@
           <t>First Floor Walls (22-35)(U-GG)</t>
         </is>
       </c>
-      <c r="D454" s="2" t="inlineStr"/>
-      <c r="E454" s="2" t="inlineStr"/>
+      <c r="D454" s="2" t="inlineStr">
+        <is>
+          <t>23/03/2022</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
       <c r="F454" s="2" t="inlineStr"/>
       <c r="G454" s="2" t="inlineStr"/>
       <c r="H454" s="2" t="inlineStr"/>
-      <c r="I454" s="2" t="inlineStr"/>
+      <c r="I454" s="2" t="inlineStr">
+        <is>
+          <t>46.8</t>
+        </is>
+      </c>
       <c r="J454" s="2" t="inlineStr"/>
     </row>
     <row r="455">
@@ -15966,13 +16008,17 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E498" s="2" t="n">
-        <v>2400</v>
+      <c r="E498" s="2" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
       </c>
       <c r="F498" s="2" t="inlineStr"/>
       <c r="G498" s="2" t="inlineStr"/>
-      <c r="H498" s="2" t="n">
-        <v>51</v>
+      <c r="H498" s="2" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
       </c>
       <c r="I498" s="2" t="inlineStr"/>
       <c r="J498" s="2" t="inlineStr"/>
@@ -15997,13 +16043,17 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E499" s="2" t="n">
-        <v>2430</v>
+      <c r="E499" s="2" t="inlineStr">
+        <is>
+          <t>2430</t>
+        </is>
       </c>
       <c r="F499" s="2" t="inlineStr"/>
       <c r="G499" s="2" t="inlineStr"/>
-      <c r="H499" s="2" t="n">
-        <v>50.1</v>
+      <c r="H499" s="2" t="inlineStr">
+        <is>
+          <t>50.1</t>
+        </is>
       </c>
       <c r="I499" s="2" t="inlineStr"/>
       <c r="J499" s="2" t="inlineStr"/>
@@ -16078,13 +16128,17 @@
           <t>10/03/2022</t>
         </is>
       </c>
-      <c r="E502" s="2" t="n">
-        <v>2380</v>
+      <c r="E502" s="2" t="inlineStr">
+        <is>
+          <t>2380</t>
+        </is>
       </c>
       <c r="F502" s="2" t="inlineStr"/>
       <c r="G502" s="2" t="inlineStr"/>
-      <c r="H502" s="2" t="n">
-        <v>45.5</v>
+      <c r="H502" s="2" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
       </c>
       <c r="I502" s="2" t="inlineStr"/>
       <c r="J502" s="2" t="inlineStr"/>
@@ -16108,13 +16162,17 @@
           <t>10/03/2022</t>
         </is>
       </c>
-      <c r="E503" s="2" t="n">
-        <v>2380</v>
+      <c r="E503" s="2" t="inlineStr">
+        <is>
+          <t>2380</t>
+        </is>
       </c>
       <c r="F503" s="2" t="inlineStr"/>
       <c r="G503" s="2" t="inlineStr"/>
-      <c r="H503" s="2" t="n">
-        <v>39.3</v>
+      <c r="H503" s="2" t="inlineStr">
+        <is>
+          <t>39.3</t>
+        </is>
       </c>
       <c r="I503" s="2" t="inlineStr"/>
       <c r="J503" s="2" t="inlineStr"/>
@@ -16216,13 +16274,17 @@
           <t>11/03/2022</t>
         </is>
       </c>
-      <c r="E507" s="2" t="n">
-        <v>2360</v>
+      <c r="E507" s="2" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
       </c>
       <c r="F507" s="2" t="inlineStr"/>
       <c r="G507" s="2" t="inlineStr"/>
-      <c r="H507" s="2" t="n">
-        <v>43</v>
+      <c r="H507" s="2" t="inlineStr">
+        <is>
+          <t>43.0</t>
+        </is>
       </c>
       <c r="I507" s="2" t="inlineStr"/>
       <c r="J507" s="2" t="inlineStr"/>
@@ -16246,13 +16308,17 @@
           <t>11/03/2022</t>
         </is>
       </c>
-      <c r="E508" s="2" t="n">
-        <v>2370</v>
+      <c r="E508" s="2" t="inlineStr">
+        <is>
+          <t>2370</t>
+        </is>
       </c>
       <c r="F508" s="2" t="inlineStr"/>
       <c r="G508" s="2" t="inlineStr"/>
-      <c r="H508" s="2" t="n">
-        <v>44.5</v>
+      <c r="H508" s="2" t="inlineStr">
+        <is>
+          <t>44.5</t>
+        </is>
       </c>
       <c r="I508" s="2" t="inlineStr"/>
       <c r="J508" s="2" t="inlineStr"/>
@@ -16326,13 +16392,17 @@
           <t>14/03/2022</t>
         </is>
       </c>
-      <c r="E511" s="2" t="n">
-        <v>2330</v>
+      <c r="E511" s="2" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
       </c>
       <c r="F511" s="2" t="inlineStr"/>
       <c r="G511" s="2" t="inlineStr"/>
-      <c r="H511" s="2" t="n">
-        <v>39.6</v>
+      <c r="H511" s="2" t="inlineStr">
+        <is>
+          <t>39.6</t>
+        </is>
       </c>
       <c r="I511" s="2" t="inlineStr"/>
       <c r="J511" s="2" t="inlineStr"/>
@@ -16356,13 +16426,17 @@
           <t>14/03/2022</t>
         </is>
       </c>
-      <c r="E512" s="2" t="n">
-        <v>2330</v>
+      <c r="E512" s="2" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
       </c>
       <c r="F512" s="2" t="inlineStr"/>
       <c r="G512" s="2" t="inlineStr"/>
-      <c r="H512" s="2" t="n">
-        <v>39</v>
+      <c r="H512" s="2" t="inlineStr">
+        <is>
+          <t>39.0</t>
+        </is>
       </c>
       <c r="I512" s="2" t="inlineStr"/>
       <c r="J512" s="2" t="inlineStr"/>
@@ -16430,13 +16504,17 @@
           <t>14/03/2022</t>
         </is>
       </c>
-      <c r="E515" s="2" t="n">
-        <v>2380</v>
+      <c r="E515" s="2" t="inlineStr">
+        <is>
+          <t>2380</t>
+        </is>
       </c>
       <c r="F515" s="2" t="inlineStr"/>
       <c r="G515" s="2" t="inlineStr"/>
-      <c r="H515" s="2" t="n">
-        <v>52.9</v>
+      <c r="H515" s="2" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
       </c>
       <c r="I515" s="2" t="inlineStr"/>
       <c r="J515" s="2" t="inlineStr"/>
@@ -16460,13 +16538,17 @@
           <t>14/03/2022</t>
         </is>
       </c>
-      <c r="E516" s="2" t="n">
-        <v>2380</v>
+      <c r="E516" s="2" t="inlineStr">
+        <is>
+          <t>2380</t>
+        </is>
       </c>
       <c r="F516" s="2" t="inlineStr"/>
       <c r="G516" s="2" t="inlineStr"/>
-      <c r="H516" s="2" t="n">
-        <v>51.8</v>
+      <c r="H516" s="2" t="inlineStr">
+        <is>
+          <t>51.8</t>
+        </is>
       </c>
       <c r="I516" s="2" t="inlineStr"/>
       <c r="J516" s="2" t="inlineStr"/>
@@ -16512,8 +16594,10 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E518" s="2" t="n">
-        <v>2360</v>
+      <c r="E518" s="2" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
       </c>
       <c r="F518" s="2" t="inlineStr">
         <is>
@@ -16544,13 +16628,17 @@
           <t>15/03/2022</t>
         </is>
       </c>
-      <c r="E519" s="2" t="n">
-        <v>2350</v>
+      <c r="E519" s="2" t="inlineStr">
+        <is>
+          <t>2350</t>
+        </is>
       </c>
       <c r="F519" s="2" t="inlineStr"/>
       <c r="G519" s="2" t="inlineStr"/>
-      <c r="H519" s="2" t="n">
-        <v>45.6</v>
+      <c r="H519" s="2" t="inlineStr">
+        <is>
+          <t>45.6</t>
+        </is>
       </c>
       <c r="I519" s="2" t="inlineStr"/>
       <c r="J519" s="2" t="inlineStr"/>
@@ -16574,13 +16662,17 @@
           <t>15/03/2022</t>
         </is>
       </c>
-      <c r="E520" s="2" t="n">
-        <v>2360</v>
+      <c r="E520" s="2" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
       </c>
       <c r="F520" s="2" t="inlineStr"/>
       <c r="G520" s="2" t="inlineStr"/>
-      <c r="H520" s="2" t="n">
-        <v>41.9</v>
+      <c r="H520" s="2" t="inlineStr">
+        <is>
+          <t>41.9</t>
+        </is>
       </c>
       <c r="I520" s="2" t="inlineStr"/>
       <c r="J520" s="2" t="inlineStr"/>
@@ -16626,8 +16718,10 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E522" s="2" t="n">
-        <v>2380</v>
+      <c r="E522" s="2" t="inlineStr">
+        <is>
+          <t>2380</t>
+        </is>
       </c>
       <c r="F522" s="2" t="inlineStr">
         <is>
@@ -16658,13 +16752,17 @@
           <t>16/03/2022</t>
         </is>
       </c>
-      <c r="E523" s="2" t="n">
-        <v>2370</v>
+      <c r="E523" s="2" t="inlineStr">
+        <is>
+          <t>2370</t>
+        </is>
       </c>
       <c r="F523" s="2" t="inlineStr"/>
       <c r="G523" s="2" t="inlineStr"/>
-      <c r="H523" s="2" t="n">
-        <v>50.4</v>
+      <c r="H523" s="2" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
       </c>
       <c r="I523" s="2" t="inlineStr"/>
       <c r="J523" s="2" t="inlineStr"/>
@@ -16688,13 +16786,17 @@
           <t>16/03/2022</t>
         </is>
       </c>
-      <c r="E524" s="2" t="n">
-        <v>2370</v>
+      <c r="E524" s="2" t="inlineStr">
+        <is>
+          <t>2370</t>
+        </is>
       </c>
       <c r="F524" s="2" t="inlineStr"/>
       <c r="G524" s="2" t="inlineStr"/>
-      <c r="H524" s="2" t="n">
-        <v>49.7</v>
+      <c r="H524" s="2" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
       </c>
       <c r="I524" s="2" t="inlineStr"/>
       <c r="J524" s="2" t="inlineStr"/>
@@ -16740,8 +16842,10 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E526" s="2" t="n">
-        <v>2380</v>
+      <c r="E526" s="2" t="inlineStr">
+        <is>
+          <t>2380</t>
+        </is>
       </c>
       <c r="F526" s="2" t="inlineStr">
         <is>
@@ -16772,13 +16876,17 @@
           <t>17/03/2022</t>
         </is>
       </c>
-      <c r="E527" s="2" t="n">
-        <v>2380</v>
+      <c r="E527" s="2" t="inlineStr">
+        <is>
+          <t>2380</t>
+        </is>
       </c>
       <c r="F527" s="2" t="inlineStr"/>
       <c r="G527" s="2" t="inlineStr"/>
-      <c r="H527" s="2" t="n">
-        <v>49.7</v>
+      <c r="H527" s="2" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
       </c>
       <c r="I527" s="2" t="inlineStr"/>
       <c r="J527" s="2" t="inlineStr"/>
@@ -16802,13 +16910,17 @@
           <t>17/03/2022</t>
         </is>
       </c>
-      <c r="E528" s="2" t="n">
-        <v>2390</v>
+      <c r="E528" s="2" t="inlineStr">
+        <is>
+          <t>2390</t>
+        </is>
       </c>
       <c r="F528" s="2" t="inlineStr"/>
       <c r="G528" s="2" t="inlineStr"/>
-      <c r="H528" s="2" t="n">
-        <v>48.6</v>
+      <c r="H528" s="2" t="inlineStr">
+        <is>
+          <t>48.6</t>
+        </is>
       </c>
       <c r="I528" s="2" t="inlineStr"/>
       <c r="J528" s="2" t="inlineStr"/>
@@ -16854,8 +16966,10 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E530" s="2" t="n">
-        <v>2380</v>
+      <c r="E530" s="2" t="inlineStr">
+        <is>
+          <t>2380</t>
+        </is>
       </c>
       <c r="F530" s="2" t="inlineStr">
         <is>
@@ -16886,13 +17000,17 @@
           <t>18/03/2022</t>
         </is>
       </c>
-      <c r="E531" s="2" t="n">
-        <v>2390</v>
+      <c r="E531" s="2" t="inlineStr">
+        <is>
+          <t>2390</t>
+        </is>
       </c>
       <c r="F531" s="2" t="inlineStr"/>
       <c r="G531" s="2" t="inlineStr"/>
-      <c r="H531" s="2" t="n">
-        <v>45.6</v>
+      <c r="H531" s="2" t="inlineStr">
+        <is>
+          <t>45.6</t>
+        </is>
       </c>
       <c r="I531" s="2" t="inlineStr"/>
       <c r="J531" s="2" t="inlineStr"/>
@@ -16916,13 +17034,17 @@
           <t>18/03/2022</t>
         </is>
       </c>
-      <c r="E532" s="2" t="n">
-        <v>2400</v>
+      <c r="E532" s="2" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
       </c>
       <c r="F532" s="2" t="inlineStr"/>
       <c r="G532" s="2" t="inlineStr"/>
-      <c r="H532" s="2" t="n">
-        <v>46.8</v>
+      <c r="H532" s="2" t="inlineStr">
+        <is>
+          <t>46.8</t>
+        </is>
       </c>
       <c r="I532" s="2" t="inlineStr"/>
       <c r="J532" s="2" t="inlineStr"/>
@@ -17002,13 +17124,17 @@
           <t>21/03/2022</t>
         </is>
       </c>
-      <c r="E535" s="2" t="n">
-        <v>2370</v>
+      <c r="E535" s="2" t="inlineStr">
+        <is>
+          <t>2370</t>
+        </is>
       </c>
       <c r="F535" s="2" t="inlineStr"/>
       <c r="G535" s="2" t="inlineStr"/>
-      <c r="H535" s="2" t="n">
-        <v>44.4</v>
+      <c r="H535" s="2" t="inlineStr">
+        <is>
+          <t>44.4</t>
+        </is>
       </c>
       <c r="I535" s="2" t="inlineStr"/>
       <c r="J535" s="2" t="inlineStr"/>
@@ -17032,13 +17158,17 @@
           <t>21/03/2022</t>
         </is>
       </c>
-      <c r="E536" s="2" t="n">
-        <v>2360</v>
+      <c r="E536" s="2" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
       </c>
       <c r="F536" s="2" t="inlineStr"/>
       <c r="G536" s="2" t="inlineStr"/>
-      <c r="H536" s="2" t="n">
-        <v>45.3</v>
+      <c r="H536" s="2" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
       </c>
       <c r="I536" s="2" t="inlineStr"/>
       <c r="J536" s="2" t="inlineStr"/>
@@ -17361,11 +17491,23 @@
           <t>2nd Floor Walls (A-E)(35-45),W1(U-GG)(31-35),W1 (Z-EE)(37-41)</t>
         </is>
       </c>
-      <c r="D547" s="2" t="inlineStr"/>
-      <c r="E547" s="2" t="inlineStr"/>
+      <c r="D547" s="2" t="inlineStr">
+        <is>
+          <t>23/03/2022</t>
+        </is>
+      </c>
+      <c r="E547" s="2" t="inlineStr">
+        <is>
+          <t>2390</t>
+        </is>
+      </c>
       <c r="F547" s="2" t="inlineStr"/>
       <c r="G547" s="2" t="inlineStr"/>
-      <c r="H547" s="2" t="inlineStr"/>
+      <c r="H547" s="2" t="inlineStr">
+        <is>
+          <t>40.2</t>
+        </is>
+      </c>
       <c r="I547" s="2" t="inlineStr"/>
       <c r="J547" s="2" t="inlineStr"/>
     </row>
@@ -17383,11 +17525,23 @@
           <t>2nd Floor Walls (A-E)(35-45),W1(U-GG)(31-35),W1 (Z-EE)(37-41)</t>
         </is>
       </c>
-      <c r="D548" s="2" t="inlineStr"/>
-      <c r="E548" s="2" t="inlineStr"/>
+      <c r="D548" s="2" t="inlineStr">
+        <is>
+          <t>23/03/2022</t>
+        </is>
+      </c>
+      <c r="E548" s="2" t="inlineStr">
+        <is>
+          <t>2410</t>
+        </is>
+      </c>
       <c r="F548" s="2" t="inlineStr"/>
       <c r="G548" s="2" t="inlineStr"/>
-      <c r="H548" s="2" t="inlineStr"/>
+      <c r="H548" s="2" t="inlineStr">
+        <is>
+          <t>44.6</t>
+        </is>
+      </c>
       <c r="I548" s="2" t="inlineStr"/>
       <c r="J548" s="2" t="inlineStr"/>
     </row>
@@ -17432,8 +17586,10 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E550" s="2" t="n">
-        <v>2350</v>
+      <c r="E550" s="2" t="inlineStr">
+        <is>
+          <t>2350</t>
+        </is>
       </c>
       <c r="F550" s="2" t="inlineStr">
         <is>
@@ -17486,13 +17642,17 @@
           <t>14/03/2022</t>
         </is>
       </c>
-      <c r="E552" s="2" t="n">
-        <v>2340</v>
+      <c r="E552" s="2" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
       </c>
       <c r="F552" s="2" t="inlineStr"/>
       <c r="G552" s="2" t="inlineStr"/>
-      <c r="H552" s="2" t="n">
-        <v>38.2</v>
+      <c r="H552" s="2" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
       </c>
       <c r="I552" s="2" t="inlineStr"/>
       <c r="J552" s="2" t="inlineStr"/>
@@ -17538,8 +17698,10 @@
           <t>11/03/2022</t>
         </is>
       </c>
-      <c r="E554" s="2" t="n">
-        <v>2320</v>
+      <c r="E554" s="2" t="inlineStr">
+        <is>
+          <t>2320</t>
+        </is>
       </c>
       <c r="F554" s="2" t="inlineStr"/>
       <c r="G554" s="2" t="inlineStr">
@@ -17636,8 +17798,10 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E558" s="2" t="n">
-        <v>2350</v>
+      <c r="E558" s="2" t="inlineStr">
+        <is>
+          <t>2350</t>
+        </is>
       </c>
       <c r="F558" s="2" t="inlineStr">
         <is>
@@ -17734,8 +17898,10 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E562" s="2" t="n">
-        <v>2370</v>
+      <c r="E562" s="2" t="inlineStr">
+        <is>
+          <t>2370</t>
+        </is>
       </c>
       <c r="F562" s="2" t="inlineStr">
         <is>
@@ -17832,8 +17998,10 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E566" s="2" t="n">
-        <v>2360</v>
+      <c r="E566" s="2" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
       </c>
       <c r="F566" s="2" t="inlineStr">
         <is>
@@ -17930,8 +18098,10 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E570" s="2" t="n">
-        <v>2350</v>
+      <c r="E570" s="2" t="inlineStr">
+        <is>
+          <t>2350</t>
+        </is>
       </c>
       <c r="F570" s="2" t="inlineStr">
         <is>
@@ -18028,8 +18198,10 @@
           <t>10/03/2022</t>
         </is>
       </c>
-      <c r="E574" s="2" t="n">
-        <v>2360</v>
+      <c r="E574" s="2" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
       </c>
       <c r="F574" s="2" t="inlineStr">
         <is>
@@ -18126,8 +18298,10 @@
           <t>11/03/2022</t>
         </is>
       </c>
-      <c r="E578" s="2" t="n">
-        <v>2380</v>
+      <c r="E578" s="2" t="inlineStr">
+        <is>
+          <t>2380</t>
+        </is>
       </c>
       <c r="F578" s="2" t="inlineStr">
         <is>

--- a/Cube_finish.xlsx
+++ b/Cube_finish.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J600"/>
+  <dimension ref="A1:J1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13524,10 +13524,8 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E409" s="2" t="inlineStr">
-        <is>
-          <t>2390</t>
-        </is>
+      <c r="E409" s="2" t="n">
+        <v>2390</v>
       </c>
       <c r="F409" s="2" t="inlineStr"/>
       <c r="G409" s="2" t="inlineStr"/>
@@ -14959,12 +14957,24 @@
           <t>First Floor Wall (36-45)(H-GG)</t>
         </is>
       </c>
-      <c r="D458" s="2" t="inlineStr"/>
-      <c r="E458" s="2" t="inlineStr"/>
+      <c r="D458" s="2" t="inlineStr">
+        <is>
+          <t>24/03/2022</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
       <c r="F458" s="2" t="inlineStr"/>
       <c r="G458" s="2" t="inlineStr"/>
       <c r="H458" s="2" t="inlineStr"/>
-      <c r="I458" s="2" t="inlineStr"/>
+      <c r="I458" s="2" t="inlineStr">
+        <is>
+          <t>44.1</t>
+        </is>
+      </c>
       <c r="J458" s="2" t="inlineStr"/>
     </row>
     <row r="459">
@@ -17615,11 +17625,23 @@
           <t>2nd Floor Walls (30-33)(B-N), W1(41-45)(N-P), W1(40-43)(Z-GG)</t>
         </is>
       </c>
-      <c r="D551" s="2" t="inlineStr"/>
-      <c r="E551" s="2" t="inlineStr"/>
+      <c r="D551" s="2" t="inlineStr">
+        <is>
+          <t>24/03/2022</t>
+        </is>
+      </c>
+      <c r="E551" s="2" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
       <c r="F551" s="2" t="inlineStr"/>
       <c r="G551" s="2" t="inlineStr"/>
-      <c r="H551" s="2" t="inlineStr"/>
+      <c r="H551" s="2" t="inlineStr">
+        <is>
+          <t>45.2</t>
+        </is>
+      </c>
       <c r="I551" s="2" t="inlineStr"/>
       <c r="J551" s="2" t="inlineStr"/>
     </row>
@@ -18380,232 +18402,5308 @@
       <c r="J581" s="2" t="inlineStr"/>
     </row>
     <row r="582">
-      <c r="A582" s="2" t="n"/>
-      <c r="B582" s="2" t="n"/>
-      <c r="C582" s="2" t="n"/>
-      <c r="D582" s="2" t="n"/>
-      <c r="E582" s="2" t="n"/>
-      <c r="F582" s="2" t="n"/>
-      <c r="G582" s="2" t="n"/>
-      <c r="H582" s="2" t="n"/>
-      <c r="I582" s="2" t="n"/>
-      <c r="J582" s="2" t="n"/>
+      <c r="A582" s="2" t="inlineStr">
+        <is>
+          <t>111A</t>
+        </is>
+      </c>
+      <c r="B582" s="2" t="inlineStr"/>
+      <c r="C582" s="2" t="inlineStr"/>
+      <c r="D582" s="2" t="inlineStr">
+        <is>
+          <t>23/03/2022</t>
+        </is>
+      </c>
+      <c r="E582" s="2" t="inlineStr">
+        <is>
+          <t>2320</t>
+        </is>
+      </c>
+      <c r="F582" s="2" t="inlineStr">
+        <is>
+          <t>35.9(16Days)</t>
+        </is>
+      </c>
+      <c r="G582" s="2" t="inlineStr"/>
+      <c r="H582" s="2" t="inlineStr"/>
+      <c r="I582" s="2" t="inlineStr"/>
+      <c r="J582" s="2" t="inlineStr"/>
     </row>
     <row r="583">
-      <c r="A583" s="2" t="n"/>
-      <c r="B583" s="2" t="n"/>
-      <c r="C583" s="2" t="n"/>
-      <c r="D583" s="2" t="n"/>
-      <c r="E583" s="2" t="n"/>
-      <c r="F583" s="2" t="n"/>
-      <c r="G583" s="2" t="n"/>
-      <c r="H583" s="2" t="n"/>
-      <c r="I583" s="2" t="n"/>
-      <c r="J583" s="2" t="n"/>
+      <c r="A583" s="2" t="inlineStr">
+        <is>
+          <t>111B</t>
+        </is>
+      </c>
+      <c r="B583" s="2" t="inlineStr"/>
+      <c r="C583" s="2" t="inlineStr"/>
+      <c r="D583" s="2" t="inlineStr"/>
+      <c r="E583" s="2" t="inlineStr"/>
+      <c r="F583" s="2" t="inlineStr"/>
+      <c r="G583" s="2" t="inlineStr"/>
+      <c r="H583" s="2" t="inlineStr"/>
+      <c r="I583" s="2" t="inlineStr"/>
+      <c r="J583" s="2" t="inlineStr"/>
     </row>
     <row r="584">
-      <c r="A584" s="2" t="n"/>
-      <c r="B584" s="2" t="n"/>
-      <c r="C584" s="2" t="n"/>
-      <c r="D584" s="2" t="n"/>
-      <c r="E584" s="2" t="n"/>
-      <c r="F584" s="2" t="n"/>
-      <c r="G584" s="2" t="n"/>
-      <c r="H584" s="2" t="n"/>
-      <c r="I584" s="2" t="n"/>
-      <c r="J584" s="2" t="n"/>
+      <c r="A584" s="2" t="inlineStr">
+        <is>
+          <t>111C</t>
+        </is>
+      </c>
+      <c r="B584" s="2" t="inlineStr"/>
+      <c r="C584" s="2" t="inlineStr"/>
+      <c r="D584" s="2" t="inlineStr"/>
+      <c r="E584" s="2" t="inlineStr"/>
+      <c r="F584" s="2" t="inlineStr"/>
+      <c r="G584" s="2" t="inlineStr"/>
+      <c r="H584" s="2" t="inlineStr"/>
+      <c r="I584" s="2" t="inlineStr"/>
+      <c r="J584" s="2" t="inlineStr"/>
     </row>
     <row r="585">
-      <c r="A585" s="2" t="n"/>
-      <c r="B585" s="2" t="n"/>
-      <c r="C585" s="2" t="n"/>
-      <c r="D585" s="2" t="n"/>
-      <c r="E585" s="2" t="n"/>
-      <c r="F585" s="2" t="n"/>
-      <c r="G585" s="2" t="n"/>
-      <c r="H585" s="2" t="n"/>
-      <c r="I585" s="2" t="n"/>
-      <c r="J585" s="2" t="n"/>
+      <c r="A585" s="2" t="inlineStr">
+        <is>
+          <t>111D</t>
+        </is>
+      </c>
+      <c r="B585" s="2" t="inlineStr"/>
+      <c r="C585" s="2" t="inlineStr"/>
+      <c r="D585" s="2" t="inlineStr"/>
+      <c r="E585" s="2" t="inlineStr"/>
+      <c r="F585" s="2" t="inlineStr"/>
+      <c r="G585" s="2" t="inlineStr"/>
+      <c r="H585" s="2" t="inlineStr"/>
+      <c r="I585" s="2" t="inlineStr"/>
+      <c r="J585" s="2" t="inlineStr"/>
     </row>
     <row r="586">
-      <c r="A586" s="2" t="n"/>
-      <c r="B586" s="2" t="n"/>
-      <c r="C586" s="2" t="n"/>
-      <c r="D586" s="2" t="n"/>
-      <c r="E586" s="2" t="n"/>
-      <c r="F586" s="2" t="n"/>
-      <c r="G586" s="2" t="n"/>
-      <c r="H586" s="2" t="n"/>
-      <c r="I586" s="2" t="n"/>
-      <c r="J586" s="2" t="n"/>
+      <c r="A586" s="2" t="inlineStr">
+        <is>
+          <t>112A</t>
+        </is>
+      </c>
+      <c r="B586" s="2" t="inlineStr"/>
+      <c r="C586" s="2" t="inlineStr"/>
+      <c r="D586" s="2" t="inlineStr">
+        <is>
+          <t>23/03/2022</t>
+        </is>
+      </c>
+      <c r="E586" s="2" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="F586" s="2" t="inlineStr">
+        <is>
+          <t>38.3(16Days)</t>
+        </is>
+      </c>
+      <c r="G586" s="2" t="inlineStr"/>
+      <c r="H586" s="2" t="inlineStr"/>
+      <c r="I586" s="2" t="inlineStr"/>
+      <c r="J586" s="2" t="inlineStr"/>
     </row>
     <row r="587">
-      <c r="A587" s="2" t="n"/>
-      <c r="B587" s="2" t="n"/>
-      <c r="C587" s="2" t="n"/>
-      <c r="D587" s="2" t="n"/>
-      <c r="E587" s="2" t="n"/>
-      <c r="F587" s="2" t="n"/>
-      <c r="G587" s="2" t="n"/>
-      <c r="H587" s="2" t="n"/>
-      <c r="I587" s="2" t="n"/>
-      <c r="J587" s="2" t="n"/>
+      <c r="A587" s="2" t="inlineStr">
+        <is>
+          <t>112B</t>
+        </is>
+      </c>
+      <c r="B587" s="2" t="inlineStr"/>
+      <c r="C587" s="2" t="inlineStr"/>
+      <c r="D587" s="2" t="inlineStr"/>
+      <c r="E587" s="2" t="inlineStr"/>
+      <c r="F587" s="2" t="inlineStr"/>
+      <c r="G587" s="2" t="inlineStr"/>
+      <c r="H587" s="2" t="inlineStr"/>
+      <c r="I587" s="2" t="inlineStr"/>
+      <c r="J587" s="2" t="inlineStr"/>
     </row>
     <row r="588">
-      <c r="A588" s="2" t="n"/>
-      <c r="B588" s="2" t="n"/>
-      <c r="C588" s="2" t="n"/>
-      <c r="D588" s="2" t="n"/>
-      <c r="E588" s="2" t="n"/>
-      <c r="F588" s="2" t="n"/>
-      <c r="G588" s="2" t="n"/>
-      <c r="H588" s="2" t="n"/>
-      <c r="I588" s="2" t="n"/>
-      <c r="J588" s="2" t="n"/>
+      <c r="A588" s="2" t="inlineStr">
+        <is>
+          <t>112C</t>
+        </is>
+      </c>
+      <c r="B588" s="2" t="inlineStr"/>
+      <c r="C588" s="2" t="inlineStr"/>
+      <c r="D588" s="2" t="inlineStr"/>
+      <c r="E588" s="2" t="inlineStr"/>
+      <c r="F588" s="2" t="inlineStr"/>
+      <c r="G588" s="2" t="inlineStr"/>
+      <c r="H588" s="2" t="inlineStr"/>
+      <c r="I588" s="2" t="inlineStr"/>
+      <c r="J588" s="2" t="inlineStr"/>
     </row>
     <row r="589">
-      <c r="A589" s="2" t="n"/>
-      <c r="B589" s="2" t="n"/>
-      <c r="C589" s="2" t="n"/>
-      <c r="D589" s="2" t="n"/>
-      <c r="E589" s="2" t="n"/>
-      <c r="F589" s="2" t="n"/>
-      <c r="G589" s="2" t="n"/>
-      <c r="H589" s="2" t="n"/>
-      <c r="I589" s="2" t="n"/>
-      <c r="J589" s="2" t="n"/>
+      <c r="A589" s="2" t="inlineStr">
+        <is>
+          <t>112D</t>
+        </is>
+      </c>
+      <c r="B589" s="2" t="inlineStr"/>
+      <c r="C589" s="2" t="inlineStr"/>
+      <c r="D589" s="2" t="inlineStr"/>
+      <c r="E589" s="2" t="inlineStr"/>
+      <c r="F589" s="2" t="inlineStr"/>
+      <c r="G589" s="2" t="inlineStr"/>
+      <c r="H589" s="2" t="inlineStr"/>
+      <c r="I589" s="2" t="inlineStr"/>
+      <c r="J589" s="2" t="inlineStr"/>
     </row>
     <row r="590">
-      <c r="A590" s="2" t="n"/>
-      <c r="B590" s="2" t="n"/>
-      <c r="C590" s="2" t="n"/>
-      <c r="D590" s="2" t="n"/>
-      <c r="E590" s="2" t="n"/>
-      <c r="F590" s="2" t="n"/>
-      <c r="G590" s="2" t="n"/>
-      <c r="H590" s="2" t="n"/>
-      <c r="I590" s="2" t="n"/>
-      <c r="J590" s="2" t="n"/>
+      <c r="A590" s="2" t="inlineStr">
+        <is>
+          <t>113A</t>
+        </is>
+      </c>
+      <c r="B590" s="2" t="inlineStr"/>
+      <c r="C590" s="2" t="inlineStr"/>
+      <c r="D590" s="2" t="inlineStr">
+        <is>
+          <t>23/03/2022</t>
+        </is>
+      </c>
+      <c r="E590" s="2" t="inlineStr">
+        <is>
+          <t>2350</t>
+        </is>
+      </c>
+      <c r="F590" s="2" t="inlineStr"/>
+      <c r="G590" s="2" t="inlineStr">
+        <is>
+          <t>42.3</t>
+        </is>
+      </c>
+      <c r="H590" s="2" t="inlineStr"/>
+      <c r="I590" s="2" t="inlineStr"/>
+      <c r="J590" s="2" t="inlineStr"/>
     </row>
     <row r="591">
-      <c r="A591" s="2" t="n"/>
-      <c r="B591" s="2" t="n"/>
-      <c r="C591" s="2" t="n"/>
-      <c r="D591" s="2" t="n"/>
-      <c r="E591" s="2" t="n"/>
-      <c r="F591" s="2" t="n"/>
-      <c r="G591" s="2" t="n"/>
-      <c r="H591" s="2" t="n"/>
-      <c r="I591" s="2" t="n"/>
-      <c r="J591" s="2" t="n"/>
+      <c r="A591" s="2" t="inlineStr">
+        <is>
+          <t>113B</t>
+        </is>
+      </c>
+      <c r="B591" s="2" t="inlineStr"/>
+      <c r="C591" s="2" t="inlineStr"/>
+      <c r="D591" s="2" t="inlineStr"/>
+      <c r="E591" s="2" t="inlineStr"/>
+      <c r="F591" s="2" t="inlineStr"/>
+      <c r="G591" s="2" t="inlineStr"/>
+      <c r="H591" s="2" t="inlineStr"/>
+      <c r="I591" s="2" t="inlineStr"/>
+      <c r="J591" s="2" t="inlineStr"/>
     </row>
     <row r="592">
-      <c r="A592" s="2" t="n"/>
-      <c r="B592" s="2" t="n"/>
-      <c r="C592" s="2" t="n"/>
-      <c r="D592" s="2" t="n"/>
-      <c r="E592" s="2" t="n"/>
-      <c r="F592" s="2" t="n"/>
-      <c r="G592" s="2" t="n"/>
-      <c r="H592" s="2" t="n"/>
-      <c r="I592" s="2" t="n"/>
-      <c r="J592" s="2" t="n"/>
+      <c r="A592" s="2" t="inlineStr">
+        <is>
+          <t>113C</t>
+        </is>
+      </c>
+      <c r="B592" s="2" t="inlineStr"/>
+      <c r="C592" s="2" t="inlineStr"/>
+      <c r="D592" s="2" t="inlineStr"/>
+      <c r="E592" s="2" t="inlineStr"/>
+      <c r="F592" s="2" t="inlineStr"/>
+      <c r="G592" s="2" t="inlineStr"/>
+      <c r="H592" s="2" t="inlineStr"/>
+      <c r="I592" s="2" t="inlineStr"/>
+      <c r="J592" s="2" t="inlineStr"/>
     </row>
     <row r="593">
-      <c r="A593" s="2" t="n"/>
-      <c r="B593" s="2" t="n"/>
-      <c r="C593" s="2" t="n"/>
-      <c r="D593" s="2" t="n"/>
-      <c r="E593" s="2" t="n"/>
-      <c r="F593" s="2" t="n"/>
-      <c r="G593" s="2" t="n"/>
-      <c r="H593" s="2" t="n"/>
-      <c r="I593" s="2" t="n"/>
-      <c r="J593" s="2" t="n"/>
+      <c r="A593" s="2" t="inlineStr">
+        <is>
+          <t>113D</t>
+        </is>
+      </c>
+      <c r="B593" s="2" t="inlineStr"/>
+      <c r="C593" s="2" t="inlineStr"/>
+      <c r="D593" s="2" t="inlineStr"/>
+      <c r="E593" s="2" t="inlineStr"/>
+      <c r="F593" s="2" t="inlineStr"/>
+      <c r="G593" s="2" t="inlineStr"/>
+      <c r="H593" s="2" t="inlineStr"/>
+      <c r="I593" s="2" t="inlineStr"/>
+      <c r="J593" s="2" t="inlineStr"/>
     </row>
     <row r="594">
-      <c r="A594" s="2" t="n"/>
-      <c r="B594" s="2" t="n"/>
-      <c r="C594" s="2" t="n"/>
-      <c r="D594" s="2" t="n"/>
-      <c r="E594" s="2" t="n"/>
-      <c r="F594" s="2" t="n"/>
-      <c r="G594" s="2" t="n"/>
-      <c r="H594" s="2" t="n"/>
-      <c r="I594" s="2" t="n"/>
-      <c r="J594" s="2" t="n"/>
+      <c r="A594" s="2" t="inlineStr">
+        <is>
+          <t>114A</t>
+        </is>
+      </c>
+      <c r="B594" s="2" t="inlineStr"/>
+      <c r="C594" s="2" t="inlineStr"/>
+      <c r="D594" s="2" t="inlineStr">
+        <is>
+          <t>24/03/2022</t>
+        </is>
+      </c>
+      <c r="E594" s="2" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="F594" s="2" t="inlineStr"/>
+      <c r="G594" s="2" t="inlineStr">
+        <is>
+          <t>40.5</t>
+        </is>
+      </c>
+      <c r="H594" s="2" t="inlineStr"/>
+      <c r="I594" s="2" t="inlineStr"/>
+      <c r="J594" s="2" t="inlineStr"/>
     </row>
     <row r="595">
-      <c r="A595" s="2" t="n"/>
-      <c r="B595" s="2" t="n"/>
-      <c r="C595" s="2" t="n"/>
-      <c r="D595" s="2" t="n"/>
-      <c r="E595" s="2" t="n"/>
-      <c r="F595" s="2" t="n"/>
-      <c r="G595" s="2" t="n"/>
-      <c r="H595" s="2" t="n"/>
-      <c r="I595" s="2" t="n"/>
-      <c r="J595" s="2" t="n"/>
+      <c r="A595" s="2" t="inlineStr">
+        <is>
+          <t>114B</t>
+        </is>
+      </c>
+      <c r="B595" s="2" t="inlineStr"/>
+      <c r="C595" s="2" t="inlineStr"/>
+      <c r="D595" s="2" t="inlineStr"/>
+      <c r="E595" s="2" t="inlineStr"/>
+      <c r="F595" s="2" t="inlineStr"/>
+      <c r="G595" s="2" t="inlineStr"/>
+      <c r="H595" s="2" t="inlineStr"/>
+      <c r="I595" s="2" t="inlineStr"/>
+      <c r="J595" s="2" t="inlineStr"/>
     </row>
     <row r="596">
-      <c r="A596" s="2" t="n"/>
-      <c r="B596" s="2" t="n"/>
-      <c r="C596" s="2" t="n"/>
-      <c r="D596" s="2" t="n"/>
-      <c r="E596" s="2" t="n"/>
-      <c r="F596" s="2" t="n"/>
-      <c r="G596" s="2" t="n"/>
-      <c r="H596" s="2" t="n"/>
-      <c r="I596" s="2" t="n"/>
-      <c r="J596" s="2" t="n"/>
+      <c r="A596" s="2" t="inlineStr">
+        <is>
+          <t>114C</t>
+        </is>
+      </c>
+      <c r="B596" s="2" t="inlineStr"/>
+      <c r="C596" s="2" t="inlineStr"/>
+      <c r="D596" s="2" t="inlineStr"/>
+      <c r="E596" s="2" t="inlineStr"/>
+      <c r="F596" s="2" t="inlineStr"/>
+      <c r="G596" s="2" t="inlineStr"/>
+      <c r="H596" s="2" t="inlineStr"/>
+      <c r="I596" s="2" t="inlineStr"/>
+      <c r="J596" s="2" t="inlineStr"/>
     </row>
     <row r="597">
-      <c r="A597" s="2" t="n"/>
-      <c r="B597" s="2" t="n"/>
-      <c r="C597" s="2" t="n"/>
-      <c r="D597" s="2" t="n"/>
-      <c r="E597" s="2" t="n"/>
-      <c r="F597" s="2" t="n"/>
-      <c r="G597" s="2" t="n"/>
-      <c r="H597" s="2" t="n"/>
-      <c r="I597" s="2" t="n"/>
-      <c r="J597" s="2" t="n"/>
+      <c r="A597" s="2" t="inlineStr">
+        <is>
+          <t>114D</t>
+        </is>
+      </c>
+      <c r="B597" s="2" t="inlineStr"/>
+      <c r="C597" s="2" t="inlineStr"/>
+      <c r="D597" s="2" t="inlineStr"/>
+      <c r="E597" s="2" t="inlineStr"/>
+      <c r="F597" s="2" t="inlineStr"/>
+      <c r="G597" s="2" t="inlineStr"/>
+      <c r="H597" s="2" t="inlineStr"/>
+      <c r="I597" s="2" t="inlineStr"/>
+      <c r="J597" s="2" t="inlineStr"/>
     </row>
     <row r="598">
-      <c r="A598" s="2" t="n"/>
-      <c r="B598" s="2" t="n"/>
-      <c r="C598" s="2" t="n"/>
-      <c r="D598" s="2" t="n"/>
-      <c r="E598" s="2" t="n"/>
-      <c r="F598" s="2" t="n"/>
-      <c r="G598" s="2" t="n"/>
-      <c r="H598" s="2" t="n"/>
-      <c r="I598" s="2" t="n"/>
-      <c r="J598" s="2" t="n"/>
+      <c r="A598" s="2" t="inlineStr">
+        <is>
+          <t>115A</t>
+        </is>
+      </c>
+      <c r="B598" s="2" t="inlineStr"/>
+      <c r="C598" s="2" t="inlineStr"/>
+      <c r="D598" s="2" t="inlineStr">
+        <is>
+          <t>24/03/2022</t>
+        </is>
+      </c>
+      <c r="E598" s="2" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="F598" s="2" t="inlineStr"/>
+      <c r="G598" s="2" t="inlineStr">
+        <is>
+          <t>42.7</t>
+        </is>
+      </c>
+      <c r="H598" s="2" t="inlineStr"/>
+      <c r="I598" s="2" t="inlineStr"/>
+      <c r="J598" s="2" t="inlineStr"/>
     </row>
     <row r="599">
-      <c r="A599" s="2" t="n"/>
-      <c r="B599" s="2" t="n"/>
-      <c r="C599" s="2" t="n"/>
-      <c r="D599" s="2" t="n"/>
-      <c r="E599" s="2" t="n"/>
-      <c r="F599" s="2" t="n"/>
-      <c r="G599" s="2" t="n"/>
-      <c r="H599" s="2" t="n"/>
-      <c r="I599" s="2" t="n"/>
-      <c r="J599" s="2" t="n"/>
+      <c r="A599" s="2" t="inlineStr">
+        <is>
+          <t>115B</t>
+        </is>
+      </c>
+      <c r="B599" s="2" t="inlineStr"/>
+      <c r="C599" s="2" t="inlineStr"/>
+      <c r="D599" s="2" t="inlineStr"/>
+      <c r="E599" s="2" t="inlineStr"/>
+      <c r="F599" s="2" t="inlineStr"/>
+      <c r="G599" s="2" t="inlineStr"/>
+      <c r="H599" s="2" t="inlineStr"/>
+      <c r="I599" s="2" t="inlineStr"/>
+      <c r="J599" s="2" t="inlineStr"/>
     </row>
     <row r="600">
-      <c r="A600" s="2" t="n"/>
-      <c r="B600" s="2" t="n"/>
-      <c r="C600" s="2" t="n"/>
-      <c r="D600" s="2" t="n"/>
-      <c r="E600" s="2" t="n"/>
-      <c r="F600" s="2" t="n"/>
-      <c r="G600" s="2" t="n"/>
-      <c r="H600" s="2" t="n"/>
-      <c r="I600" s="2" t="n"/>
-      <c r="J600" s="2" t="n"/>
+      <c r="A600" s="2" t="inlineStr">
+        <is>
+          <t>115C</t>
+        </is>
+      </c>
+      <c r="B600" s="2" t="inlineStr"/>
+      <c r="C600" s="2" t="inlineStr"/>
+      <c r="D600" s="2" t="inlineStr"/>
+      <c r="E600" s="2" t="inlineStr"/>
+      <c r="F600" s="2" t="inlineStr"/>
+      <c r="G600" s="2" t="inlineStr"/>
+      <c r="H600" s="2" t="inlineStr"/>
+      <c r="I600" s="2" t="inlineStr"/>
+      <c r="J600" s="2" t="inlineStr"/>
+    </row>
+    <row r="601">
+      <c r="A601" s="2" t="inlineStr">
+        <is>
+          <t>115D</t>
+        </is>
+      </c>
+      <c r="B601" s="2" t="inlineStr"/>
+      <c r="C601" s="2" t="inlineStr"/>
+      <c r="D601" s="2" t="inlineStr"/>
+      <c r="E601" s="2" t="inlineStr"/>
+      <c r="F601" s="2" t="inlineStr"/>
+      <c r="G601" s="2" t="inlineStr"/>
+      <c r="H601" s="2" t="inlineStr"/>
+      <c r="I601" s="2" t="inlineStr"/>
+      <c r="J601" s="2" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" s="2" t="inlineStr">
+        <is>
+          <t>116A</t>
+        </is>
+      </c>
+      <c r="B602" s="2" t="inlineStr"/>
+      <c r="C602" s="2" t="inlineStr"/>
+      <c r="D602" s="2" t="inlineStr"/>
+      <c r="E602" s="2" t="inlineStr"/>
+      <c r="F602" s="2" t="inlineStr"/>
+      <c r="G602" s="2" t="inlineStr"/>
+      <c r="H602" s="2" t="inlineStr"/>
+      <c r="I602" s="2" t="inlineStr"/>
+      <c r="J602" s="2" t="inlineStr"/>
+    </row>
+    <row r="603">
+      <c r="A603" s="2" t="inlineStr">
+        <is>
+          <t>116B</t>
+        </is>
+      </c>
+      <c r="B603" s="2" t="inlineStr"/>
+      <c r="C603" s="2" t="inlineStr"/>
+      <c r="D603" s="2" t="inlineStr"/>
+      <c r="E603" s="2" t="inlineStr"/>
+      <c r="F603" s="2" t="inlineStr"/>
+      <c r="G603" s="2" t="inlineStr"/>
+      <c r="H603" s="2" t="inlineStr"/>
+      <c r="I603" s="2" t="inlineStr"/>
+      <c r="J603" s="2" t="inlineStr"/>
+    </row>
+    <row r="604">
+      <c r="A604" s="2" t="inlineStr">
+        <is>
+          <t>116C</t>
+        </is>
+      </c>
+      <c r="B604" s="2" t="inlineStr"/>
+      <c r="C604" s="2" t="inlineStr"/>
+      <c r="D604" s="2" t="inlineStr"/>
+      <c r="E604" s="2" t="inlineStr"/>
+      <c r="F604" s="2" t="inlineStr"/>
+      <c r="G604" s="2" t="inlineStr"/>
+      <c r="H604" s="2" t="inlineStr"/>
+      <c r="I604" s="2" t="inlineStr"/>
+      <c r="J604" s="2" t="inlineStr"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="2" t="inlineStr">
+        <is>
+          <t>116D</t>
+        </is>
+      </c>
+      <c r="B605" s="2" t="inlineStr"/>
+      <c r="C605" s="2" t="inlineStr"/>
+      <c r="D605" s="2" t="inlineStr"/>
+      <c r="E605" s="2" t="inlineStr"/>
+      <c r="F605" s="2" t="inlineStr"/>
+      <c r="G605" s="2" t="inlineStr"/>
+      <c r="H605" s="2" t="inlineStr"/>
+      <c r="I605" s="2" t="inlineStr"/>
+      <c r="J605" s="2" t="inlineStr"/>
+    </row>
+    <row r="606">
+      <c r="A606" s="2" t="inlineStr">
+        <is>
+          <t>117A</t>
+        </is>
+      </c>
+      <c r="B606" s="2" t="inlineStr"/>
+      <c r="C606" s="2" t="inlineStr"/>
+      <c r="D606" s="2" t="inlineStr">
+        <is>
+          <t>23/03/2022</t>
+        </is>
+      </c>
+      <c r="E606" s="2" t="inlineStr">
+        <is>
+          <t>2350</t>
+        </is>
+      </c>
+      <c r="F606" s="2" t="inlineStr">
+        <is>
+          <t>34.2(9Days)</t>
+        </is>
+      </c>
+      <c r="G606" s="2" t="inlineStr"/>
+      <c r="H606" s="2" t="inlineStr"/>
+      <c r="I606" s="2" t="inlineStr"/>
+      <c r="J606" s="2" t="inlineStr"/>
+    </row>
+    <row r="607">
+      <c r="A607" s="2" t="inlineStr">
+        <is>
+          <t>11B</t>
+        </is>
+      </c>
+      <c r="B607" s="2" t="inlineStr"/>
+      <c r="C607" s="2" t="inlineStr"/>
+      <c r="D607" s="2" t="inlineStr"/>
+      <c r="E607" s="2" t="inlineStr"/>
+      <c r="F607" s="2" t="inlineStr"/>
+      <c r="G607" s="2" t="inlineStr"/>
+      <c r="H607" s="2" t="inlineStr"/>
+      <c r="I607" s="2" t="inlineStr"/>
+      <c r="J607" s="2" t="inlineStr"/>
+    </row>
+    <row r="608">
+      <c r="A608" s="2" t="inlineStr">
+        <is>
+          <t>117C</t>
+        </is>
+      </c>
+      <c r="B608" s="2" t="inlineStr"/>
+      <c r="C608" s="2" t="inlineStr"/>
+      <c r="D608" s="2" t="inlineStr"/>
+      <c r="E608" s="2" t="inlineStr"/>
+      <c r="F608" s="2" t="inlineStr"/>
+      <c r="G608" s="2" t="inlineStr"/>
+      <c r="H608" s="2" t="inlineStr"/>
+      <c r="I608" s="2" t="inlineStr"/>
+      <c r="J608" s="2" t="inlineStr"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="2" t="inlineStr">
+        <is>
+          <t>117D</t>
+        </is>
+      </c>
+      <c r="B609" s="2" t="inlineStr"/>
+      <c r="C609" s="2" t="inlineStr"/>
+      <c r="D609" s="2" t="inlineStr"/>
+      <c r="E609" s="2" t="inlineStr"/>
+      <c r="F609" s="2" t="inlineStr"/>
+      <c r="G609" s="2" t="inlineStr"/>
+      <c r="H609" s="2" t="inlineStr"/>
+      <c r="I609" s="2" t="inlineStr"/>
+      <c r="J609" s="2" t="inlineStr"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="2" t="inlineStr">
+        <is>
+          <t>118A</t>
+        </is>
+      </c>
+      <c r="B610" s="2" t="inlineStr"/>
+      <c r="C610" s="2" t="inlineStr"/>
+      <c r="D610" s="2" t="inlineStr">
+        <is>
+          <t>23/03/2022</t>
+        </is>
+      </c>
+      <c r="E610" s="2" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="F610" s="2" t="inlineStr">
+        <is>
+          <t>40.5(8Days)</t>
+        </is>
+      </c>
+      <c r="G610" s="2" t="inlineStr"/>
+      <c r="H610" s="2" t="inlineStr"/>
+      <c r="I610" s="2" t="inlineStr"/>
+      <c r="J610" s="2" t="inlineStr"/>
+    </row>
+    <row r="611">
+      <c r="A611" s="2" t="inlineStr">
+        <is>
+          <t>118B</t>
+        </is>
+      </c>
+      <c r="B611" s="2" t="inlineStr"/>
+      <c r="C611" s="2" t="inlineStr"/>
+      <c r="D611" s="2" t="inlineStr"/>
+      <c r="E611" s="2" t="inlineStr"/>
+      <c r="F611" s="2" t="inlineStr"/>
+      <c r="G611" s="2" t="inlineStr"/>
+      <c r="H611" s="2" t="inlineStr"/>
+      <c r="I611" s="2" t="inlineStr"/>
+      <c r="J611" s="2" t="inlineStr"/>
+    </row>
+    <row r="612">
+      <c r="A612" s="2" t="inlineStr">
+        <is>
+          <t>118C</t>
+        </is>
+      </c>
+      <c r="B612" s="2" t="inlineStr"/>
+      <c r="C612" s="2" t="inlineStr"/>
+      <c r="D612" s="2" t="inlineStr"/>
+      <c r="E612" s="2" t="inlineStr"/>
+      <c r="F612" s="2" t="inlineStr"/>
+      <c r="G612" s="2" t="inlineStr"/>
+      <c r="H612" s="2" t="inlineStr"/>
+      <c r="I612" s="2" t="inlineStr"/>
+      <c r="J612" s="2" t="inlineStr"/>
+    </row>
+    <row r="613">
+      <c r="A613" s="2" t="inlineStr">
+        <is>
+          <t>118D</t>
+        </is>
+      </c>
+      <c r="B613" s="2" t="inlineStr"/>
+      <c r="C613" s="2" t="inlineStr"/>
+      <c r="D613" s="2" t="inlineStr"/>
+      <c r="E613" s="2" t="inlineStr"/>
+      <c r="F613" s="2" t="inlineStr"/>
+      <c r="G613" s="2" t="inlineStr"/>
+      <c r="H613" s="2" t="inlineStr"/>
+      <c r="I613" s="2" t="inlineStr"/>
+      <c r="J613" s="2" t="inlineStr"/>
+    </row>
+    <row r="614">
+      <c r="A614" s="2" t="inlineStr">
+        <is>
+          <t>119A</t>
+        </is>
+      </c>
+      <c r="B614" s="2" t="inlineStr"/>
+      <c r="C614" s="2" t="inlineStr"/>
+      <c r="D614" s="2" t="inlineStr"/>
+      <c r="E614" s="2" t="inlineStr"/>
+      <c r="F614" s="2" t="inlineStr"/>
+      <c r="G614" s="2" t="inlineStr"/>
+      <c r="H614" s="2" t="inlineStr"/>
+      <c r="I614" s="2" t="inlineStr"/>
+      <c r="J614" s="2" t="inlineStr"/>
+    </row>
+    <row r="615">
+      <c r="A615" s="2" t="inlineStr">
+        <is>
+          <t>119B</t>
+        </is>
+      </c>
+      <c r="B615" s="2" t="inlineStr"/>
+      <c r="C615" s="2" t="inlineStr"/>
+      <c r="D615" s="2" t="inlineStr"/>
+      <c r="E615" s="2" t="inlineStr"/>
+      <c r="F615" s="2" t="inlineStr"/>
+      <c r="G615" s="2" t="inlineStr"/>
+      <c r="H615" s="2" t="inlineStr"/>
+      <c r="I615" s="2" t="inlineStr"/>
+      <c r="J615" s="2" t="inlineStr"/>
+    </row>
+    <row r="616">
+      <c r="A616" s="2" t="inlineStr">
+        <is>
+          <t>119C</t>
+        </is>
+      </c>
+      <c r="B616" s="2" t="inlineStr"/>
+      <c r="C616" s="2" t="inlineStr"/>
+      <c r="D616" s="2" t="inlineStr"/>
+      <c r="E616" s="2" t="inlineStr"/>
+      <c r="F616" s="2" t="inlineStr"/>
+      <c r="G616" s="2" t="inlineStr"/>
+      <c r="H616" s="2" t="inlineStr"/>
+      <c r="I616" s="2" t="inlineStr"/>
+      <c r="J616" s="2" t="inlineStr"/>
+    </row>
+    <row r="617">
+      <c r="A617" s="2" t="inlineStr">
+        <is>
+          <t>119D</t>
+        </is>
+      </c>
+      <c r="B617" s="2" t="inlineStr"/>
+      <c r="C617" s="2" t="inlineStr"/>
+      <c r="D617" s="2" t="inlineStr"/>
+      <c r="E617" s="2" t="inlineStr"/>
+      <c r="F617" s="2" t="inlineStr"/>
+      <c r="G617" s="2" t="inlineStr"/>
+      <c r="H617" s="2" t="inlineStr"/>
+      <c r="I617" s="2" t="inlineStr"/>
+      <c r="J617" s="2" t="inlineStr"/>
+    </row>
+    <row r="618">
+      <c r="A618" s="2" t="inlineStr">
+        <is>
+          <t>120A</t>
+        </is>
+      </c>
+      <c r="B618" s="2" t="inlineStr"/>
+      <c r="C618" s="2" t="inlineStr"/>
+      <c r="D618" s="2" t="inlineStr"/>
+      <c r="E618" s="2" t="inlineStr"/>
+      <c r="F618" s="2" t="inlineStr"/>
+      <c r="G618" s="2" t="inlineStr"/>
+      <c r="H618" s="2" t="inlineStr"/>
+      <c r="I618" s="2" t="inlineStr"/>
+      <c r="J618" s="2" t="inlineStr"/>
+    </row>
+    <row r="619">
+      <c r="A619" s="2" t="inlineStr">
+        <is>
+          <t>120B</t>
+        </is>
+      </c>
+      <c r="B619" s="2" t="inlineStr"/>
+      <c r="C619" s="2" t="inlineStr"/>
+      <c r="D619" s="2" t="inlineStr"/>
+      <c r="E619" s="2" t="inlineStr"/>
+      <c r="F619" s="2" t="inlineStr"/>
+      <c r="G619" s="2" t="inlineStr"/>
+      <c r="H619" s="2" t="inlineStr"/>
+      <c r="I619" s="2" t="inlineStr"/>
+      <c r="J619" s="2" t="inlineStr"/>
+    </row>
+    <row r="620">
+      <c r="A620" s="2" t="inlineStr">
+        <is>
+          <t>120C</t>
+        </is>
+      </c>
+      <c r="B620" s="2" t="inlineStr"/>
+      <c r="C620" s="2" t="inlineStr"/>
+      <c r="D620" s="2" t="inlineStr"/>
+      <c r="E620" s="2" t="inlineStr"/>
+      <c r="F620" s="2" t="inlineStr"/>
+      <c r="G620" s="2" t="inlineStr"/>
+      <c r="H620" s="2" t="inlineStr"/>
+      <c r="I620" s="2" t="inlineStr"/>
+      <c r="J620" s="2" t="inlineStr"/>
+    </row>
+    <row r="621">
+      <c r="A621" s="2" t="inlineStr">
+        <is>
+          <t>120D</t>
+        </is>
+      </c>
+      <c r="B621" s="2" t="inlineStr"/>
+      <c r="C621" s="2" t="inlineStr"/>
+      <c r="D621" s="2" t="inlineStr"/>
+      <c r="E621" s="2" t="inlineStr"/>
+      <c r="F621" s="2" t="inlineStr"/>
+      <c r="G621" s="2" t="inlineStr"/>
+      <c r="H621" s="2" t="inlineStr"/>
+      <c r="I621" s="2" t="inlineStr"/>
+      <c r="J621" s="2" t="inlineStr"/>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="inlineStr">
+        <is>
+          <t>121A</t>
+        </is>
+      </c>
+      <c r="B622" s="2" t="inlineStr"/>
+      <c r="C622" s="2" t="inlineStr"/>
+      <c r="D622" s="2" t="inlineStr"/>
+      <c r="E622" s="2" t="inlineStr"/>
+      <c r="F622" s="2" t="inlineStr"/>
+      <c r="G622" s="2" t="inlineStr"/>
+      <c r="H622" s="2" t="inlineStr"/>
+      <c r="I622" s="2" t="inlineStr"/>
+      <c r="J622" s="2" t="inlineStr"/>
+    </row>
+    <row r="623">
+      <c r="A623" s="2" t="inlineStr">
+        <is>
+          <t>121B</t>
+        </is>
+      </c>
+      <c r="B623" s="2" t="inlineStr"/>
+      <c r="C623" s="2" t="inlineStr"/>
+      <c r="D623" s="2" t="inlineStr"/>
+      <c r="E623" s="2" t="inlineStr"/>
+      <c r="F623" s="2" t="inlineStr"/>
+      <c r="G623" s="2" t="inlineStr"/>
+      <c r="H623" s="2" t="inlineStr"/>
+      <c r="I623" s="2" t="inlineStr"/>
+      <c r="J623" s="2" t="inlineStr"/>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="inlineStr">
+        <is>
+          <t>121C</t>
+        </is>
+      </c>
+      <c r="B624" s="2" t="inlineStr"/>
+      <c r="C624" s="2" t="inlineStr"/>
+      <c r="D624" s="2" t="inlineStr"/>
+      <c r="E624" s="2" t="inlineStr"/>
+      <c r="F624" s="2" t="inlineStr"/>
+      <c r="G624" s="2" t="inlineStr"/>
+      <c r="H624" s="2" t="inlineStr"/>
+      <c r="I624" s="2" t="inlineStr"/>
+      <c r="J624" s="2" t="inlineStr"/>
+    </row>
+    <row r="625">
+      <c r="A625" s="2" t="inlineStr">
+        <is>
+          <t>121D</t>
+        </is>
+      </c>
+      <c r="B625" s="2" t="inlineStr"/>
+      <c r="C625" s="2" t="inlineStr"/>
+      <c r="D625" s="2" t="inlineStr"/>
+      <c r="E625" s="2" t="inlineStr"/>
+      <c r="F625" s="2" t="inlineStr"/>
+      <c r="G625" s="2" t="inlineStr"/>
+      <c r="H625" s="2" t="inlineStr"/>
+      <c r="I625" s="2" t="inlineStr"/>
+      <c r="J625" s="2" t="inlineStr"/>
+    </row>
+    <row r="626">
+      <c r="A626" s="2" t="inlineStr">
+        <is>
+          <t>122A</t>
+        </is>
+      </c>
+      <c r="B626" s="2" t="inlineStr"/>
+      <c r="C626" s="2" t="inlineStr"/>
+      <c r="D626" s="2" t="inlineStr"/>
+      <c r="E626" s="2" t="inlineStr"/>
+      <c r="F626" s="2" t="inlineStr"/>
+      <c r="G626" s="2" t="inlineStr"/>
+      <c r="H626" s="2" t="inlineStr"/>
+      <c r="I626" s="2" t="inlineStr"/>
+      <c r="J626" s="2" t="inlineStr"/>
+    </row>
+    <row r="627">
+      <c r="A627" s="2" t="inlineStr">
+        <is>
+          <t>122B</t>
+        </is>
+      </c>
+      <c r="B627" s="2" t="inlineStr"/>
+      <c r="C627" s="2" t="inlineStr"/>
+      <c r="D627" s="2" t="inlineStr"/>
+      <c r="E627" s="2" t="inlineStr"/>
+      <c r="F627" s="2" t="inlineStr"/>
+      <c r="G627" s="2" t="inlineStr"/>
+      <c r="H627" s="2" t="inlineStr"/>
+      <c r="I627" s="2" t="inlineStr"/>
+      <c r="J627" s="2" t="inlineStr"/>
+    </row>
+    <row r="628">
+      <c r="A628" s="2" t="inlineStr">
+        <is>
+          <t>122C</t>
+        </is>
+      </c>
+      <c r="B628" s="2" t="inlineStr"/>
+      <c r="C628" s="2" t="inlineStr"/>
+      <c r="D628" s="2" t="inlineStr"/>
+      <c r="E628" s="2" t="inlineStr"/>
+      <c r="F628" s="2" t="inlineStr"/>
+      <c r="G628" s="2" t="inlineStr"/>
+      <c r="H628" s="2" t="inlineStr"/>
+      <c r="I628" s="2" t="inlineStr"/>
+      <c r="J628" s="2" t="inlineStr"/>
+    </row>
+    <row r="629">
+      <c r="A629" s="2" t="inlineStr">
+        <is>
+          <t>122D</t>
+        </is>
+      </c>
+      <c r="B629" s="2" t="inlineStr"/>
+      <c r="C629" s="2" t="inlineStr"/>
+      <c r="D629" s="2" t="inlineStr"/>
+      <c r="E629" s="2" t="inlineStr"/>
+      <c r="F629" s="2" t="inlineStr"/>
+      <c r="G629" s="2" t="inlineStr"/>
+      <c r="H629" s="2" t="inlineStr"/>
+      <c r="I629" s="2" t="inlineStr"/>
+      <c r="J629" s="2" t="inlineStr"/>
+    </row>
+    <row r="630">
+      <c r="A630" s="2" t="n"/>
+      <c r="B630" s="2" t="n"/>
+      <c r="C630" s="2" t="n"/>
+      <c r="D630" s="2" t="n"/>
+      <c r="E630" s="2" t="n"/>
+      <c r="F630" s="2" t="n"/>
+      <c r="G630" s="2" t="n"/>
+      <c r="H630" s="2" t="n"/>
+      <c r="I630" s="2" t="n"/>
+      <c r="J630" s="2" t="n"/>
+    </row>
+    <row r="631">
+      <c r="A631" s="2" t="n"/>
+      <c r="B631" s="2" t="n"/>
+      <c r="C631" s="2" t="n"/>
+      <c r="D631" s="2" t="n"/>
+      <c r="E631" s="2" t="n"/>
+      <c r="F631" s="2" t="n"/>
+      <c r="G631" s="2" t="n"/>
+      <c r="H631" s="2" t="n"/>
+      <c r="I631" s="2" t="n"/>
+      <c r="J631" s="2" t="n"/>
+    </row>
+    <row r="632">
+      <c r="A632" s="2" t="n"/>
+      <c r="B632" s="2" t="n"/>
+      <c r="C632" s="2" t="n"/>
+      <c r="D632" s="2" t="n"/>
+      <c r="E632" s="2" t="n"/>
+      <c r="F632" s="2" t="n"/>
+      <c r="G632" s="2" t="n"/>
+      <c r="H632" s="2" t="n"/>
+      <c r="I632" s="2" t="n"/>
+      <c r="J632" s="2" t="n"/>
+    </row>
+    <row r="633">
+      <c r="A633" s="2" t="n"/>
+      <c r="B633" s="2" t="n"/>
+      <c r="C633" s="2" t="n"/>
+      <c r="D633" s="2" t="n"/>
+      <c r="E633" s="2" t="n"/>
+      <c r="F633" s="2" t="n"/>
+      <c r="G633" s="2" t="n"/>
+      <c r="H633" s="2" t="n"/>
+      <c r="I633" s="2" t="n"/>
+      <c r="J633" s="2" t="n"/>
+    </row>
+    <row r="634">
+      <c r="A634" s="2" t="n"/>
+      <c r="B634" s="2" t="n"/>
+      <c r="C634" s="2" t="n"/>
+      <c r="D634" s="2" t="n"/>
+      <c r="E634" s="2" t="n"/>
+      <c r="F634" s="2" t="n"/>
+      <c r="G634" s="2" t="n"/>
+      <c r="H634" s="2" t="n"/>
+      <c r="I634" s="2" t="n"/>
+      <c r="J634" s="2" t="n"/>
+    </row>
+    <row r="635">
+      <c r="A635" s="2" t="n"/>
+      <c r="B635" s="2" t="n"/>
+      <c r="C635" s="2" t="n"/>
+      <c r="D635" s="2" t="n"/>
+      <c r="E635" s="2" t="n"/>
+      <c r="F635" s="2" t="n"/>
+      <c r="G635" s="2" t="n"/>
+      <c r="H635" s="2" t="n"/>
+      <c r="I635" s="2" t="n"/>
+      <c r="J635" s="2" t="n"/>
+    </row>
+    <row r="636">
+      <c r="A636" s="2" t="n"/>
+      <c r="B636" s="2" t="n"/>
+      <c r="C636" s="2" t="n"/>
+      <c r="D636" s="2" t="n"/>
+      <c r="E636" s="2" t="n"/>
+      <c r="F636" s="2" t="n"/>
+      <c r="G636" s="2" t="n"/>
+      <c r="H636" s="2" t="n"/>
+      <c r="I636" s="2" t="n"/>
+      <c r="J636" s="2" t="n"/>
+    </row>
+    <row r="637">
+      <c r="A637" s="2" t="n"/>
+      <c r="B637" s="2" t="n"/>
+      <c r="C637" s="2" t="n"/>
+      <c r="D637" s="2" t="n"/>
+      <c r="E637" s="2" t="n"/>
+      <c r="F637" s="2" t="n"/>
+      <c r="G637" s="2" t="n"/>
+      <c r="H637" s="2" t="n"/>
+      <c r="I637" s="2" t="n"/>
+      <c r="J637" s="2" t="n"/>
+    </row>
+    <row r="638">
+      <c r="A638" s="2" t="n"/>
+      <c r="B638" s="2" t="n"/>
+      <c r="C638" s="2" t="n"/>
+      <c r="D638" s="2" t="n"/>
+      <c r="E638" s="2" t="n"/>
+      <c r="F638" s="2" t="n"/>
+      <c r="G638" s="2" t="n"/>
+      <c r="H638" s="2" t="n"/>
+      <c r="I638" s="2" t="n"/>
+      <c r="J638" s="2" t="n"/>
+    </row>
+    <row r="639">
+      <c r="A639" s="2" t="n"/>
+      <c r="B639" s="2" t="n"/>
+      <c r="C639" s="2" t="n"/>
+      <c r="D639" s="2" t="n"/>
+      <c r="E639" s="2" t="n"/>
+      <c r="F639" s="2" t="n"/>
+      <c r="G639" s="2" t="n"/>
+      <c r="H639" s="2" t="n"/>
+      <c r="I639" s="2" t="n"/>
+      <c r="J639" s="2" t="n"/>
+    </row>
+    <row r="640">
+      <c r="A640" s="2" t="n"/>
+      <c r="B640" s="2" t="n"/>
+      <c r="C640" s="2" t="n"/>
+      <c r="D640" s="2" t="n"/>
+      <c r="E640" s="2" t="n"/>
+      <c r="F640" s="2" t="n"/>
+      <c r="G640" s="2" t="n"/>
+      <c r="H640" s="2" t="n"/>
+      <c r="I640" s="2" t="n"/>
+      <c r="J640" s="2" t="n"/>
+    </row>
+    <row r="641">
+      <c r="A641" s="2" t="n"/>
+      <c r="B641" s="2" t="n"/>
+      <c r="C641" s="2" t="n"/>
+      <c r="D641" s="2" t="n"/>
+      <c r="E641" s="2" t="n"/>
+      <c r="F641" s="2" t="n"/>
+      <c r="G641" s="2" t="n"/>
+      <c r="H641" s="2" t="n"/>
+      <c r="I641" s="2" t="n"/>
+      <c r="J641" s="2" t="n"/>
+    </row>
+    <row r="642">
+      <c r="A642" s="2" t="n"/>
+      <c r="B642" s="2" t="n"/>
+      <c r="C642" s="2" t="n"/>
+      <c r="D642" s="2" t="n"/>
+      <c r="E642" s="2" t="n"/>
+      <c r="F642" s="2" t="n"/>
+      <c r="G642" s="2" t="n"/>
+      <c r="H642" s="2" t="n"/>
+      <c r="I642" s="2" t="n"/>
+      <c r="J642" s="2" t="n"/>
+    </row>
+    <row r="643">
+      <c r="A643" s="2" t="n"/>
+      <c r="B643" s="2" t="n"/>
+      <c r="C643" s="2" t="n"/>
+      <c r="D643" s="2" t="n"/>
+      <c r="E643" s="2" t="n"/>
+      <c r="F643" s="2" t="n"/>
+      <c r="G643" s="2" t="n"/>
+      <c r="H643" s="2" t="n"/>
+      <c r="I643" s="2" t="n"/>
+      <c r="J643" s="2" t="n"/>
+    </row>
+    <row r="644">
+      <c r="A644" s="2" t="n"/>
+      <c r="B644" s="2" t="n"/>
+      <c r="C644" s="2" t="n"/>
+      <c r="D644" s="2" t="n"/>
+      <c r="E644" s="2" t="n"/>
+      <c r="F644" s="2" t="n"/>
+      <c r="G644" s="2" t="n"/>
+      <c r="H644" s="2" t="n"/>
+      <c r="I644" s="2" t="n"/>
+      <c r="J644" s="2" t="n"/>
+    </row>
+    <row r="645">
+      <c r="A645" s="2" t="n"/>
+      <c r="B645" s="2" t="n"/>
+      <c r="C645" s="2" t="n"/>
+      <c r="D645" s="2" t="n"/>
+      <c r="E645" s="2" t="n"/>
+      <c r="F645" s="2" t="n"/>
+      <c r="G645" s="2" t="n"/>
+      <c r="H645" s="2" t="n"/>
+      <c r="I645" s="2" t="n"/>
+      <c r="J645" s="2" t="n"/>
+    </row>
+    <row r="646">
+      <c r="A646" s="2" t="n"/>
+      <c r="B646" s="2" t="n"/>
+      <c r="C646" s="2" t="n"/>
+      <c r="D646" s="2" t="n"/>
+      <c r="E646" s="2" t="n"/>
+      <c r="F646" s="2" t="n"/>
+      <c r="G646" s="2" t="n"/>
+      <c r="H646" s="2" t="n"/>
+      <c r="I646" s="2" t="n"/>
+      <c r="J646" s="2" t="n"/>
+    </row>
+    <row r="647">
+      <c r="A647" s="2" t="n"/>
+      <c r="B647" s="2" t="n"/>
+      <c r="C647" s="2" t="n"/>
+      <c r="D647" s="2" t="n"/>
+      <c r="E647" s="2" t="n"/>
+      <c r="F647" s="2" t="n"/>
+      <c r="G647" s="2" t="n"/>
+      <c r="H647" s="2" t="n"/>
+      <c r="I647" s="2" t="n"/>
+      <c r="J647" s="2" t="n"/>
+    </row>
+    <row r="648">
+      <c r="A648" s="2" t="n"/>
+      <c r="B648" s="2" t="n"/>
+      <c r="C648" s="2" t="n"/>
+      <c r="D648" s="2" t="n"/>
+      <c r="E648" s="2" t="n"/>
+      <c r="F648" s="2" t="n"/>
+      <c r="G648" s="2" t="n"/>
+      <c r="H648" s="2" t="n"/>
+      <c r="I648" s="2" t="n"/>
+      <c r="J648" s="2" t="n"/>
+    </row>
+    <row r="649">
+      <c r="A649" s="2" t="n"/>
+      <c r="B649" s="2" t="n"/>
+      <c r="C649" s="2" t="n"/>
+      <c r="D649" s="2" t="n"/>
+      <c r="E649" s="2" t="n"/>
+      <c r="F649" s="2" t="n"/>
+      <c r="G649" s="2" t="n"/>
+      <c r="H649" s="2" t="n"/>
+      <c r="I649" s="2" t="n"/>
+      <c r="J649" s="2" t="n"/>
+    </row>
+    <row r="650">
+      <c r="A650" s="2" t="n"/>
+      <c r="B650" s="2" t="n"/>
+      <c r="C650" s="2" t="n"/>
+      <c r="D650" s="2" t="n"/>
+      <c r="E650" s="2" t="n"/>
+      <c r="F650" s="2" t="n"/>
+      <c r="G650" s="2" t="n"/>
+      <c r="H650" s="2" t="n"/>
+      <c r="I650" s="2" t="n"/>
+      <c r="J650" s="2" t="n"/>
+    </row>
+    <row r="651">
+      <c r="A651" s="2" t="n"/>
+      <c r="B651" s="2" t="n"/>
+      <c r="C651" s="2" t="n"/>
+      <c r="D651" s="2" t="n"/>
+      <c r="E651" s="2" t="n"/>
+      <c r="F651" s="2" t="n"/>
+      <c r="G651" s="2" t="n"/>
+      <c r="H651" s="2" t="n"/>
+      <c r="I651" s="2" t="n"/>
+      <c r="J651" s="2" t="n"/>
+    </row>
+    <row r="652">
+      <c r="A652" s="2" t="n"/>
+      <c r="B652" s="2" t="n"/>
+      <c r="C652" s="2" t="n"/>
+      <c r="D652" s="2" t="n"/>
+      <c r="E652" s="2" t="n"/>
+      <c r="F652" s="2" t="n"/>
+      <c r="G652" s="2" t="n"/>
+      <c r="H652" s="2" t="n"/>
+      <c r="I652" s="2" t="n"/>
+      <c r="J652" s="2" t="n"/>
+    </row>
+    <row r="653">
+      <c r="A653" s="2" t="n"/>
+      <c r="B653" s="2" t="n"/>
+      <c r="C653" s="2" t="n"/>
+      <c r="D653" s="2" t="n"/>
+      <c r="E653" s="2" t="n"/>
+      <c r="F653" s="2" t="n"/>
+      <c r="G653" s="2" t="n"/>
+      <c r="H653" s="2" t="n"/>
+      <c r="I653" s="2" t="n"/>
+      <c r="J653" s="2" t="n"/>
+    </row>
+    <row r="654">
+      <c r="A654" s="2" t="n"/>
+      <c r="B654" s="2" t="n"/>
+      <c r="C654" s="2" t="n"/>
+      <c r="D654" s="2" t="n"/>
+      <c r="E654" s="2" t="n"/>
+      <c r="F654" s="2" t="n"/>
+      <c r="G654" s="2" t="n"/>
+      <c r="H654" s="2" t="n"/>
+      <c r="I654" s="2" t="n"/>
+      <c r="J654" s="2" t="n"/>
+    </row>
+    <row r="655">
+      <c r="A655" s="2" t="n"/>
+      <c r="B655" s="2" t="n"/>
+      <c r="C655" s="2" t="n"/>
+      <c r="D655" s="2" t="n"/>
+      <c r="E655" s="2" t="n"/>
+      <c r="F655" s="2" t="n"/>
+      <c r="G655" s="2" t="n"/>
+      <c r="H655" s="2" t="n"/>
+      <c r="I655" s="2" t="n"/>
+      <c r="J655" s="2" t="n"/>
+    </row>
+    <row r="656">
+      <c r="A656" s="2" t="n"/>
+      <c r="B656" s="2" t="n"/>
+      <c r="C656" s="2" t="n"/>
+      <c r="D656" s="2" t="n"/>
+      <c r="E656" s="2" t="n"/>
+      <c r="F656" s="2" t="n"/>
+      <c r="G656" s="2" t="n"/>
+      <c r="H656" s="2" t="n"/>
+      <c r="I656" s="2" t="n"/>
+      <c r="J656" s="2" t="n"/>
+    </row>
+    <row r="657">
+      <c r="A657" s="2" t="n"/>
+      <c r="B657" s="2" t="n"/>
+      <c r="C657" s="2" t="n"/>
+      <c r="D657" s="2" t="n"/>
+      <c r="E657" s="2" t="n"/>
+      <c r="F657" s="2" t="n"/>
+      <c r="G657" s="2" t="n"/>
+      <c r="H657" s="2" t="n"/>
+      <c r="I657" s="2" t="n"/>
+      <c r="J657" s="2" t="n"/>
+    </row>
+    <row r="658">
+      <c r="A658" s="2" t="n"/>
+      <c r="B658" s="2" t="n"/>
+      <c r="C658" s="2" t="n"/>
+      <c r="D658" s="2" t="n"/>
+      <c r="E658" s="2" t="n"/>
+      <c r="F658" s="2" t="n"/>
+      <c r="G658" s="2" t="n"/>
+      <c r="H658" s="2" t="n"/>
+      <c r="I658" s="2" t="n"/>
+      <c r="J658" s="2" t="n"/>
+    </row>
+    <row r="659">
+      <c r="A659" s="2" t="n"/>
+      <c r="B659" s="2" t="n"/>
+      <c r="C659" s="2" t="n"/>
+      <c r="D659" s="2" t="n"/>
+      <c r="E659" s="2" t="n"/>
+      <c r="F659" s="2" t="n"/>
+      <c r="G659" s="2" t="n"/>
+      <c r="H659" s="2" t="n"/>
+      <c r="I659" s="2" t="n"/>
+      <c r="J659" s="2" t="n"/>
+    </row>
+    <row r="660">
+      <c r="A660" s="2" t="n"/>
+      <c r="B660" s="2" t="n"/>
+      <c r="C660" s="2" t="n"/>
+      <c r="D660" s="2" t="n"/>
+      <c r="E660" s="2" t="n"/>
+      <c r="F660" s="2" t="n"/>
+      <c r="G660" s="2" t="n"/>
+      <c r="H660" s="2" t="n"/>
+      <c r="I660" s="2" t="n"/>
+      <c r="J660" s="2" t="n"/>
+    </row>
+    <row r="661">
+      <c r="A661" s="2" t="n"/>
+      <c r="B661" s="2" t="n"/>
+      <c r="C661" s="2" t="n"/>
+      <c r="D661" s="2" t="n"/>
+      <c r="E661" s="2" t="n"/>
+      <c r="F661" s="2" t="n"/>
+      <c r="G661" s="2" t="n"/>
+      <c r="H661" s="2" t="n"/>
+      <c r="I661" s="2" t="n"/>
+      <c r="J661" s="2" t="n"/>
+    </row>
+    <row r="662">
+      <c r="A662" s="2" t="n"/>
+      <c r="B662" s="2" t="n"/>
+      <c r="C662" s="2" t="n"/>
+      <c r="D662" s="2" t="n"/>
+      <c r="E662" s="2" t="n"/>
+      <c r="F662" s="2" t="n"/>
+      <c r="G662" s="2" t="n"/>
+      <c r="H662" s="2" t="n"/>
+      <c r="I662" s="2" t="n"/>
+      <c r="J662" s="2" t="n"/>
+    </row>
+    <row r="663">
+      <c r="A663" s="2" t="n"/>
+      <c r="B663" s="2" t="n"/>
+      <c r="C663" s="2" t="n"/>
+      <c r="D663" s="2" t="n"/>
+      <c r="E663" s="2" t="n"/>
+      <c r="F663" s="2" t="n"/>
+      <c r="G663" s="2" t="n"/>
+      <c r="H663" s="2" t="n"/>
+      <c r="I663" s="2" t="n"/>
+      <c r="J663" s="2" t="n"/>
+    </row>
+    <row r="664">
+      <c r="A664" s="2" t="n"/>
+      <c r="B664" s="2" t="n"/>
+      <c r="C664" s="2" t="n"/>
+      <c r="D664" s="2" t="n"/>
+      <c r="E664" s="2" t="n"/>
+      <c r="F664" s="2" t="n"/>
+      <c r="G664" s="2" t="n"/>
+      <c r="H664" s="2" t="n"/>
+      <c r="I664" s="2" t="n"/>
+      <c r="J664" s="2" t="n"/>
+    </row>
+    <row r="665">
+      <c r="A665" s="2" t="n"/>
+      <c r="B665" s="2" t="n"/>
+      <c r="C665" s="2" t="n"/>
+      <c r="D665" s="2" t="n"/>
+      <c r="E665" s="2" t="n"/>
+      <c r="F665" s="2" t="n"/>
+      <c r="G665" s="2" t="n"/>
+      <c r="H665" s="2" t="n"/>
+      <c r="I665" s="2" t="n"/>
+      <c r="J665" s="2" t="n"/>
+    </row>
+    <row r="666">
+      <c r="A666" s="2" t="n"/>
+      <c r="B666" s="2" t="n"/>
+      <c r="C666" s="2" t="n"/>
+      <c r="D666" s="2" t="n"/>
+      <c r="E666" s="2" t="n"/>
+      <c r="F666" s="2" t="n"/>
+      <c r="G666" s="2" t="n"/>
+      <c r="H666" s="2" t="n"/>
+      <c r="I666" s="2" t="n"/>
+      <c r="J666" s="2" t="n"/>
+    </row>
+    <row r="667">
+      <c r="A667" s="2" t="n"/>
+      <c r="B667" s="2" t="n"/>
+      <c r="C667" s="2" t="n"/>
+      <c r="D667" s="2" t="n"/>
+      <c r="E667" s="2" t="n"/>
+      <c r="F667" s="2" t="n"/>
+      <c r="G667" s="2" t="n"/>
+      <c r="H667" s="2" t="n"/>
+      <c r="I667" s="2" t="n"/>
+      <c r="J667" s="2" t="n"/>
+    </row>
+    <row r="668">
+      <c r="A668" s="2" t="n"/>
+      <c r="B668" s="2" t="n"/>
+      <c r="C668" s="2" t="n"/>
+      <c r="D668" s="2" t="n"/>
+      <c r="E668" s="2" t="n"/>
+      <c r="F668" s="2" t="n"/>
+      <c r="G668" s="2" t="n"/>
+      <c r="H668" s="2" t="n"/>
+      <c r="I668" s="2" t="n"/>
+      <c r="J668" s="2" t="n"/>
+    </row>
+    <row r="669">
+      <c r="A669" s="2" t="n"/>
+      <c r="B669" s="2" t="n"/>
+      <c r="C669" s="2" t="n"/>
+      <c r="D669" s="2" t="n"/>
+      <c r="E669" s="2" t="n"/>
+      <c r="F669" s="2" t="n"/>
+      <c r="G669" s="2" t="n"/>
+      <c r="H669" s="2" t="n"/>
+      <c r="I669" s="2" t="n"/>
+      <c r="J669" s="2" t="n"/>
+    </row>
+    <row r="670">
+      <c r="A670" s="2" t="n"/>
+      <c r="B670" s="2" t="n"/>
+      <c r="C670" s="2" t="n"/>
+      <c r="D670" s="2" t="n"/>
+      <c r="E670" s="2" t="n"/>
+      <c r="F670" s="2" t="n"/>
+      <c r="G670" s="2" t="n"/>
+      <c r="H670" s="2" t="n"/>
+      <c r="I670" s="2" t="n"/>
+      <c r="J670" s="2" t="n"/>
+    </row>
+    <row r="671">
+      <c r="A671" s="2" t="n"/>
+      <c r="B671" s="2" t="n"/>
+      <c r="C671" s="2" t="n"/>
+      <c r="D671" s="2" t="n"/>
+      <c r="E671" s="2" t="n"/>
+      <c r="F671" s="2" t="n"/>
+      <c r="G671" s="2" t="n"/>
+      <c r="H671" s="2" t="n"/>
+      <c r="I671" s="2" t="n"/>
+      <c r="J671" s="2" t="n"/>
+    </row>
+    <row r="672">
+      <c r="A672" s="2" t="n"/>
+      <c r="B672" s="2" t="n"/>
+      <c r="C672" s="2" t="n"/>
+      <c r="D672" s="2" t="n"/>
+      <c r="E672" s="2" t="n"/>
+      <c r="F672" s="2" t="n"/>
+      <c r="G672" s="2" t="n"/>
+      <c r="H672" s="2" t="n"/>
+      <c r="I672" s="2" t="n"/>
+      <c r="J672" s="2" t="n"/>
+    </row>
+    <row r="673">
+      <c r="A673" s="2" t="n"/>
+      <c r="B673" s="2" t="n"/>
+      <c r="C673" s="2" t="n"/>
+      <c r="D673" s="2" t="n"/>
+      <c r="E673" s="2" t="n"/>
+      <c r="F673" s="2" t="n"/>
+      <c r="G673" s="2" t="n"/>
+      <c r="H673" s="2" t="n"/>
+      <c r="I673" s="2" t="n"/>
+      <c r="J673" s="2" t="n"/>
+    </row>
+    <row r="674">
+      <c r="A674" s="2" t="n"/>
+      <c r="B674" s="2" t="n"/>
+      <c r="C674" s="2" t="n"/>
+      <c r="D674" s="2" t="n"/>
+      <c r="E674" s="2" t="n"/>
+      <c r="F674" s="2" t="n"/>
+      <c r="G674" s="2" t="n"/>
+      <c r="H674" s="2" t="n"/>
+      <c r="I674" s="2" t="n"/>
+      <c r="J674" s="2" t="n"/>
+    </row>
+    <row r="675">
+      <c r="A675" s="2" t="n"/>
+      <c r="B675" s="2" t="n"/>
+      <c r="C675" s="2" t="n"/>
+      <c r="D675" s="2" t="n"/>
+      <c r="E675" s="2" t="n"/>
+      <c r="F675" s="2" t="n"/>
+      <c r="G675" s="2" t="n"/>
+      <c r="H675" s="2" t="n"/>
+      <c r="I675" s="2" t="n"/>
+      <c r="J675" s="2" t="n"/>
+    </row>
+    <row r="676">
+      <c r="A676" s="2" t="n"/>
+      <c r="B676" s="2" t="n"/>
+      <c r="C676" s="2" t="n"/>
+      <c r="D676" s="2" t="n"/>
+      <c r="E676" s="2" t="n"/>
+      <c r="F676" s="2" t="n"/>
+      <c r="G676" s="2" t="n"/>
+      <c r="H676" s="2" t="n"/>
+      <c r="I676" s="2" t="n"/>
+      <c r="J676" s="2" t="n"/>
+    </row>
+    <row r="677">
+      <c r="A677" s="2" t="n"/>
+      <c r="B677" s="2" t="n"/>
+      <c r="C677" s="2" t="n"/>
+      <c r="D677" s="2" t="n"/>
+      <c r="E677" s="2" t="n"/>
+      <c r="F677" s="2" t="n"/>
+      <c r="G677" s="2" t="n"/>
+      <c r="H677" s="2" t="n"/>
+      <c r="I677" s="2" t="n"/>
+      <c r="J677" s="2" t="n"/>
+    </row>
+    <row r="678">
+      <c r="A678" s="2" t="n"/>
+      <c r="B678" s="2" t="n"/>
+      <c r="C678" s="2" t="n"/>
+      <c r="D678" s="2" t="n"/>
+      <c r="E678" s="2" t="n"/>
+      <c r="F678" s="2" t="n"/>
+      <c r="G678" s="2" t="n"/>
+      <c r="H678" s="2" t="n"/>
+      <c r="I678" s="2" t="n"/>
+      <c r="J678" s="2" t="n"/>
+    </row>
+    <row r="679">
+      <c r="A679" s="2" t="n"/>
+      <c r="B679" s="2" t="n"/>
+      <c r="C679" s="2" t="n"/>
+      <c r="D679" s="2" t="n"/>
+      <c r="E679" s="2" t="n"/>
+      <c r="F679" s="2" t="n"/>
+      <c r="G679" s="2" t="n"/>
+      <c r="H679" s="2" t="n"/>
+      <c r="I679" s="2" t="n"/>
+      <c r="J679" s="2" t="n"/>
+    </row>
+    <row r="680">
+      <c r="A680" s="2" t="n"/>
+      <c r="B680" s="2" t="n"/>
+      <c r="C680" s="2" t="n"/>
+      <c r="D680" s="2" t="n"/>
+      <c r="E680" s="2" t="n"/>
+      <c r="F680" s="2" t="n"/>
+      <c r="G680" s="2" t="n"/>
+      <c r="H680" s="2" t="n"/>
+      <c r="I680" s="2" t="n"/>
+      <c r="J680" s="2" t="n"/>
+    </row>
+    <row r="681">
+      <c r="A681" s="2" t="n"/>
+      <c r="B681" s="2" t="n"/>
+      <c r="C681" s="2" t="n"/>
+      <c r="D681" s="2" t="n"/>
+      <c r="E681" s="2" t="n"/>
+      <c r="F681" s="2" t="n"/>
+      <c r="G681" s="2" t="n"/>
+      <c r="H681" s="2" t="n"/>
+      <c r="I681" s="2" t="n"/>
+      <c r="J681" s="2" t="n"/>
+    </row>
+    <row r="682">
+      <c r="A682" s="2" t="n"/>
+      <c r="B682" s="2" t="n"/>
+      <c r="C682" s="2" t="n"/>
+      <c r="D682" s="2" t="n"/>
+      <c r="E682" s="2" t="n"/>
+      <c r="F682" s="2" t="n"/>
+      <c r="G682" s="2" t="n"/>
+      <c r="H682" s="2" t="n"/>
+      <c r="I682" s="2" t="n"/>
+      <c r="J682" s="2" t="n"/>
+    </row>
+    <row r="683">
+      <c r="A683" s="2" t="n"/>
+      <c r="B683" s="2" t="n"/>
+      <c r="C683" s="2" t="n"/>
+      <c r="D683" s="2" t="n"/>
+      <c r="E683" s="2" t="n"/>
+      <c r="F683" s="2" t="n"/>
+      <c r="G683" s="2" t="n"/>
+      <c r="H683" s="2" t="n"/>
+      <c r="I683" s="2" t="n"/>
+      <c r="J683" s="2" t="n"/>
+    </row>
+    <row r="684">
+      <c r="A684" s="2" t="n"/>
+      <c r="B684" s="2" t="n"/>
+      <c r="C684" s="2" t="n"/>
+      <c r="D684" s="2" t="n"/>
+      <c r="E684" s="2" t="n"/>
+      <c r="F684" s="2" t="n"/>
+      <c r="G684" s="2" t="n"/>
+      <c r="H684" s="2" t="n"/>
+      <c r="I684" s="2" t="n"/>
+      <c r="J684" s="2" t="n"/>
+    </row>
+    <row r="685">
+      <c r="A685" s="2" t="n"/>
+      <c r="B685" s="2" t="n"/>
+      <c r="C685" s="2" t="n"/>
+      <c r="D685" s="2" t="n"/>
+      <c r="E685" s="2" t="n"/>
+      <c r="F685" s="2" t="n"/>
+      <c r="G685" s="2" t="n"/>
+      <c r="H685" s="2" t="n"/>
+      <c r="I685" s="2" t="n"/>
+      <c r="J685" s="2" t="n"/>
+    </row>
+    <row r="686">
+      <c r="A686" s="2" t="n"/>
+      <c r="B686" s="2" t="n"/>
+      <c r="C686" s="2" t="n"/>
+      <c r="D686" s="2" t="n"/>
+      <c r="E686" s="2" t="n"/>
+      <c r="F686" s="2" t="n"/>
+      <c r="G686" s="2" t="n"/>
+      <c r="H686" s="2" t="n"/>
+      <c r="I686" s="2" t="n"/>
+      <c r="J686" s="2" t="n"/>
+    </row>
+    <row r="687">
+      <c r="A687" s="2" t="n"/>
+      <c r="B687" s="2" t="n"/>
+      <c r="C687" s="2" t="n"/>
+      <c r="D687" s="2" t="n"/>
+      <c r="E687" s="2" t="n"/>
+      <c r="F687" s="2" t="n"/>
+      <c r="G687" s="2" t="n"/>
+      <c r="H687" s="2" t="n"/>
+      <c r="I687" s="2" t="n"/>
+      <c r="J687" s="2" t="n"/>
+    </row>
+    <row r="688">
+      <c r="A688" s="2" t="n"/>
+      <c r="B688" s="2" t="n"/>
+      <c r="C688" s="2" t="n"/>
+      <c r="D688" s="2" t="n"/>
+      <c r="E688" s="2" t="n"/>
+      <c r="F688" s="2" t="n"/>
+      <c r="G688" s="2" t="n"/>
+      <c r="H688" s="2" t="n"/>
+      <c r="I688" s="2" t="n"/>
+      <c r="J688" s="2" t="n"/>
+    </row>
+    <row r="689">
+      <c r="A689" s="2" t="n"/>
+      <c r="B689" s="2" t="n"/>
+      <c r="C689" s="2" t="n"/>
+      <c r="D689" s="2" t="n"/>
+      <c r="E689" s="2" t="n"/>
+      <c r="F689" s="2" t="n"/>
+      <c r="G689" s="2" t="n"/>
+      <c r="H689" s="2" t="n"/>
+      <c r="I689" s="2" t="n"/>
+      <c r="J689" s="2" t="n"/>
+    </row>
+    <row r="690">
+      <c r="A690" s="2" t="n"/>
+      <c r="B690" s="2" t="n"/>
+      <c r="C690" s="2" t="n"/>
+      <c r="D690" s="2" t="n"/>
+      <c r="E690" s="2" t="n"/>
+      <c r="F690" s="2" t="n"/>
+      <c r="G690" s="2" t="n"/>
+      <c r="H690" s="2" t="n"/>
+      <c r="I690" s="2" t="n"/>
+      <c r="J690" s="2" t="n"/>
+    </row>
+    <row r="691">
+      <c r="A691" s="2" t="n"/>
+      <c r="B691" s="2" t="n"/>
+      <c r="C691" s="2" t="n"/>
+      <c r="D691" s="2" t="n"/>
+      <c r="E691" s="2" t="n"/>
+      <c r="F691" s="2" t="n"/>
+      <c r="G691" s="2" t="n"/>
+      <c r="H691" s="2" t="n"/>
+      <c r="I691" s="2" t="n"/>
+      <c r="J691" s="2" t="n"/>
+    </row>
+    <row r="692">
+      <c r="A692" s="2" t="n"/>
+      <c r="B692" s="2" t="n"/>
+      <c r="C692" s="2" t="n"/>
+      <c r="D692" s="2" t="n"/>
+      <c r="E692" s="2" t="n"/>
+      <c r="F692" s="2" t="n"/>
+      <c r="G692" s="2" t="n"/>
+      <c r="H692" s="2" t="n"/>
+      <c r="I692" s="2" t="n"/>
+      <c r="J692" s="2" t="n"/>
+    </row>
+    <row r="693">
+      <c r="A693" s="2" t="n"/>
+      <c r="B693" s="2" t="n"/>
+      <c r="C693" s="2" t="n"/>
+      <c r="D693" s="2" t="n"/>
+      <c r="E693" s="2" t="n"/>
+      <c r="F693" s="2" t="n"/>
+      <c r="G693" s="2" t="n"/>
+      <c r="H693" s="2" t="n"/>
+      <c r="I693" s="2" t="n"/>
+      <c r="J693" s="2" t="n"/>
+    </row>
+    <row r="694">
+      <c r="A694" s="2" t="n"/>
+      <c r="B694" s="2" t="n"/>
+      <c r="C694" s="2" t="n"/>
+      <c r="D694" s="2" t="n"/>
+      <c r="E694" s="2" t="n"/>
+      <c r="F694" s="2" t="n"/>
+      <c r="G694" s="2" t="n"/>
+      <c r="H694" s="2" t="n"/>
+      <c r="I694" s="2" t="n"/>
+      <c r="J694" s="2" t="n"/>
+    </row>
+    <row r="695">
+      <c r="A695" s="2" t="n"/>
+      <c r="B695" s="2" t="n"/>
+      <c r="C695" s="2" t="n"/>
+      <c r="D695" s="2" t="n"/>
+      <c r="E695" s="2" t="n"/>
+      <c r="F695" s="2" t="n"/>
+      <c r="G695" s="2" t="n"/>
+      <c r="H695" s="2" t="n"/>
+      <c r="I695" s="2" t="n"/>
+      <c r="J695" s="2" t="n"/>
+    </row>
+    <row r="696">
+      <c r="A696" s="2" t="n"/>
+      <c r="B696" s="2" t="n"/>
+      <c r="C696" s="2" t="n"/>
+      <c r="D696" s="2" t="n"/>
+      <c r="E696" s="2" t="n"/>
+      <c r="F696" s="2" t="n"/>
+      <c r="G696" s="2" t="n"/>
+      <c r="H696" s="2" t="n"/>
+      <c r="I696" s="2" t="n"/>
+      <c r="J696" s="2" t="n"/>
+    </row>
+    <row r="697">
+      <c r="A697" s="2" t="n"/>
+      <c r="B697" s="2" t="n"/>
+      <c r="C697" s="2" t="n"/>
+      <c r="D697" s="2" t="n"/>
+      <c r="E697" s="2" t="n"/>
+      <c r="F697" s="2" t="n"/>
+      <c r="G697" s="2" t="n"/>
+      <c r="H697" s="2" t="n"/>
+      <c r="I697" s="2" t="n"/>
+      <c r="J697" s="2" t="n"/>
+    </row>
+    <row r="698">
+      <c r="A698" s="2" t="n"/>
+      <c r="B698" s="2" t="n"/>
+      <c r="C698" s="2" t="n"/>
+      <c r="D698" s="2" t="n"/>
+      <c r="E698" s="2" t="n"/>
+      <c r="F698" s="2" t="n"/>
+      <c r="G698" s="2" t="n"/>
+      <c r="H698" s="2" t="n"/>
+      <c r="I698" s="2" t="n"/>
+      <c r="J698" s="2" t="n"/>
+    </row>
+    <row r="699">
+      <c r="A699" s="2" t="n"/>
+      <c r="B699" s="2" t="n"/>
+      <c r="C699" s="2" t="n"/>
+      <c r="D699" s="2" t="n"/>
+      <c r="E699" s="2" t="n"/>
+      <c r="F699" s="2" t="n"/>
+      <c r="G699" s="2" t="n"/>
+      <c r="H699" s="2" t="n"/>
+      <c r="I699" s="2" t="n"/>
+      <c r="J699" s="2" t="n"/>
+    </row>
+    <row r="700">
+      <c r="A700" s="2" t="n"/>
+      <c r="B700" s="2" t="n"/>
+      <c r="C700" s="2" t="n"/>
+      <c r="D700" s="2" t="n"/>
+      <c r="E700" s="2" t="n"/>
+      <c r="F700" s="2" t="n"/>
+      <c r="G700" s="2" t="n"/>
+      <c r="H700" s="2" t="n"/>
+      <c r="I700" s="2" t="n"/>
+      <c r="J700" s="2" t="n"/>
+    </row>
+    <row r="701">
+      <c r="A701" s="2" t="n"/>
+      <c r="B701" s="2" t="n"/>
+      <c r="C701" s="2" t="n"/>
+      <c r="D701" s="2" t="n"/>
+      <c r="E701" s="2" t="n"/>
+      <c r="F701" s="2" t="n"/>
+      <c r="G701" s="2" t="n"/>
+      <c r="H701" s="2" t="n"/>
+      <c r="I701" s="2" t="n"/>
+      <c r="J701" s="2" t="n"/>
+    </row>
+    <row r="702">
+      <c r="A702" s="2" t="n"/>
+      <c r="B702" s="2" t="n"/>
+      <c r="C702" s="2" t="n"/>
+      <c r="D702" s="2" t="n"/>
+      <c r="E702" s="2" t="n"/>
+      <c r="F702" s="2" t="n"/>
+      <c r="G702" s="2" t="n"/>
+      <c r="H702" s="2" t="n"/>
+      <c r="I702" s="2" t="n"/>
+      <c r="J702" s="2" t="n"/>
+    </row>
+    <row r="703">
+      <c r="A703" s="2" t="n"/>
+      <c r="B703" s="2" t="n"/>
+      <c r="C703" s="2" t="n"/>
+      <c r="D703" s="2" t="n"/>
+      <c r="E703" s="2" t="n"/>
+      <c r="F703" s="2" t="n"/>
+      <c r="G703" s="2" t="n"/>
+      <c r="H703" s="2" t="n"/>
+      <c r="I703" s="2" t="n"/>
+      <c r="J703" s="2" t="n"/>
+    </row>
+    <row r="704">
+      <c r="A704" s="2" t="n"/>
+      <c r="B704" s="2" t="n"/>
+      <c r="C704" s="2" t="n"/>
+      <c r="D704" s="2" t="n"/>
+      <c r="E704" s="2" t="n"/>
+      <c r="F704" s="2" t="n"/>
+      <c r="G704" s="2" t="n"/>
+      <c r="H704" s="2" t="n"/>
+      <c r="I704" s="2" t="n"/>
+      <c r="J704" s="2" t="n"/>
+    </row>
+    <row r="705">
+      <c r="A705" s="2" t="n"/>
+      <c r="B705" s="2" t="n"/>
+      <c r="C705" s="2" t="n"/>
+      <c r="D705" s="2" t="n"/>
+      <c r="E705" s="2" t="n"/>
+      <c r="F705" s="2" t="n"/>
+      <c r="G705" s="2" t="n"/>
+      <c r="H705" s="2" t="n"/>
+      <c r="I705" s="2" t="n"/>
+      <c r="J705" s="2" t="n"/>
+    </row>
+    <row r="706">
+      <c r="A706" s="2" t="n"/>
+      <c r="B706" s="2" t="n"/>
+      <c r="C706" s="2" t="n"/>
+      <c r="D706" s="2" t="n"/>
+      <c r="E706" s="2" t="n"/>
+      <c r="F706" s="2" t="n"/>
+      <c r="G706" s="2" t="n"/>
+      <c r="H706" s="2" t="n"/>
+      <c r="I706" s="2" t="n"/>
+      <c r="J706" s="2" t="n"/>
+    </row>
+    <row r="707">
+      <c r="A707" s="2" t="n"/>
+      <c r="B707" s="2" t="n"/>
+      <c r="C707" s="2" t="n"/>
+      <c r="D707" s="2" t="n"/>
+      <c r="E707" s="2" t="n"/>
+      <c r="F707" s="2" t="n"/>
+      <c r="G707" s="2" t="n"/>
+      <c r="H707" s="2" t="n"/>
+      <c r="I707" s="2" t="n"/>
+      <c r="J707" s="2" t="n"/>
+    </row>
+    <row r="708">
+      <c r="A708" s="2" t="n"/>
+      <c r="B708" s="2" t="n"/>
+      <c r="C708" s="2" t="n"/>
+      <c r="D708" s="2" t="n"/>
+      <c r="E708" s="2" t="n"/>
+      <c r="F708" s="2" t="n"/>
+      <c r="G708" s="2" t="n"/>
+      <c r="H708" s="2" t="n"/>
+      <c r="I708" s="2" t="n"/>
+      <c r="J708" s="2" t="n"/>
+    </row>
+    <row r="709">
+      <c r="A709" s="2" t="n"/>
+      <c r="B709" s="2" t="n"/>
+      <c r="C709" s="2" t="n"/>
+      <c r="D709" s="2" t="n"/>
+      <c r="E709" s="2" t="n"/>
+      <c r="F709" s="2" t="n"/>
+      <c r="G709" s="2" t="n"/>
+      <c r="H709" s="2" t="n"/>
+      <c r="I709" s="2" t="n"/>
+      <c r="J709" s="2" t="n"/>
+    </row>
+    <row r="710">
+      <c r="A710" s="2" t="n"/>
+      <c r="B710" s="2" t="n"/>
+      <c r="C710" s="2" t="n"/>
+      <c r="D710" s="2" t="n"/>
+      <c r="E710" s="2" t="n"/>
+      <c r="F710" s="2" t="n"/>
+      <c r="G710" s="2" t="n"/>
+      <c r="H710" s="2" t="n"/>
+      <c r="I710" s="2" t="n"/>
+      <c r="J710" s="2" t="n"/>
+    </row>
+    <row r="711">
+      <c r="A711" s="2" t="n"/>
+      <c r="B711" s="2" t="n"/>
+      <c r="C711" s="2" t="n"/>
+      <c r="D711" s="2" t="n"/>
+      <c r="E711" s="2" t="n"/>
+      <c r="F711" s="2" t="n"/>
+      <c r="G711" s="2" t="n"/>
+      <c r="H711" s="2" t="n"/>
+      <c r="I711" s="2" t="n"/>
+      <c r="J711" s="2" t="n"/>
+    </row>
+    <row r="712">
+      <c r="A712" s="2" t="n"/>
+      <c r="B712" s="2" t="n"/>
+      <c r="C712" s="2" t="n"/>
+      <c r="D712" s="2" t="n"/>
+      <c r="E712" s="2" t="n"/>
+      <c r="F712" s="2" t="n"/>
+      <c r="G712" s="2" t="n"/>
+      <c r="H712" s="2" t="n"/>
+      <c r="I712" s="2" t="n"/>
+      <c r="J712" s="2" t="n"/>
+    </row>
+    <row r="713">
+      <c r="A713" s="2" t="n"/>
+      <c r="B713" s="2" t="n"/>
+      <c r="C713" s="2" t="n"/>
+      <c r="D713" s="2" t="n"/>
+      <c r="E713" s="2" t="n"/>
+      <c r="F713" s="2" t="n"/>
+      <c r="G713" s="2" t="n"/>
+      <c r="H713" s="2" t="n"/>
+      <c r="I713" s="2" t="n"/>
+      <c r="J713" s="2" t="n"/>
+    </row>
+    <row r="714">
+      <c r="A714" s="2" t="n"/>
+      <c r="B714" s="2" t="n"/>
+      <c r="C714" s="2" t="n"/>
+      <c r="D714" s="2" t="n"/>
+      <c r="E714" s="2" t="n"/>
+      <c r="F714" s="2" t="n"/>
+      <c r="G714" s="2" t="n"/>
+      <c r="H714" s="2" t="n"/>
+      <c r="I714" s="2" t="n"/>
+      <c r="J714" s="2" t="n"/>
+    </row>
+    <row r="715">
+      <c r="A715" s="2" t="n"/>
+      <c r="B715" s="2" t="n"/>
+      <c r="C715" s="2" t="n"/>
+      <c r="D715" s="2" t="n"/>
+      <c r="E715" s="2" t="n"/>
+      <c r="F715" s="2" t="n"/>
+      <c r="G715" s="2" t="n"/>
+      <c r="H715" s="2" t="n"/>
+      <c r="I715" s="2" t="n"/>
+      <c r="J715" s="2" t="n"/>
+    </row>
+    <row r="716">
+      <c r="A716" s="2" t="n"/>
+      <c r="B716" s="2" t="n"/>
+      <c r="C716" s="2" t="n"/>
+      <c r="D716" s="2" t="n"/>
+      <c r="E716" s="2" t="n"/>
+      <c r="F716" s="2" t="n"/>
+      <c r="G716" s="2" t="n"/>
+      <c r="H716" s="2" t="n"/>
+      <c r="I716" s="2" t="n"/>
+      <c r="J716" s="2" t="n"/>
+    </row>
+    <row r="717">
+      <c r="A717" s="2" t="n"/>
+      <c r="B717" s="2" t="n"/>
+      <c r="C717" s="2" t="n"/>
+      <c r="D717" s="2" t="n"/>
+      <c r="E717" s="2" t="n"/>
+      <c r="F717" s="2" t="n"/>
+      <c r="G717" s="2" t="n"/>
+      <c r="H717" s="2" t="n"/>
+      <c r="I717" s="2" t="n"/>
+      <c r="J717" s="2" t="n"/>
+    </row>
+    <row r="718">
+      <c r="A718" s="2" t="n"/>
+      <c r="B718" s="2" t="n"/>
+      <c r="C718" s="2" t="n"/>
+      <c r="D718" s="2" t="n"/>
+      <c r="E718" s="2" t="n"/>
+      <c r="F718" s="2" t="n"/>
+      <c r="G718" s="2" t="n"/>
+      <c r="H718" s="2" t="n"/>
+      <c r="I718" s="2" t="n"/>
+      <c r="J718" s="2" t="n"/>
+    </row>
+    <row r="719">
+      <c r="A719" s="2" t="n"/>
+      <c r="B719" s="2" t="n"/>
+      <c r="C719" s="2" t="n"/>
+      <c r="D719" s="2" t="n"/>
+      <c r="E719" s="2" t="n"/>
+      <c r="F719" s="2" t="n"/>
+      <c r="G719" s="2" t="n"/>
+      <c r="H719" s="2" t="n"/>
+      <c r="I719" s="2" t="n"/>
+      <c r="J719" s="2" t="n"/>
+    </row>
+    <row r="720">
+      <c r="A720" s="2" t="n"/>
+      <c r="B720" s="2" t="n"/>
+      <c r="C720" s="2" t="n"/>
+      <c r="D720" s="2" t="n"/>
+      <c r="E720" s="2" t="n"/>
+      <c r="F720" s="2" t="n"/>
+      <c r="G720" s="2" t="n"/>
+      <c r="H720" s="2" t="n"/>
+      <c r="I720" s="2" t="n"/>
+      <c r="J720" s="2" t="n"/>
+    </row>
+    <row r="721">
+      <c r="A721" s="2" t="n"/>
+      <c r="B721" s="2" t="n"/>
+      <c r="C721" s="2" t="n"/>
+      <c r="D721" s="2" t="n"/>
+      <c r="E721" s="2" t="n"/>
+      <c r="F721" s="2" t="n"/>
+      <c r="G721" s="2" t="n"/>
+      <c r="H721" s="2" t="n"/>
+      <c r="I721" s="2" t="n"/>
+      <c r="J721" s="2" t="n"/>
+    </row>
+    <row r="722">
+      <c r="A722" s="2" t="n"/>
+      <c r="B722" s="2" t="n"/>
+      <c r="C722" s="2" t="n"/>
+      <c r="D722" s="2" t="n"/>
+      <c r="E722" s="2" t="n"/>
+      <c r="F722" s="2" t="n"/>
+      <c r="G722" s="2" t="n"/>
+      <c r="H722" s="2" t="n"/>
+      <c r="I722" s="2" t="n"/>
+      <c r="J722" s="2" t="n"/>
+    </row>
+    <row r="723">
+      <c r="A723" s="2" t="n"/>
+      <c r="B723" s="2" t="n"/>
+      <c r="C723" s="2" t="n"/>
+      <c r="D723" s="2" t="n"/>
+      <c r="E723" s="2" t="n"/>
+      <c r="F723" s="2" t="n"/>
+      <c r="G723" s="2" t="n"/>
+      <c r="H723" s="2" t="n"/>
+      <c r="I723" s="2" t="n"/>
+      <c r="J723" s="2" t="n"/>
+    </row>
+    <row r="724">
+      <c r="A724" s="2" t="n"/>
+      <c r="B724" s="2" t="n"/>
+      <c r="C724" s="2" t="n"/>
+      <c r="D724" s="2" t="n"/>
+      <c r="E724" s="2" t="n"/>
+      <c r="F724" s="2" t="n"/>
+      <c r="G724" s="2" t="n"/>
+      <c r="H724" s="2" t="n"/>
+      <c r="I724" s="2" t="n"/>
+      <c r="J724" s="2" t="n"/>
+    </row>
+    <row r="725">
+      <c r="A725" s="2" t="n"/>
+      <c r="B725" s="2" t="n"/>
+      <c r="C725" s="2" t="n"/>
+      <c r="D725" s="2" t="n"/>
+      <c r="E725" s="2" t="n"/>
+      <c r="F725" s="2" t="n"/>
+      <c r="G725" s="2" t="n"/>
+      <c r="H725" s="2" t="n"/>
+      <c r="I725" s="2" t="n"/>
+      <c r="J725" s="2" t="n"/>
+    </row>
+    <row r="726">
+      <c r="A726" s="2" t="n"/>
+      <c r="B726" s="2" t="n"/>
+      <c r="C726" s="2" t="n"/>
+      <c r="D726" s="2" t="n"/>
+      <c r="E726" s="2" t="n"/>
+      <c r="F726" s="2" t="n"/>
+      <c r="G726" s="2" t="n"/>
+      <c r="H726" s="2" t="n"/>
+      <c r="I726" s="2" t="n"/>
+      <c r="J726" s="2" t="n"/>
+    </row>
+    <row r="727">
+      <c r="A727" s="2" t="n"/>
+      <c r="B727" s="2" t="n"/>
+      <c r="C727" s="2" t="n"/>
+      <c r="D727" s="2" t="n"/>
+      <c r="E727" s="2" t="n"/>
+      <c r="F727" s="2" t="n"/>
+      <c r="G727" s="2" t="n"/>
+      <c r="H727" s="2" t="n"/>
+      <c r="I727" s="2" t="n"/>
+      <c r="J727" s="2" t="n"/>
+    </row>
+    <row r="728">
+      <c r="A728" s="2" t="n"/>
+      <c r="B728" s="2" t="n"/>
+      <c r="C728" s="2" t="n"/>
+      <c r="D728" s="2" t="n"/>
+      <c r="E728" s="2" t="n"/>
+      <c r="F728" s="2" t="n"/>
+      <c r="G728" s="2" t="n"/>
+      <c r="H728" s="2" t="n"/>
+      <c r="I728" s="2" t="n"/>
+      <c r="J728" s="2" t="n"/>
+    </row>
+    <row r="729">
+      <c r="A729" s="2" t="n"/>
+      <c r="B729" s="2" t="n"/>
+      <c r="C729" s="2" t="n"/>
+      <c r="D729" s="2" t="n"/>
+      <c r="E729" s="2" t="n"/>
+      <c r="F729" s="2" t="n"/>
+      <c r="G729" s="2" t="n"/>
+      <c r="H729" s="2" t="n"/>
+      <c r="I729" s="2" t="n"/>
+      <c r="J729" s="2" t="n"/>
+    </row>
+    <row r="730">
+      <c r="A730" s="2" t="n"/>
+      <c r="B730" s="2" t="n"/>
+      <c r="C730" s="2" t="n"/>
+      <c r="D730" s="2" t="n"/>
+      <c r="E730" s="2" t="n"/>
+      <c r="F730" s="2" t="n"/>
+      <c r="G730" s="2" t="n"/>
+      <c r="H730" s="2" t="n"/>
+      <c r="I730" s="2" t="n"/>
+      <c r="J730" s="2" t="n"/>
+    </row>
+    <row r="731">
+      <c r="A731" s="2" t="n"/>
+      <c r="B731" s="2" t="n"/>
+      <c r="C731" s="2" t="n"/>
+      <c r="D731" s="2" t="n"/>
+      <c r="E731" s="2" t="n"/>
+      <c r="F731" s="2" t="n"/>
+      <c r="G731" s="2" t="n"/>
+      <c r="H731" s="2" t="n"/>
+      <c r="I731" s="2" t="n"/>
+      <c r="J731" s="2" t="n"/>
+    </row>
+    <row r="732">
+      <c r="A732" s="2" t="n"/>
+      <c r="B732" s="2" t="n"/>
+      <c r="C732" s="2" t="n"/>
+      <c r="D732" s="2" t="n"/>
+      <c r="E732" s="2" t="n"/>
+      <c r="F732" s="2" t="n"/>
+      <c r="G732" s="2" t="n"/>
+      <c r="H732" s="2" t="n"/>
+      <c r="I732" s="2" t="n"/>
+      <c r="J732" s="2" t="n"/>
+    </row>
+    <row r="733">
+      <c r="A733" s="2" t="n"/>
+      <c r="B733" s="2" t="n"/>
+      <c r="C733" s="2" t="n"/>
+      <c r="D733" s="2" t="n"/>
+      <c r="E733" s="2" t="n"/>
+      <c r="F733" s="2" t="n"/>
+      <c r="G733" s="2" t="n"/>
+      <c r="H733" s="2" t="n"/>
+      <c r="I733" s="2" t="n"/>
+      <c r="J733" s="2" t="n"/>
+    </row>
+    <row r="734">
+      <c r="A734" s="2" t="n"/>
+      <c r="B734" s="2" t="n"/>
+      <c r="C734" s="2" t="n"/>
+      <c r="D734" s="2" t="n"/>
+      <c r="E734" s="2" t="n"/>
+      <c r="F734" s="2" t="n"/>
+      <c r="G734" s="2" t="n"/>
+      <c r="H734" s="2" t="n"/>
+      <c r="I734" s="2" t="n"/>
+      <c r="J734" s="2" t="n"/>
+    </row>
+    <row r="735">
+      <c r="A735" s="2" t="n"/>
+      <c r="B735" s="2" t="n"/>
+      <c r="C735" s="2" t="n"/>
+      <c r="D735" s="2" t="n"/>
+      <c r="E735" s="2" t="n"/>
+      <c r="F735" s="2" t="n"/>
+      <c r="G735" s="2" t="n"/>
+      <c r="H735" s="2" t="n"/>
+      <c r="I735" s="2" t="n"/>
+      <c r="J735" s="2" t="n"/>
+    </row>
+    <row r="736">
+      <c r="A736" s="2" t="n"/>
+      <c r="B736" s="2" t="n"/>
+      <c r="C736" s="2" t="n"/>
+      <c r="D736" s="2" t="n"/>
+      <c r="E736" s="2" t="n"/>
+      <c r="F736" s="2" t="n"/>
+      <c r="G736" s="2" t="n"/>
+      <c r="H736" s="2" t="n"/>
+      <c r="I736" s="2" t="n"/>
+      <c r="J736" s="2" t="n"/>
+    </row>
+    <row r="737">
+      <c r="A737" s="2" t="n"/>
+      <c r="B737" s="2" t="n"/>
+      <c r="C737" s="2" t="n"/>
+      <c r="D737" s="2" t="n"/>
+      <c r="E737" s="2" t="n"/>
+      <c r="F737" s="2" t="n"/>
+      <c r="G737" s="2" t="n"/>
+      <c r="H737" s="2" t="n"/>
+      <c r="I737" s="2" t="n"/>
+      <c r="J737" s="2" t="n"/>
+    </row>
+    <row r="738">
+      <c r="A738" s="2" t="n"/>
+      <c r="B738" s="2" t="n"/>
+      <c r="C738" s="2" t="n"/>
+      <c r="D738" s="2" t="n"/>
+      <c r="E738" s="2" t="n"/>
+      <c r="F738" s="2" t="n"/>
+      <c r="G738" s="2" t="n"/>
+      <c r="H738" s="2" t="n"/>
+      <c r="I738" s="2" t="n"/>
+      <c r="J738" s="2" t="n"/>
+    </row>
+    <row r="739">
+      <c r="A739" s="2" t="n"/>
+      <c r="B739" s="2" t="n"/>
+      <c r="C739" s="2" t="n"/>
+      <c r="D739" s="2" t="n"/>
+      <c r="E739" s="2" t="n"/>
+      <c r="F739" s="2" t="n"/>
+      <c r="G739" s="2" t="n"/>
+      <c r="H739" s="2" t="n"/>
+      <c r="I739" s="2" t="n"/>
+      <c r="J739" s="2" t="n"/>
+    </row>
+    <row r="740">
+      <c r="A740" s="2" t="n"/>
+      <c r="B740" s="2" t="n"/>
+      <c r="C740" s="2" t="n"/>
+      <c r="D740" s="2" t="n"/>
+      <c r="E740" s="2" t="n"/>
+      <c r="F740" s="2" t="n"/>
+      <c r="G740" s="2" t="n"/>
+      <c r="H740" s="2" t="n"/>
+      <c r="I740" s="2" t="n"/>
+      <c r="J740" s="2" t="n"/>
+    </row>
+    <row r="741">
+      <c r="A741" s="2" t="n"/>
+      <c r="B741" s="2" t="n"/>
+      <c r="C741" s="2" t="n"/>
+      <c r="D741" s="2" t="n"/>
+      <c r="E741" s="2" t="n"/>
+      <c r="F741" s="2" t="n"/>
+      <c r="G741" s="2" t="n"/>
+      <c r="H741" s="2" t="n"/>
+      <c r="I741" s="2" t="n"/>
+      <c r="J741" s="2" t="n"/>
+    </row>
+    <row r="742">
+      <c r="A742" s="2" t="n"/>
+      <c r="B742" s="2" t="n"/>
+      <c r="C742" s="2" t="n"/>
+      <c r="D742" s="2" t="n"/>
+      <c r="E742" s="2" t="n"/>
+      <c r="F742" s="2" t="n"/>
+      <c r="G742" s="2" t="n"/>
+      <c r="H742" s="2" t="n"/>
+      <c r="I742" s="2" t="n"/>
+      <c r="J742" s="2" t="n"/>
+    </row>
+    <row r="743">
+      <c r="A743" s="2" t="n"/>
+      <c r="B743" s="2" t="n"/>
+      <c r="C743" s="2" t="n"/>
+      <c r="D743" s="2" t="n"/>
+      <c r="E743" s="2" t="n"/>
+      <c r="F743" s="2" t="n"/>
+      <c r="G743" s="2" t="n"/>
+      <c r="H743" s="2" t="n"/>
+      <c r="I743" s="2" t="n"/>
+      <c r="J743" s="2" t="n"/>
+    </row>
+    <row r="744">
+      <c r="A744" s="2" t="n"/>
+      <c r="B744" s="2" t="n"/>
+      <c r="C744" s="2" t="n"/>
+      <c r="D744" s="2" t="n"/>
+      <c r="E744" s="2" t="n"/>
+      <c r="F744" s="2" t="n"/>
+      <c r="G744" s="2" t="n"/>
+      <c r="H744" s="2" t="n"/>
+      <c r="I744" s="2" t="n"/>
+      <c r="J744" s="2" t="n"/>
+    </row>
+    <row r="745">
+      <c r="A745" s="2" t="n"/>
+      <c r="B745" s="2" t="n"/>
+      <c r="C745" s="2" t="n"/>
+      <c r="D745" s="2" t="n"/>
+      <c r="E745" s="2" t="n"/>
+      <c r="F745" s="2" t="n"/>
+      <c r="G745" s="2" t="n"/>
+      <c r="H745" s="2" t="n"/>
+      <c r="I745" s="2" t="n"/>
+      <c r="J745" s="2" t="n"/>
+    </row>
+    <row r="746">
+      <c r="A746" s="2" t="n"/>
+      <c r="B746" s="2" t="n"/>
+      <c r="C746" s="2" t="n"/>
+      <c r="D746" s="2" t="n"/>
+      <c r="E746" s="2" t="n"/>
+      <c r="F746" s="2" t="n"/>
+      <c r="G746" s="2" t="n"/>
+      <c r="H746" s="2" t="n"/>
+      <c r="I746" s="2" t="n"/>
+      <c r="J746" s="2" t="n"/>
+    </row>
+    <row r="747">
+      <c r="A747" s="2" t="n"/>
+      <c r="B747" s="2" t="n"/>
+      <c r="C747" s="2" t="n"/>
+      <c r="D747" s="2" t="n"/>
+      <c r="E747" s="2" t="n"/>
+      <c r="F747" s="2" t="n"/>
+      <c r="G747" s="2" t="n"/>
+      <c r="H747" s="2" t="n"/>
+      <c r="I747" s="2" t="n"/>
+      <c r="J747" s="2" t="n"/>
+    </row>
+    <row r="748">
+      <c r="A748" s="2" t="n"/>
+      <c r="B748" s="2" t="n"/>
+      <c r="C748" s="2" t="n"/>
+      <c r="D748" s="2" t="n"/>
+      <c r="E748" s="2" t="n"/>
+      <c r="F748" s="2" t="n"/>
+      <c r="G748" s="2" t="n"/>
+      <c r="H748" s="2" t="n"/>
+      <c r="I748" s="2" t="n"/>
+      <c r="J748" s="2" t="n"/>
+    </row>
+    <row r="749">
+      <c r="A749" s="2" t="n"/>
+      <c r="B749" s="2" t="n"/>
+      <c r="C749" s="2" t="n"/>
+      <c r="D749" s="2" t="n"/>
+      <c r="E749" s="2" t="n"/>
+      <c r="F749" s="2" t="n"/>
+      <c r="G749" s="2" t="n"/>
+      <c r="H749" s="2" t="n"/>
+      <c r="I749" s="2" t="n"/>
+      <c r="J749" s="2" t="n"/>
+    </row>
+    <row r="750">
+      <c r="A750" s="2" t="n"/>
+      <c r="B750" s="2" t="n"/>
+      <c r="C750" s="2" t="n"/>
+      <c r="D750" s="2" t="n"/>
+      <c r="E750" s="2" t="n"/>
+      <c r="F750" s="2" t="n"/>
+      <c r="G750" s="2" t="n"/>
+      <c r="H750" s="2" t="n"/>
+      <c r="I750" s="2" t="n"/>
+      <c r="J750" s="2" t="n"/>
+    </row>
+    <row r="751">
+      <c r="A751" s="2" t="n"/>
+      <c r="B751" s="2" t="n"/>
+      <c r="C751" s="2" t="n"/>
+      <c r="D751" s="2" t="n"/>
+      <c r="E751" s="2" t="n"/>
+      <c r="F751" s="2" t="n"/>
+      <c r="G751" s="2" t="n"/>
+      <c r="H751" s="2" t="n"/>
+      <c r="I751" s="2" t="n"/>
+      <c r="J751" s="2" t="n"/>
+    </row>
+    <row r="752">
+      <c r="A752" s="2" t="n"/>
+      <c r="B752" s="2" t="n"/>
+      <c r="C752" s="2" t="n"/>
+      <c r="D752" s="2" t="n"/>
+      <c r="E752" s="2" t="n"/>
+      <c r="F752" s="2" t="n"/>
+      <c r="G752" s="2" t="n"/>
+      <c r="H752" s="2" t="n"/>
+      <c r="I752" s="2" t="n"/>
+      <c r="J752" s="2" t="n"/>
+    </row>
+    <row r="753">
+      <c r="A753" s="2" t="n"/>
+      <c r="B753" s="2" t="n"/>
+      <c r="C753" s="2" t="n"/>
+      <c r="D753" s="2" t="n"/>
+      <c r="E753" s="2" t="n"/>
+      <c r="F753" s="2" t="n"/>
+      <c r="G753" s="2" t="n"/>
+      <c r="H753" s="2" t="n"/>
+      <c r="I753" s="2" t="n"/>
+      <c r="J753" s="2" t="n"/>
+    </row>
+    <row r="754">
+      <c r="A754" s="2" t="n"/>
+      <c r="B754" s="2" t="n"/>
+      <c r="C754" s="2" t="n"/>
+      <c r="D754" s="2" t="n"/>
+      <c r="E754" s="2" t="n"/>
+      <c r="F754" s="2" t="n"/>
+      <c r="G754" s="2" t="n"/>
+      <c r="H754" s="2" t="n"/>
+      <c r="I754" s="2" t="n"/>
+      <c r="J754" s="2" t="n"/>
+    </row>
+    <row r="755">
+      <c r="A755" s="2" t="n"/>
+      <c r="B755" s="2" t="n"/>
+      <c r="C755" s="2" t="n"/>
+      <c r="D755" s="2" t="n"/>
+      <c r="E755" s="2" t="n"/>
+      <c r="F755" s="2" t="n"/>
+      <c r="G755" s="2" t="n"/>
+      <c r="H755" s="2" t="n"/>
+      <c r="I755" s="2" t="n"/>
+      <c r="J755" s="2" t="n"/>
+    </row>
+    <row r="756">
+      <c r="A756" s="2" t="n"/>
+      <c r="B756" s="2" t="n"/>
+      <c r="C756" s="2" t="n"/>
+      <c r="D756" s="2" t="n"/>
+      <c r="E756" s="2" t="n"/>
+      <c r="F756" s="2" t="n"/>
+      <c r="G756" s="2" t="n"/>
+      <c r="H756" s="2" t="n"/>
+      <c r="I756" s="2" t="n"/>
+      <c r="J756" s="2" t="n"/>
+    </row>
+    <row r="757">
+      <c r="A757" s="2" t="n"/>
+      <c r="B757" s="2" t="n"/>
+      <c r="C757" s="2" t="n"/>
+      <c r="D757" s="2" t="n"/>
+      <c r="E757" s="2" t="n"/>
+      <c r="F757" s="2" t="n"/>
+      <c r="G757" s="2" t="n"/>
+      <c r="H757" s="2" t="n"/>
+      <c r="I757" s="2" t="n"/>
+      <c r="J757" s="2" t="n"/>
+    </row>
+    <row r="758">
+      <c r="A758" s="2" t="n"/>
+      <c r="B758" s="2" t="n"/>
+      <c r="C758" s="2" t="n"/>
+      <c r="D758" s="2" t="n"/>
+      <c r="E758" s="2" t="n"/>
+      <c r="F758" s="2" t="n"/>
+      <c r="G758" s="2" t="n"/>
+      <c r="H758" s="2" t="n"/>
+      <c r="I758" s="2" t="n"/>
+      <c r="J758" s="2" t="n"/>
+    </row>
+    <row r="759">
+      <c r="A759" s="2" t="n"/>
+      <c r="B759" s="2" t="n"/>
+      <c r="C759" s="2" t="n"/>
+      <c r="D759" s="2" t="n"/>
+      <c r="E759" s="2" t="n"/>
+      <c r="F759" s="2" t="n"/>
+      <c r="G759" s="2" t="n"/>
+      <c r="H759" s="2" t="n"/>
+      <c r="I759" s="2" t="n"/>
+      <c r="J759" s="2" t="n"/>
+    </row>
+    <row r="760">
+      <c r="A760" s="2" t="n"/>
+      <c r="B760" s="2" t="n"/>
+      <c r="C760" s="2" t="n"/>
+      <c r="D760" s="2" t="n"/>
+      <c r="E760" s="2" t="n"/>
+      <c r="F760" s="2" t="n"/>
+      <c r="G760" s="2" t="n"/>
+      <c r="H760" s="2" t="n"/>
+      <c r="I760" s="2" t="n"/>
+      <c r="J760" s="2" t="n"/>
+    </row>
+    <row r="761">
+      <c r="A761" s="2" t="n"/>
+      <c r="B761" s="2" t="n"/>
+      <c r="C761" s="2" t="n"/>
+      <c r="D761" s="2" t="n"/>
+      <c r="E761" s="2" t="n"/>
+      <c r="F761" s="2" t="n"/>
+      <c r="G761" s="2" t="n"/>
+      <c r="H761" s="2" t="n"/>
+      <c r="I761" s="2" t="n"/>
+      <c r="J761" s="2" t="n"/>
+    </row>
+    <row r="762">
+      <c r="A762" s="2" t="n"/>
+      <c r="B762" s="2" t="n"/>
+      <c r="C762" s="2" t="n"/>
+      <c r="D762" s="2" t="n"/>
+      <c r="E762" s="2" t="n"/>
+      <c r="F762" s="2" t="n"/>
+      <c r="G762" s="2" t="n"/>
+      <c r="H762" s="2" t="n"/>
+      <c r="I762" s="2" t="n"/>
+      <c r="J762" s="2" t="n"/>
+    </row>
+    <row r="763">
+      <c r="A763" s="2" t="n"/>
+      <c r="B763" s="2" t="n"/>
+      <c r="C763" s="2" t="n"/>
+      <c r="D763" s="2" t="n"/>
+      <c r="E763" s="2" t="n"/>
+      <c r="F763" s="2" t="n"/>
+      <c r="G763" s="2" t="n"/>
+      <c r="H763" s="2" t="n"/>
+      <c r="I763" s="2" t="n"/>
+      <c r="J763" s="2" t="n"/>
+    </row>
+    <row r="764">
+      <c r="A764" s="2" t="n"/>
+      <c r="B764" s="2" t="n"/>
+      <c r="C764" s="2" t="n"/>
+      <c r="D764" s="2" t="n"/>
+      <c r="E764" s="2" t="n"/>
+      <c r="F764" s="2" t="n"/>
+      <c r="G764" s="2" t="n"/>
+      <c r="H764" s="2" t="n"/>
+      <c r="I764" s="2" t="n"/>
+      <c r="J764" s="2" t="n"/>
+    </row>
+    <row r="765">
+      <c r="A765" s="2" t="n"/>
+      <c r="B765" s="2" t="n"/>
+      <c r="C765" s="2" t="n"/>
+      <c r="D765" s="2" t="n"/>
+      <c r="E765" s="2" t="n"/>
+      <c r="F765" s="2" t="n"/>
+      <c r="G765" s="2" t="n"/>
+      <c r="H765" s="2" t="n"/>
+      <c r="I765" s="2" t="n"/>
+      <c r="J765" s="2" t="n"/>
+    </row>
+    <row r="766">
+      <c r="A766" s="2" t="n"/>
+      <c r="B766" s="2" t="n"/>
+      <c r="C766" s="2" t="n"/>
+      <c r="D766" s="2" t="n"/>
+      <c r="E766" s="2" t="n"/>
+      <c r="F766" s="2" t="n"/>
+      <c r="G766" s="2" t="n"/>
+      <c r="H766" s="2" t="n"/>
+      <c r="I766" s="2" t="n"/>
+      <c r="J766" s="2" t="n"/>
+    </row>
+    <row r="767">
+      <c r="A767" s="2" t="n"/>
+      <c r="B767" s="2" t="n"/>
+      <c r="C767" s="2" t="n"/>
+      <c r="D767" s="2" t="n"/>
+      <c r="E767" s="2" t="n"/>
+      <c r="F767" s="2" t="n"/>
+      <c r="G767" s="2" t="n"/>
+      <c r="H767" s="2" t="n"/>
+      <c r="I767" s="2" t="n"/>
+      <c r="J767" s="2" t="n"/>
+    </row>
+    <row r="768">
+      <c r="A768" s="2" t="n"/>
+      <c r="B768" s="2" t="n"/>
+      <c r="C768" s="2" t="n"/>
+      <c r="D768" s="2" t="n"/>
+      <c r="E768" s="2" t="n"/>
+      <c r="F768" s="2" t="n"/>
+      <c r="G768" s="2" t="n"/>
+      <c r="H768" s="2" t="n"/>
+      <c r="I768" s="2" t="n"/>
+      <c r="J768" s="2" t="n"/>
+    </row>
+    <row r="769">
+      <c r="A769" s="2" t="n"/>
+      <c r="B769" s="2" t="n"/>
+      <c r="C769" s="2" t="n"/>
+      <c r="D769" s="2" t="n"/>
+      <c r="E769" s="2" t="n"/>
+      <c r="F769" s="2" t="n"/>
+      <c r="G769" s="2" t="n"/>
+      <c r="H769" s="2" t="n"/>
+      <c r="I769" s="2" t="n"/>
+      <c r="J769" s="2" t="n"/>
+    </row>
+    <row r="770">
+      <c r="A770" s="2" t="n"/>
+      <c r="B770" s="2" t="n"/>
+      <c r="C770" s="2" t="n"/>
+      <c r="D770" s="2" t="n"/>
+      <c r="E770" s="2" t="n"/>
+      <c r="F770" s="2" t="n"/>
+      <c r="G770" s="2" t="n"/>
+      <c r="H770" s="2" t="n"/>
+      <c r="I770" s="2" t="n"/>
+      <c r="J770" s="2" t="n"/>
+    </row>
+    <row r="771">
+      <c r="A771" s="2" t="n"/>
+      <c r="B771" s="2" t="n"/>
+      <c r="C771" s="2" t="n"/>
+      <c r="D771" s="2" t="n"/>
+      <c r="E771" s="2" t="n"/>
+      <c r="F771" s="2" t="n"/>
+      <c r="G771" s="2" t="n"/>
+      <c r="H771" s="2" t="n"/>
+      <c r="I771" s="2" t="n"/>
+      <c r="J771" s="2" t="n"/>
+    </row>
+    <row r="772">
+      <c r="A772" s="2" t="n"/>
+      <c r="B772" s="2" t="n"/>
+      <c r="C772" s="2" t="n"/>
+      <c r="D772" s="2" t="n"/>
+      <c r="E772" s="2" t="n"/>
+      <c r="F772" s="2" t="n"/>
+      <c r="G772" s="2" t="n"/>
+      <c r="H772" s="2" t="n"/>
+      <c r="I772" s="2" t="n"/>
+      <c r="J772" s="2" t="n"/>
+    </row>
+    <row r="773">
+      <c r="A773" s="2" t="n"/>
+      <c r="B773" s="2" t="n"/>
+      <c r="C773" s="2" t="n"/>
+      <c r="D773" s="2" t="n"/>
+      <c r="E773" s="2" t="n"/>
+      <c r="F773" s="2" t="n"/>
+      <c r="G773" s="2" t="n"/>
+      <c r="H773" s="2" t="n"/>
+      <c r="I773" s="2" t="n"/>
+      <c r="J773" s="2" t="n"/>
+    </row>
+    <row r="774">
+      <c r="A774" s="2" t="n"/>
+      <c r="B774" s="2" t="n"/>
+      <c r="C774" s="2" t="n"/>
+      <c r="D774" s="2" t="n"/>
+      <c r="E774" s="2" t="n"/>
+      <c r="F774" s="2" t="n"/>
+      <c r="G774" s="2" t="n"/>
+      <c r="H774" s="2" t="n"/>
+      <c r="I774" s="2" t="n"/>
+      <c r="J774" s="2" t="n"/>
+    </row>
+    <row r="775">
+      <c r="A775" s="2" t="n"/>
+      <c r="B775" s="2" t="n"/>
+      <c r="C775" s="2" t="n"/>
+      <c r="D775" s="2" t="n"/>
+      <c r="E775" s="2" t="n"/>
+      <c r="F775" s="2" t="n"/>
+      <c r="G775" s="2" t="n"/>
+      <c r="H775" s="2" t="n"/>
+      <c r="I775" s="2" t="n"/>
+      <c r="J775" s="2" t="n"/>
+    </row>
+    <row r="776">
+      <c r="A776" s="2" t="n"/>
+      <c r="B776" s="2" t="n"/>
+      <c r="C776" s="2" t="n"/>
+      <c r="D776" s="2" t="n"/>
+      <c r="E776" s="2" t="n"/>
+      <c r="F776" s="2" t="n"/>
+      <c r="G776" s="2" t="n"/>
+      <c r="H776" s="2" t="n"/>
+      <c r="I776" s="2" t="n"/>
+      <c r="J776" s="2" t="n"/>
+    </row>
+    <row r="777">
+      <c r="A777" s="2" t="n"/>
+      <c r="B777" s="2" t="n"/>
+      <c r="C777" s="2" t="n"/>
+      <c r="D777" s="2" t="n"/>
+      <c r="E777" s="2" t="n"/>
+      <c r="F777" s="2" t="n"/>
+      <c r="G777" s="2" t="n"/>
+      <c r="H777" s="2" t="n"/>
+      <c r="I777" s="2" t="n"/>
+      <c r="J777" s="2" t="n"/>
+    </row>
+    <row r="778">
+      <c r="A778" s="2" t="n"/>
+      <c r="B778" s="2" t="n"/>
+      <c r="C778" s="2" t="n"/>
+      <c r="D778" s="2" t="n"/>
+      <c r="E778" s="2" t="n"/>
+      <c r="F778" s="2" t="n"/>
+      <c r="G778" s="2" t="n"/>
+      <c r="H778" s="2" t="n"/>
+      <c r="I778" s="2" t="n"/>
+      <c r="J778" s="2" t="n"/>
+    </row>
+    <row r="779">
+      <c r="A779" s="2" t="n"/>
+      <c r="B779" s="2" t="n"/>
+      <c r="C779" s="2" t="n"/>
+      <c r="D779" s="2" t="n"/>
+      <c r="E779" s="2" t="n"/>
+      <c r="F779" s="2" t="n"/>
+      <c r="G779" s="2" t="n"/>
+      <c r="H779" s="2" t="n"/>
+      <c r="I779" s="2" t="n"/>
+      <c r="J779" s="2" t="n"/>
+    </row>
+    <row r="780">
+      <c r="A780" s="2" t="n"/>
+      <c r="B780" s="2" t="n"/>
+      <c r="C780" s="2" t="n"/>
+      <c r="D780" s="2" t="n"/>
+      <c r="E780" s="2" t="n"/>
+      <c r="F780" s="2" t="n"/>
+      <c r="G780" s="2" t="n"/>
+      <c r="H780" s="2" t="n"/>
+      <c r="I780" s="2" t="n"/>
+      <c r="J780" s="2" t="n"/>
+    </row>
+    <row r="781">
+      <c r="A781" s="2" t="n"/>
+      <c r="B781" s="2" t="n"/>
+      <c r="C781" s="2" t="n"/>
+      <c r="D781" s="2" t="n"/>
+      <c r="E781" s="2" t="n"/>
+      <c r="F781" s="2" t="n"/>
+      <c r="G781" s="2" t="n"/>
+      <c r="H781" s="2" t="n"/>
+      <c r="I781" s="2" t="n"/>
+      <c r="J781" s="2" t="n"/>
+    </row>
+    <row r="782">
+      <c r="A782" s="2" t="n"/>
+      <c r="B782" s="2" t="n"/>
+      <c r="C782" s="2" t="n"/>
+      <c r="D782" s="2" t="n"/>
+      <c r="E782" s="2" t="n"/>
+      <c r="F782" s="2" t="n"/>
+      <c r="G782" s="2" t="n"/>
+      <c r="H782" s="2" t="n"/>
+      <c r="I782" s="2" t="n"/>
+      <c r="J782" s="2" t="n"/>
+    </row>
+    <row r="783">
+      <c r="A783" s="2" t="n"/>
+      <c r="B783" s="2" t="n"/>
+      <c r="C783" s="2" t="n"/>
+      <c r="D783" s="2" t="n"/>
+      <c r="E783" s="2" t="n"/>
+      <c r="F783" s="2" t="n"/>
+      <c r="G783" s="2" t="n"/>
+      <c r="H783" s="2" t="n"/>
+      <c r="I783" s="2" t="n"/>
+      <c r="J783" s="2" t="n"/>
+    </row>
+    <row r="784">
+      <c r="A784" s="2" t="n"/>
+      <c r="B784" s="2" t="n"/>
+      <c r="C784" s="2" t="n"/>
+      <c r="D784" s="2" t="n"/>
+      <c r="E784" s="2" t="n"/>
+      <c r="F784" s="2" t="n"/>
+      <c r="G784" s="2" t="n"/>
+      <c r="H784" s="2" t="n"/>
+      <c r="I784" s="2" t="n"/>
+      <c r="J784" s="2" t="n"/>
+    </row>
+    <row r="785">
+      <c r="A785" s="2" t="n"/>
+      <c r="B785" s="2" t="n"/>
+      <c r="C785" s="2" t="n"/>
+      <c r="D785" s="2" t="n"/>
+      <c r="E785" s="2" t="n"/>
+      <c r="F785" s="2" t="n"/>
+      <c r="G785" s="2" t="n"/>
+      <c r="H785" s="2" t="n"/>
+      <c r="I785" s="2" t="n"/>
+      <c r="J785" s="2" t="n"/>
+    </row>
+    <row r="786">
+      <c r="A786" s="2" t="n"/>
+      <c r="B786" s="2" t="n"/>
+      <c r="C786" s="2" t="n"/>
+      <c r="D786" s="2" t="n"/>
+      <c r="E786" s="2" t="n"/>
+      <c r="F786" s="2" t="n"/>
+      <c r="G786" s="2" t="n"/>
+      <c r="H786" s="2" t="n"/>
+      <c r="I786" s="2" t="n"/>
+      <c r="J786" s="2" t="n"/>
+    </row>
+    <row r="787">
+      <c r="A787" s="2" t="n"/>
+      <c r="B787" s="2" t="n"/>
+      <c r="C787" s="2" t="n"/>
+      <c r="D787" s="2" t="n"/>
+      <c r="E787" s="2" t="n"/>
+      <c r="F787" s="2" t="n"/>
+      <c r="G787" s="2" t="n"/>
+      <c r="H787" s="2" t="n"/>
+      <c r="I787" s="2" t="n"/>
+      <c r="J787" s="2" t="n"/>
+    </row>
+    <row r="788">
+      <c r="A788" s="2" t="n"/>
+      <c r="B788" s="2" t="n"/>
+      <c r="C788" s="2" t="n"/>
+      <c r="D788" s="2" t="n"/>
+      <c r="E788" s="2" t="n"/>
+      <c r="F788" s="2" t="n"/>
+      <c r="G788" s="2" t="n"/>
+      <c r="H788" s="2" t="n"/>
+      <c r="I788" s="2" t="n"/>
+      <c r="J788" s="2" t="n"/>
+    </row>
+    <row r="789">
+      <c r="A789" s="2" t="n"/>
+      <c r="B789" s="2" t="n"/>
+      <c r="C789" s="2" t="n"/>
+      <c r="D789" s="2" t="n"/>
+      <c r="E789" s="2" t="n"/>
+      <c r="F789" s="2" t="n"/>
+      <c r="G789" s="2" t="n"/>
+      <c r="H789" s="2" t="n"/>
+      <c r="I789" s="2" t="n"/>
+      <c r="J789" s="2" t="n"/>
+    </row>
+    <row r="790">
+      <c r="A790" s="2" t="n"/>
+      <c r="B790" s="2" t="n"/>
+      <c r="C790" s="2" t="n"/>
+      <c r="D790" s="2" t="n"/>
+      <c r="E790" s="2" t="n"/>
+      <c r="F790" s="2" t="n"/>
+      <c r="G790" s="2" t="n"/>
+      <c r="H790" s="2" t="n"/>
+      <c r="I790" s="2" t="n"/>
+      <c r="J790" s="2" t="n"/>
+    </row>
+    <row r="791">
+      <c r="A791" s="2" t="n"/>
+      <c r="B791" s="2" t="n"/>
+      <c r="C791" s="2" t="n"/>
+      <c r="D791" s="2" t="n"/>
+      <c r="E791" s="2" t="n"/>
+      <c r="F791" s="2" t="n"/>
+      <c r="G791" s="2" t="n"/>
+      <c r="H791" s="2" t="n"/>
+      <c r="I791" s="2" t="n"/>
+      <c r="J791" s="2" t="n"/>
+    </row>
+    <row r="792">
+      <c r="A792" s="2" t="n"/>
+      <c r="B792" s="2" t="n"/>
+      <c r="C792" s="2" t="n"/>
+      <c r="D792" s="2" t="n"/>
+      <c r="E792" s="2" t="n"/>
+      <c r="F792" s="2" t="n"/>
+      <c r="G792" s="2" t="n"/>
+      <c r="H792" s="2" t="n"/>
+      <c r="I792" s="2" t="n"/>
+      <c r="J792" s="2" t="n"/>
+    </row>
+    <row r="793">
+      <c r="A793" s="2" t="n"/>
+      <c r="B793" s="2" t="n"/>
+      <c r="C793" s="2" t="n"/>
+      <c r="D793" s="2" t="n"/>
+      <c r="E793" s="2" t="n"/>
+      <c r="F793" s="2" t="n"/>
+      <c r="G793" s="2" t="n"/>
+      <c r="H793" s="2" t="n"/>
+      <c r="I793" s="2" t="n"/>
+      <c r="J793" s="2" t="n"/>
+    </row>
+    <row r="794">
+      <c r="A794" s="2" t="n"/>
+      <c r="B794" s="2" t="n"/>
+      <c r="C794" s="2" t="n"/>
+      <c r="D794" s="2" t="n"/>
+      <c r="E794" s="2" t="n"/>
+      <c r="F794" s="2" t="n"/>
+      <c r="G794" s="2" t="n"/>
+      <c r="H794" s="2" t="n"/>
+      <c r="I794" s="2" t="n"/>
+      <c r="J794" s="2" t="n"/>
+    </row>
+    <row r="795">
+      <c r="A795" s="2" t="n"/>
+      <c r="B795" s="2" t="n"/>
+      <c r="C795" s="2" t="n"/>
+      <c r="D795" s="2" t="n"/>
+      <c r="E795" s="2" t="n"/>
+      <c r="F795" s="2" t="n"/>
+      <c r="G795" s="2" t="n"/>
+      <c r="H795" s="2" t="n"/>
+      <c r="I795" s="2" t="n"/>
+      <c r="J795" s="2" t="n"/>
+    </row>
+    <row r="796">
+      <c r="A796" s="2" t="n"/>
+      <c r="B796" s="2" t="n"/>
+      <c r="C796" s="2" t="n"/>
+      <c r="D796" s="2" t="n"/>
+      <c r="E796" s="2" t="n"/>
+      <c r="F796" s="2" t="n"/>
+      <c r="G796" s="2" t="n"/>
+      <c r="H796" s="2" t="n"/>
+      <c r="I796" s="2" t="n"/>
+      <c r="J796" s="2" t="n"/>
+    </row>
+    <row r="797">
+      <c r="A797" s="2" t="n"/>
+      <c r="B797" s="2" t="n"/>
+      <c r="C797" s="2" t="n"/>
+      <c r="D797" s="2" t="n"/>
+      <c r="E797" s="2" t="n"/>
+      <c r="F797" s="2" t="n"/>
+      <c r="G797" s="2" t="n"/>
+      <c r="H797" s="2" t="n"/>
+      <c r="I797" s="2" t="n"/>
+      <c r="J797" s="2" t="n"/>
+    </row>
+    <row r="798">
+      <c r="A798" s="2" t="n"/>
+      <c r="B798" s="2" t="n"/>
+      <c r="C798" s="2" t="n"/>
+      <c r="D798" s="2" t="n"/>
+      <c r="E798" s="2" t="n"/>
+      <c r="F798" s="2" t="n"/>
+      <c r="G798" s="2" t="n"/>
+      <c r="H798" s="2" t="n"/>
+      <c r="I798" s="2" t="n"/>
+      <c r="J798" s="2" t="n"/>
+    </row>
+    <row r="799">
+      <c r="A799" s="2" t="n"/>
+      <c r="B799" s="2" t="n"/>
+      <c r="C799" s="2" t="n"/>
+      <c r="D799" s="2" t="n"/>
+      <c r="E799" s="2" t="n"/>
+      <c r="F799" s="2" t="n"/>
+      <c r="G799" s="2" t="n"/>
+      <c r="H799" s="2" t="n"/>
+      <c r="I799" s="2" t="n"/>
+      <c r="J799" s="2" t="n"/>
+    </row>
+    <row r="800">
+      <c r="A800" s="2" t="n"/>
+      <c r="B800" s="2" t="n"/>
+      <c r="C800" s="2" t="n"/>
+      <c r="D800" s="2" t="n"/>
+      <c r="E800" s="2" t="n"/>
+      <c r="F800" s="2" t="n"/>
+      <c r="G800" s="2" t="n"/>
+      <c r="H800" s="2" t="n"/>
+      <c r="I800" s="2" t="n"/>
+      <c r="J800" s="2" t="n"/>
+    </row>
+    <row r="801">
+      <c r="A801" s="2" t="n"/>
+      <c r="B801" s="2" t="n"/>
+      <c r="C801" s="2" t="n"/>
+      <c r="D801" s="2" t="n"/>
+      <c r="E801" s="2" t="n"/>
+      <c r="F801" s="2" t="n"/>
+      <c r="G801" s="2" t="n"/>
+      <c r="H801" s="2" t="n"/>
+      <c r="I801" s="2" t="n"/>
+      <c r="J801" s="2" t="n"/>
+    </row>
+    <row r="802">
+      <c r="A802" s="2" t="n"/>
+      <c r="B802" s="2" t="n"/>
+      <c r="C802" s="2" t="n"/>
+      <c r="D802" s="2" t="n"/>
+      <c r="E802" s="2" t="n"/>
+      <c r="F802" s="2" t="n"/>
+      <c r="G802" s="2" t="n"/>
+      <c r="H802" s="2" t="n"/>
+      <c r="I802" s="2" t="n"/>
+      <c r="J802" s="2" t="n"/>
+    </row>
+    <row r="803">
+      <c r="A803" s="2" t="n"/>
+      <c r="B803" s="2" t="n"/>
+      <c r="C803" s="2" t="n"/>
+      <c r="D803" s="2" t="n"/>
+      <c r="E803" s="2" t="n"/>
+      <c r="F803" s="2" t="n"/>
+      <c r="G803" s="2" t="n"/>
+      <c r="H803" s="2" t="n"/>
+      <c r="I803" s="2" t="n"/>
+      <c r="J803" s="2" t="n"/>
+    </row>
+    <row r="804">
+      <c r="A804" s="2" t="n"/>
+      <c r="B804" s="2" t="n"/>
+      <c r="C804" s="2" t="n"/>
+      <c r="D804" s="2" t="n"/>
+      <c r="E804" s="2" t="n"/>
+      <c r="F804" s="2" t="n"/>
+      <c r="G804" s="2" t="n"/>
+      <c r="H804" s="2" t="n"/>
+      <c r="I804" s="2" t="n"/>
+      <c r="J804" s="2" t="n"/>
+    </row>
+    <row r="805">
+      <c r="A805" s="2" t="n"/>
+      <c r="B805" s="2" t="n"/>
+      <c r="C805" s="2" t="n"/>
+      <c r="D805" s="2" t="n"/>
+      <c r="E805" s="2" t="n"/>
+      <c r="F805" s="2" t="n"/>
+      <c r="G805" s="2" t="n"/>
+      <c r="H805" s="2" t="n"/>
+      <c r="I805" s="2" t="n"/>
+      <c r="J805" s="2" t="n"/>
+    </row>
+    <row r="806">
+      <c r="A806" s="2" t="n"/>
+      <c r="B806" s="2" t="n"/>
+      <c r="C806" s="2" t="n"/>
+      <c r="D806" s="2" t="n"/>
+      <c r="E806" s="2" t="n"/>
+      <c r="F806" s="2" t="n"/>
+      <c r="G806" s="2" t="n"/>
+      <c r="H806" s="2" t="n"/>
+      <c r="I806" s="2" t="n"/>
+      <c r="J806" s="2" t="n"/>
+    </row>
+    <row r="807">
+      <c r="A807" s="2" t="n"/>
+      <c r="B807" s="2" t="n"/>
+      <c r="C807" s="2" t="n"/>
+      <c r="D807" s="2" t="n"/>
+      <c r="E807" s="2" t="n"/>
+      <c r="F807" s="2" t="n"/>
+      <c r="G807" s="2" t="n"/>
+      <c r="H807" s="2" t="n"/>
+      <c r="I807" s="2" t="n"/>
+      <c r="J807" s="2" t="n"/>
+    </row>
+    <row r="808">
+      <c r="A808" s="2" t="n"/>
+      <c r="B808" s="2" t="n"/>
+      <c r="C808" s="2" t="n"/>
+      <c r="D808" s="2" t="n"/>
+      <c r="E808" s="2" t="n"/>
+      <c r="F808" s="2" t="n"/>
+      <c r="G808" s="2" t="n"/>
+      <c r="H808" s="2" t="n"/>
+      <c r="I808" s="2" t="n"/>
+      <c r="J808" s="2" t="n"/>
+    </row>
+    <row r="809">
+      <c r="A809" s="2" t="n"/>
+      <c r="B809" s="2" t="n"/>
+      <c r="C809" s="2" t="n"/>
+      <c r="D809" s="2" t="n"/>
+      <c r="E809" s="2" t="n"/>
+      <c r="F809" s="2" t="n"/>
+      <c r="G809" s="2" t="n"/>
+      <c r="H809" s="2" t="n"/>
+      <c r="I809" s="2" t="n"/>
+      <c r="J809" s="2" t="n"/>
+    </row>
+    <row r="810">
+      <c r="A810" s="2" t="n"/>
+      <c r="B810" s="2" t="n"/>
+      <c r="C810" s="2" t="n"/>
+      <c r="D810" s="2" t="n"/>
+      <c r="E810" s="2" t="n"/>
+      <c r="F810" s="2" t="n"/>
+      <c r="G810" s="2" t="n"/>
+      <c r="H810" s="2" t="n"/>
+      <c r="I810" s="2" t="n"/>
+      <c r="J810" s="2" t="n"/>
+    </row>
+    <row r="811">
+      <c r="A811" s="2" t="n"/>
+      <c r="B811" s="2" t="n"/>
+      <c r="C811" s="2" t="n"/>
+      <c r="D811" s="2" t="n"/>
+      <c r="E811" s="2" t="n"/>
+      <c r="F811" s="2" t="n"/>
+      <c r="G811" s="2" t="n"/>
+      <c r="H811" s="2" t="n"/>
+      <c r="I811" s="2" t="n"/>
+      <c r="J811" s="2" t="n"/>
+    </row>
+    <row r="812">
+      <c r="A812" s="2" t="n"/>
+      <c r="B812" s="2" t="n"/>
+      <c r="C812" s="2" t="n"/>
+      <c r="D812" s="2" t="n"/>
+      <c r="E812" s="2" t="n"/>
+      <c r="F812" s="2" t="n"/>
+      <c r="G812" s="2" t="n"/>
+      <c r="H812" s="2" t="n"/>
+      <c r="I812" s="2" t="n"/>
+      <c r="J812" s="2" t="n"/>
+    </row>
+    <row r="813">
+      <c r="A813" s="2" t="n"/>
+      <c r="B813" s="2" t="n"/>
+      <c r="C813" s="2" t="n"/>
+      <c r="D813" s="2" t="n"/>
+      <c r="E813" s="2" t="n"/>
+      <c r="F813" s="2" t="n"/>
+      <c r="G813" s="2" t="n"/>
+      <c r="H813" s="2" t="n"/>
+      <c r="I813" s="2" t="n"/>
+      <c r="J813" s="2" t="n"/>
+    </row>
+    <row r="814">
+      <c r="A814" s="2" t="n"/>
+      <c r="B814" s="2" t="n"/>
+      <c r="C814" s="2" t="n"/>
+      <c r="D814" s="2" t="n"/>
+      <c r="E814" s="2" t="n"/>
+      <c r="F814" s="2" t="n"/>
+      <c r="G814" s="2" t="n"/>
+      <c r="H814" s="2" t="n"/>
+      <c r="I814" s="2" t="n"/>
+      <c r="J814" s="2" t="n"/>
+    </row>
+    <row r="815">
+      <c r="A815" s="2" t="n"/>
+      <c r="B815" s="2" t="n"/>
+      <c r="C815" s="2" t="n"/>
+      <c r="D815" s="2" t="n"/>
+      <c r="E815" s="2" t="n"/>
+      <c r="F815" s="2" t="n"/>
+      <c r="G815" s="2" t="n"/>
+      <c r="H815" s="2" t="n"/>
+      <c r="I815" s="2" t="n"/>
+      <c r="J815" s="2" t="n"/>
+    </row>
+    <row r="816">
+      <c r="A816" s="2" t="n"/>
+      <c r="B816" s="2" t="n"/>
+      <c r="C816" s="2" t="n"/>
+      <c r="D816" s="2" t="n"/>
+      <c r="E816" s="2" t="n"/>
+      <c r="F816" s="2" t="n"/>
+      <c r="G816" s="2" t="n"/>
+      <c r="H816" s="2" t="n"/>
+      <c r="I816" s="2" t="n"/>
+      <c r="J816" s="2" t="n"/>
+    </row>
+    <row r="817">
+      <c r="A817" s="2" t="n"/>
+      <c r="B817" s="2" t="n"/>
+      <c r="C817" s="2" t="n"/>
+      <c r="D817" s="2" t="n"/>
+      <c r="E817" s="2" t="n"/>
+      <c r="F817" s="2" t="n"/>
+      <c r="G817" s="2" t="n"/>
+      <c r="H817" s="2" t="n"/>
+      <c r="I817" s="2" t="n"/>
+      <c r="J817" s="2" t="n"/>
+    </row>
+    <row r="818">
+      <c r="A818" s="2" t="n"/>
+      <c r="B818" s="2" t="n"/>
+      <c r="C818" s="2" t="n"/>
+      <c r="D818" s="2" t="n"/>
+      <c r="E818" s="2" t="n"/>
+      <c r="F818" s="2" t="n"/>
+      <c r="G818" s="2" t="n"/>
+      <c r="H818" s="2" t="n"/>
+      <c r="I818" s="2" t="n"/>
+      <c r="J818" s="2" t="n"/>
+    </row>
+    <row r="819">
+      <c r="A819" s="2" t="n"/>
+      <c r="B819" s="2" t="n"/>
+      <c r="C819" s="2" t="n"/>
+      <c r="D819" s="2" t="n"/>
+      <c r="E819" s="2" t="n"/>
+      <c r="F819" s="2" t="n"/>
+      <c r="G819" s="2" t="n"/>
+      <c r="H819" s="2" t="n"/>
+      <c r="I819" s="2" t="n"/>
+      <c r="J819" s="2" t="n"/>
+    </row>
+    <row r="820">
+      <c r="A820" s="2" t="n"/>
+      <c r="B820" s="2" t="n"/>
+      <c r="C820" s="2" t="n"/>
+      <c r="D820" s="2" t="n"/>
+      <c r="E820" s="2" t="n"/>
+      <c r="F820" s="2" t="n"/>
+      <c r="G820" s="2" t="n"/>
+      <c r="H820" s="2" t="n"/>
+      <c r="I820" s="2" t="n"/>
+      <c r="J820" s="2" t="n"/>
+    </row>
+    <row r="821">
+      <c r="A821" s="2" t="n"/>
+      <c r="B821" s="2" t="n"/>
+      <c r="C821" s="2" t="n"/>
+      <c r="D821" s="2" t="n"/>
+      <c r="E821" s="2" t="n"/>
+      <c r="F821" s="2" t="n"/>
+      <c r="G821" s="2" t="n"/>
+      <c r="H821" s="2" t="n"/>
+      <c r="I821" s="2" t="n"/>
+      <c r="J821" s="2" t="n"/>
+    </row>
+    <row r="822">
+      <c r="A822" s="2" t="n"/>
+      <c r="B822" s="2" t="n"/>
+      <c r="C822" s="2" t="n"/>
+      <c r="D822" s="2" t="n"/>
+      <c r="E822" s="2" t="n"/>
+      <c r="F822" s="2" t="n"/>
+      <c r="G822" s="2" t="n"/>
+      <c r="H822" s="2" t="n"/>
+      <c r="I822" s="2" t="n"/>
+      <c r="J822" s="2" t="n"/>
+    </row>
+    <row r="823">
+      <c r="A823" s="2" t="n"/>
+      <c r="B823" s="2" t="n"/>
+      <c r="C823" s="2" t="n"/>
+      <c r="D823" s="2" t="n"/>
+      <c r="E823" s="2" t="n"/>
+      <c r="F823" s="2" t="n"/>
+      <c r="G823" s="2" t="n"/>
+      <c r="H823" s="2" t="n"/>
+      <c r="I823" s="2" t="n"/>
+      <c r="J823" s="2" t="n"/>
+    </row>
+    <row r="824">
+      <c r="A824" s="2" t="n"/>
+      <c r="B824" s="2" t="n"/>
+      <c r="C824" s="2" t="n"/>
+      <c r="D824" s="2" t="n"/>
+      <c r="E824" s="2" t="n"/>
+      <c r="F824" s="2" t="n"/>
+      <c r="G824" s="2" t="n"/>
+      <c r="H824" s="2" t="n"/>
+      <c r="I824" s="2" t="n"/>
+      <c r="J824" s="2" t="n"/>
+    </row>
+    <row r="825">
+      <c r="A825" s="2" t="n"/>
+      <c r="B825" s="2" t="n"/>
+      <c r="C825" s="2" t="n"/>
+      <c r="D825" s="2" t="n"/>
+      <c r="E825" s="2" t="n"/>
+      <c r="F825" s="2" t="n"/>
+      <c r="G825" s="2" t="n"/>
+      <c r="H825" s="2" t="n"/>
+      <c r="I825" s="2" t="n"/>
+      <c r="J825" s="2" t="n"/>
+    </row>
+    <row r="826">
+      <c r="A826" s="2" t="n"/>
+      <c r="B826" s="2" t="n"/>
+      <c r="C826" s="2" t="n"/>
+      <c r="D826" s="2" t="n"/>
+      <c r="E826" s="2" t="n"/>
+      <c r="F826" s="2" t="n"/>
+      <c r="G826" s="2" t="n"/>
+      <c r="H826" s="2" t="n"/>
+      <c r="I826" s="2" t="n"/>
+      <c r="J826" s="2" t="n"/>
+    </row>
+    <row r="827">
+      <c r="A827" s="2" t="n"/>
+      <c r="B827" s="2" t="n"/>
+      <c r="C827" s="2" t="n"/>
+      <c r="D827" s="2" t="n"/>
+      <c r="E827" s="2" t="n"/>
+      <c r="F827" s="2" t="n"/>
+      <c r="G827" s="2" t="n"/>
+      <c r="H827" s="2" t="n"/>
+      <c r="I827" s="2" t="n"/>
+      <c r="J827" s="2" t="n"/>
+    </row>
+    <row r="828">
+      <c r="A828" s="2" t="n"/>
+      <c r="B828" s="2" t="n"/>
+      <c r="C828" s="2" t="n"/>
+      <c r="D828" s="2" t="n"/>
+      <c r="E828" s="2" t="n"/>
+      <c r="F828" s="2" t="n"/>
+      <c r="G828" s="2" t="n"/>
+      <c r="H828" s="2" t="n"/>
+      <c r="I828" s="2" t="n"/>
+      <c r="J828" s="2" t="n"/>
+    </row>
+    <row r="829">
+      <c r="A829" s="2" t="n"/>
+      <c r="B829" s="2" t="n"/>
+      <c r="C829" s="2" t="n"/>
+      <c r="D829" s="2" t="n"/>
+      <c r="E829" s="2" t="n"/>
+      <c r="F829" s="2" t="n"/>
+      <c r="G829" s="2" t="n"/>
+      <c r="H829" s="2" t="n"/>
+      <c r="I829" s="2" t="n"/>
+      <c r="J829" s="2" t="n"/>
+    </row>
+    <row r="830">
+      <c r="A830" s="2" t="n"/>
+      <c r="B830" s="2" t="n"/>
+      <c r="C830" s="2" t="n"/>
+      <c r="D830" s="2" t="n"/>
+      <c r="E830" s="2" t="n"/>
+      <c r="F830" s="2" t="n"/>
+      <c r="G830" s="2" t="n"/>
+      <c r="H830" s="2" t="n"/>
+      <c r="I830" s="2" t="n"/>
+      <c r="J830" s="2" t="n"/>
+    </row>
+    <row r="831">
+      <c r="A831" s="2" t="n"/>
+      <c r="B831" s="2" t="n"/>
+      <c r="C831" s="2" t="n"/>
+      <c r="D831" s="2" t="n"/>
+      <c r="E831" s="2" t="n"/>
+      <c r="F831" s="2" t="n"/>
+      <c r="G831" s="2" t="n"/>
+      <c r="H831" s="2" t="n"/>
+      <c r="I831" s="2" t="n"/>
+      <c r="J831" s="2" t="n"/>
+    </row>
+    <row r="832">
+      <c r="A832" s="2" t="n"/>
+      <c r="B832" s="2" t="n"/>
+      <c r="C832" s="2" t="n"/>
+      <c r="D832" s="2" t="n"/>
+      <c r="E832" s="2" t="n"/>
+      <c r="F832" s="2" t="n"/>
+      <c r="G832" s="2" t="n"/>
+      <c r="H832" s="2" t="n"/>
+      <c r="I832" s="2" t="n"/>
+      <c r="J832" s="2" t="n"/>
+    </row>
+    <row r="833">
+      <c r="A833" s="2" t="n"/>
+      <c r="B833" s="2" t="n"/>
+      <c r="C833" s="2" t="n"/>
+      <c r="D833" s="2" t="n"/>
+      <c r="E833" s="2" t="n"/>
+      <c r="F833" s="2" t="n"/>
+      <c r="G833" s="2" t="n"/>
+      <c r="H833" s="2" t="n"/>
+      <c r="I833" s="2" t="n"/>
+      <c r="J833" s="2" t="n"/>
+    </row>
+    <row r="834">
+      <c r="A834" s="2" t="n"/>
+      <c r="B834" s="2" t="n"/>
+      <c r="C834" s="2" t="n"/>
+      <c r="D834" s="2" t="n"/>
+      <c r="E834" s="2" t="n"/>
+      <c r="F834" s="2" t="n"/>
+      <c r="G834" s="2" t="n"/>
+      <c r="H834" s="2" t="n"/>
+      <c r="I834" s="2" t="n"/>
+      <c r="J834" s="2" t="n"/>
+    </row>
+    <row r="835">
+      <c r="A835" s="2" t="n"/>
+      <c r="B835" s="2" t="n"/>
+      <c r="C835" s="2" t="n"/>
+      <c r="D835" s="2" t="n"/>
+      <c r="E835" s="2" t="n"/>
+      <c r="F835" s="2" t="n"/>
+      <c r="G835" s="2" t="n"/>
+      <c r="H835" s="2" t="n"/>
+      <c r="I835" s="2" t="n"/>
+      <c r="J835" s="2" t="n"/>
+    </row>
+    <row r="836">
+      <c r="A836" s="2" t="n"/>
+      <c r="B836" s="2" t="n"/>
+      <c r="C836" s="2" t="n"/>
+      <c r="D836" s="2" t="n"/>
+      <c r="E836" s="2" t="n"/>
+      <c r="F836" s="2" t="n"/>
+      <c r="G836" s="2" t="n"/>
+      <c r="H836" s="2" t="n"/>
+      <c r="I836" s="2" t="n"/>
+      <c r="J836" s="2" t="n"/>
+    </row>
+    <row r="837">
+      <c r="A837" s="2" t="n"/>
+      <c r="B837" s="2" t="n"/>
+      <c r="C837" s="2" t="n"/>
+      <c r="D837" s="2" t="n"/>
+      <c r="E837" s="2" t="n"/>
+      <c r="F837" s="2" t="n"/>
+      <c r="G837" s="2" t="n"/>
+      <c r="H837" s="2" t="n"/>
+      <c r="I837" s="2" t="n"/>
+      <c r="J837" s="2" t="n"/>
+    </row>
+    <row r="838">
+      <c r="A838" s="2" t="n"/>
+      <c r="B838" s="2" t="n"/>
+      <c r="C838" s="2" t="n"/>
+      <c r="D838" s="2" t="n"/>
+      <c r="E838" s="2" t="n"/>
+      <c r="F838" s="2" t="n"/>
+      <c r="G838" s="2" t="n"/>
+      <c r="H838" s="2" t="n"/>
+      <c r="I838" s="2" t="n"/>
+      <c r="J838" s="2" t="n"/>
+    </row>
+    <row r="839">
+      <c r="A839" s="2" t="n"/>
+      <c r="B839" s="2" t="n"/>
+      <c r="C839" s="2" t="n"/>
+      <c r="D839" s="2" t="n"/>
+      <c r="E839" s="2" t="n"/>
+      <c r="F839" s="2" t="n"/>
+      <c r="G839" s="2" t="n"/>
+      <c r="H839" s="2" t="n"/>
+      <c r="I839" s="2" t="n"/>
+      <c r="J839" s="2" t="n"/>
+    </row>
+    <row r="840">
+      <c r="A840" s="2" t="n"/>
+      <c r="B840" s="2" t="n"/>
+      <c r="C840" s="2" t="n"/>
+      <c r="D840" s="2" t="n"/>
+      <c r="E840" s="2" t="n"/>
+      <c r="F840" s="2" t="n"/>
+      <c r="G840" s="2" t="n"/>
+      <c r="H840" s="2" t="n"/>
+      <c r="I840" s="2" t="n"/>
+      <c r="J840" s="2" t="n"/>
+    </row>
+    <row r="841">
+      <c r="A841" s="2" t="n"/>
+      <c r="B841" s="2" t="n"/>
+      <c r="C841" s="2" t="n"/>
+      <c r="D841" s="2" t="n"/>
+      <c r="E841" s="2" t="n"/>
+      <c r="F841" s="2" t="n"/>
+      <c r="G841" s="2" t="n"/>
+      <c r="H841" s="2" t="n"/>
+      <c r="I841" s="2" t="n"/>
+      <c r="J841" s="2" t="n"/>
+    </row>
+    <row r="842">
+      <c r="A842" s="2" t="n"/>
+      <c r="B842" s="2" t="n"/>
+      <c r="C842" s="2" t="n"/>
+      <c r="D842" s="2" t="n"/>
+      <c r="E842" s="2" t="n"/>
+      <c r="F842" s="2" t="n"/>
+      <c r="G842" s="2" t="n"/>
+      <c r="H842" s="2" t="n"/>
+      <c r="I842" s="2" t="n"/>
+      <c r="J842" s="2" t="n"/>
+    </row>
+    <row r="843">
+      <c r="A843" s="2" t="n"/>
+      <c r="B843" s="2" t="n"/>
+      <c r="C843" s="2" t="n"/>
+      <c r="D843" s="2" t="n"/>
+      <c r="E843" s="2" t="n"/>
+      <c r="F843" s="2" t="n"/>
+      <c r="G843" s="2" t="n"/>
+      <c r="H843" s="2" t="n"/>
+      <c r="I843" s="2" t="n"/>
+      <c r="J843" s="2" t="n"/>
+    </row>
+    <row r="844">
+      <c r="A844" s="2" t="n"/>
+      <c r="B844" s="2" t="n"/>
+      <c r="C844" s="2" t="n"/>
+      <c r="D844" s="2" t="n"/>
+      <c r="E844" s="2" t="n"/>
+      <c r="F844" s="2" t="n"/>
+      <c r="G844" s="2" t="n"/>
+      <c r="H844" s="2" t="n"/>
+      <c r="I844" s="2" t="n"/>
+      <c r="J844" s="2" t="n"/>
+    </row>
+    <row r="845">
+      <c r="A845" s="2" t="n"/>
+      <c r="B845" s="2" t="n"/>
+      <c r="C845" s="2" t="n"/>
+      <c r="D845" s="2" t="n"/>
+      <c r="E845" s="2" t="n"/>
+      <c r="F845" s="2" t="n"/>
+      <c r="G845" s="2" t="n"/>
+      <c r="H845" s="2" t="n"/>
+      <c r="I845" s="2" t="n"/>
+      <c r="J845" s="2" t="n"/>
+    </row>
+    <row r="846">
+      <c r="A846" s="2" t="n"/>
+      <c r="B846" s="2" t="n"/>
+      <c r="C846" s="2" t="n"/>
+      <c r="D846" s="2" t="n"/>
+      <c r="E846" s="2" t="n"/>
+      <c r="F846" s="2" t="n"/>
+      <c r="G846" s="2" t="n"/>
+      <c r="H846" s="2" t="n"/>
+      <c r="I846" s="2" t="n"/>
+      <c r="J846" s="2" t="n"/>
+    </row>
+    <row r="847">
+      <c r="A847" s="2" t="n"/>
+      <c r="B847" s="2" t="n"/>
+      <c r="C847" s="2" t="n"/>
+      <c r="D847" s="2" t="n"/>
+      <c r="E847" s="2" t="n"/>
+      <c r="F847" s="2" t="n"/>
+      <c r="G847" s="2" t="n"/>
+      <c r="H847" s="2" t="n"/>
+      <c r="I847" s="2" t="n"/>
+      <c r="J847" s="2" t="n"/>
+    </row>
+    <row r="848">
+      <c r="A848" s="2" t="n"/>
+      <c r="B848" s="2" t="n"/>
+      <c r="C848" s="2" t="n"/>
+      <c r="D848" s="2" t="n"/>
+      <c r="E848" s="2" t="n"/>
+      <c r="F848" s="2" t="n"/>
+      <c r="G848" s="2" t="n"/>
+      <c r="H848" s="2" t="n"/>
+      <c r="I848" s="2" t="n"/>
+      <c r="J848" s="2" t="n"/>
+    </row>
+    <row r="849">
+      <c r="A849" s="2" t="n"/>
+      <c r="B849" s="2" t="n"/>
+      <c r="C849" s="2" t="n"/>
+      <c r="D849" s="2" t="n"/>
+      <c r="E849" s="2" t="n"/>
+      <c r="F849" s="2" t="n"/>
+      <c r="G849" s="2" t="n"/>
+      <c r="H849" s="2" t="n"/>
+      <c r="I849" s="2" t="n"/>
+      <c r="J849" s="2" t="n"/>
+    </row>
+    <row r="850">
+      <c r="A850" s="2" t="n"/>
+      <c r="B850" s="2" t="n"/>
+      <c r="C850" s="2" t="n"/>
+      <c r="D850" s="2" t="n"/>
+      <c r="E850" s="2" t="n"/>
+      <c r="F850" s="2" t="n"/>
+      <c r="G850" s="2" t="n"/>
+      <c r="H850" s="2" t="n"/>
+      <c r="I850" s="2" t="n"/>
+      <c r="J850" s="2" t="n"/>
+    </row>
+    <row r="851">
+      <c r="A851" s="2" t="n"/>
+      <c r="B851" s="2" t="n"/>
+      <c r="C851" s="2" t="n"/>
+      <c r="D851" s="2" t="n"/>
+      <c r="E851" s="2" t="n"/>
+      <c r="F851" s="2" t="n"/>
+      <c r="G851" s="2" t="n"/>
+      <c r="H851" s="2" t="n"/>
+      <c r="I851" s="2" t="n"/>
+      <c r="J851" s="2" t="n"/>
+    </row>
+    <row r="852">
+      <c r="A852" s="2" t="n"/>
+      <c r="B852" s="2" t="n"/>
+      <c r="C852" s="2" t="n"/>
+      <c r="D852" s="2" t="n"/>
+      <c r="E852" s="2" t="n"/>
+      <c r="F852" s="2" t="n"/>
+      <c r="G852" s="2" t="n"/>
+      <c r="H852" s="2" t="n"/>
+      <c r="I852" s="2" t="n"/>
+      <c r="J852" s="2" t="n"/>
+    </row>
+    <row r="853">
+      <c r="A853" s="2" t="n"/>
+      <c r="B853" s="2" t="n"/>
+      <c r="C853" s="2" t="n"/>
+      <c r="D853" s="2" t="n"/>
+      <c r="E853" s="2" t="n"/>
+      <c r="F853" s="2" t="n"/>
+      <c r="G853" s="2" t="n"/>
+      <c r="H853" s="2" t="n"/>
+      <c r="I853" s="2" t="n"/>
+      <c r="J853" s="2" t="n"/>
+    </row>
+    <row r="854">
+      <c r="A854" s="2" t="n"/>
+      <c r="B854" s="2" t="n"/>
+      <c r="C854" s="2" t="n"/>
+      <c r="D854" s="2" t="n"/>
+      <c r="E854" s="2" t="n"/>
+      <c r="F854" s="2" t="n"/>
+      <c r="G854" s="2" t="n"/>
+      <c r="H854" s="2" t="n"/>
+      <c r="I854" s="2" t="n"/>
+      <c r="J854" s="2" t="n"/>
+    </row>
+    <row r="855">
+      <c r="A855" s="2" t="n"/>
+      <c r="B855" s="2" t="n"/>
+      <c r="C855" s="2" t="n"/>
+      <c r="D855" s="2" t="n"/>
+      <c r="E855" s="2" t="n"/>
+      <c r="F855" s="2" t="n"/>
+      <c r="G855" s="2" t="n"/>
+      <c r="H855" s="2" t="n"/>
+      <c r="I855" s="2" t="n"/>
+      <c r="J855" s="2" t="n"/>
+    </row>
+    <row r="856">
+      <c r="A856" s="2" t="n"/>
+      <c r="B856" s="2" t="n"/>
+      <c r="C856" s="2" t="n"/>
+      <c r="D856" s="2" t="n"/>
+      <c r="E856" s="2" t="n"/>
+      <c r="F856" s="2" t="n"/>
+      <c r="G856" s="2" t="n"/>
+      <c r="H856" s="2" t="n"/>
+      <c r="I856" s="2" t="n"/>
+      <c r="J856" s="2" t="n"/>
+    </row>
+    <row r="857">
+      <c r="A857" s="2" t="n"/>
+      <c r="B857" s="2" t="n"/>
+      <c r="C857" s="2" t="n"/>
+      <c r="D857" s="2" t="n"/>
+      <c r="E857" s="2" t="n"/>
+      <c r="F857" s="2" t="n"/>
+      <c r="G857" s="2" t="n"/>
+      <c r="H857" s="2" t="n"/>
+      <c r="I857" s="2" t="n"/>
+      <c r="J857" s="2" t="n"/>
+    </row>
+    <row r="858">
+      <c r="A858" s="2" t="n"/>
+      <c r="B858" s="2" t="n"/>
+      <c r="C858" s="2" t="n"/>
+      <c r="D858" s="2" t="n"/>
+      <c r="E858" s="2" t="n"/>
+      <c r="F858" s="2" t="n"/>
+      <c r="G858" s="2" t="n"/>
+      <c r="H858" s="2" t="n"/>
+      <c r="I858" s="2" t="n"/>
+      <c r="J858" s="2" t="n"/>
+    </row>
+    <row r="859">
+      <c r="A859" s="2" t="n"/>
+      <c r="B859" s="2" t="n"/>
+      <c r="C859" s="2" t="n"/>
+      <c r="D859" s="2" t="n"/>
+      <c r="E859" s="2" t="n"/>
+      <c r="F859" s="2" t="n"/>
+      <c r="G859" s="2" t="n"/>
+      <c r="H859" s="2" t="n"/>
+      <c r="I859" s="2" t="n"/>
+      <c r="J859" s="2" t="n"/>
+    </row>
+    <row r="860">
+      <c r="A860" s="2" t="n"/>
+      <c r="B860" s="2" t="n"/>
+      <c r="C860" s="2" t="n"/>
+      <c r="D860" s="2" t="n"/>
+      <c r="E860" s="2" t="n"/>
+      <c r="F860" s="2" t="n"/>
+      <c r="G860" s="2" t="n"/>
+      <c r="H860" s="2" t="n"/>
+      <c r="I860" s="2" t="n"/>
+      <c r="J860" s="2" t="n"/>
+    </row>
+    <row r="861">
+      <c r="A861" s="2" t="n"/>
+      <c r="B861" s="2" t="n"/>
+      <c r="C861" s="2" t="n"/>
+      <c r="D861" s="2" t="n"/>
+      <c r="E861" s="2" t="n"/>
+      <c r="F861" s="2" t="n"/>
+      <c r="G861" s="2" t="n"/>
+      <c r="H861" s="2" t="n"/>
+      <c r="I861" s="2" t="n"/>
+      <c r="J861" s="2" t="n"/>
+    </row>
+    <row r="862">
+      <c r="A862" s="2" t="n"/>
+      <c r="B862" s="2" t="n"/>
+      <c r="C862" s="2" t="n"/>
+      <c r="D862" s="2" t="n"/>
+      <c r="E862" s="2" t="n"/>
+      <c r="F862" s="2" t="n"/>
+      <c r="G862" s="2" t="n"/>
+      <c r="H862" s="2" t="n"/>
+      <c r="I862" s="2" t="n"/>
+      <c r="J862" s="2" t="n"/>
+    </row>
+    <row r="863">
+      <c r="A863" s="2" t="n"/>
+      <c r="B863" s="2" t="n"/>
+      <c r="C863" s="2" t="n"/>
+      <c r="D863" s="2" t="n"/>
+      <c r="E863" s="2" t="n"/>
+      <c r="F863" s="2" t="n"/>
+      <c r="G863" s="2" t="n"/>
+      <c r="H863" s="2" t="n"/>
+      <c r="I863" s="2" t="n"/>
+      <c r="J863" s="2" t="n"/>
+    </row>
+    <row r="864">
+      <c r="A864" s="2" t="n"/>
+      <c r="B864" s="2" t="n"/>
+      <c r="C864" s="2" t="n"/>
+      <c r="D864" s="2" t="n"/>
+      <c r="E864" s="2" t="n"/>
+      <c r="F864" s="2" t="n"/>
+      <c r="G864" s="2" t="n"/>
+      <c r="H864" s="2" t="n"/>
+      <c r="I864" s="2" t="n"/>
+      <c r="J864" s="2" t="n"/>
+    </row>
+    <row r="865">
+      <c r="A865" s="2" t="n"/>
+      <c r="B865" s="2" t="n"/>
+      <c r="C865" s="2" t="n"/>
+      <c r="D865" s="2" t="n"/>
+      <c r="E865" s="2" t="n"/>
+      <c r="F865" s="2" t="n"/>
+      <c r="G865" s="2" t="n"/>
+      <c r="H865" s="2" t="n"/>
+      <c r="I865" s="2" t="n"/>
+      <c r="J865" s="2" t="n"/>
+    </row>
+    <row r="866">
+      <c r="A866" s="2" t="n"/>
+      <c r="B866" s="2" t="n"/>
+      <c r="C866" s="2" t="n"/>
+      <c r="D866" s="2" t="n"/>
+      <c r="E866" s="2" t="n"/>
+      <c r="F866" s="2" t="n"/>
+      <c r="G866" s="2" t="n"/>
+      <c r="H866" s="2" t="n"/>
+      <c r="I866" s="2" t="n"/>
+      <c r="J866" s="2" t="n"/>
+    </row>
+    <row r="867">
+      <c r="A867" s="2" t="n"/>
+      <c r="B867" s="2" t="n"/>
+      <c r="C867" s="2" t="n"/>
+      <c r="D867" s="2" t="n"/>
+      <c r="E867" s="2" t="n"/>
+      <c r="F867" s="2" t="n"/>
+      <c r="G867" s="2" t="n"/>
+      <c r="H867" s="2" t="n"/>
+      <c r="I867" s="2" t="n"/>
+      <c r="J867" s="2" t="n"/>
+    </row>
+    <row r="868">
+      <c r="A868" s="2" t="n"/>
+      <c r="B868" s="2" t="n"/>
+      <c r="C868" s="2" t="n"/>
+      <c r="D868" s="2" t="n"/>
+      <c r="E868" s="2" t="n"/>
+      <c r="F868" s="2" t="n"/>
+      <c r="G868" s="2" t="n"/>
+      <c r="H868" s="2" t="n"/>
+      <c r="I868" s="2" t="n"/>
+      <c r="J868" s="2" t="n"/>
+    </row>
+    <row r="869">
+      <c r="A869" s="2" t="n"/>
+      <c r="B869" s="2" t="n"/>
+      <c r="C869" s="2" t="n"/>
+      <c r="D869" s="2" t="n"/>
+      <c r="E869" s="2" t="n"/>
+      <c r="F869" s="2" t="n"/>
+      <c r="G869" s="2" t="n"/>
+      <c r="H869" s="2" t="n"/>
+      <c r="I869" s="2" t="n"/>
+      <c r="J869" s="2" t="n"/>
+    </row>
+    <row r="870">
+      <c r="A870" s="2" t="n"/>
+      <c r="B870" s="2" t="n"/>
+      <c r="C870" s="2" t="n"/>
+      <c r="D870" s="2" t="n"/>
+      <c r="E870" s="2" t="n"/>
+      <c r="F870" s="2" t="n"/>
+      <c r="G870" s="2" t="n"/>
+      <c r="H870" s="2" t="n"/>
+      <c r="I870" s="2" t="n"/>
+      <c r="J870" s="2" t="n"/>
+    </row>
+    <row r="871">
+      <c r="A871" s="2" t="n"/>
+      <c r="B871" s="2" t="n"/>
+      <c r="C871" s="2" t="n"/>
+      <c r="D871" s="2" t="n"/>
+      <c r="E871" s="2" t="n"/>
+      <c r="F871" s="2" t="n"/>
+      <c r="G871" s="2" t="n"/>
+      <c r="H871" s="2" t="n"/>
+      <c r="I871" s="2" t="n"/>
+      <c r="J871" s="2" t="n"/>
+    </row>
+    <row r="872">
+      <c r="A872" s="2" t="n"/>
+      <c r="B872" s="2" t="n"/>
+      <c r="C872" s="2" t="n"/>
+      <c r="D872" s="2" t="n"/>
+      <c r="E872" s="2" t="n"/>
+      <c r="F872" s="2" t="n"/>
+      <c r="G872" s="2" t="n"/>
+      <c r="H872" s="2" t="n"/>
+      <c r="I872" s="2" t="n"/>
+      <c r="J872" s="2" t="n"/>
+    </row>
+    <row r="873">
+      <c r="A873" s="2" t="n"/>
+      <c r="B873" s="2" t="n"/>
+      <c r="C873" s="2" t="n"/>
+      <c r="D873" s="2" t="n"/>
+      <c r="E873" s="2" t="n"/>
+      <c r="F873" s="2" t="n"/>
+      <c r="G873" s="2" t="n"/>
+      <c r="H873" s="2" t="n"/>
+      <c r="I873" s="2" t="n"/>
+      <c r="J873" s="2" t="n"/>
+    </row>
+    <row r="874">
+      <c r="A874" s="2" t="n"/>
+      <c r="B874" s="2" t="n"/>
+      <c r="C874" s="2" t="n"/>
+      <c r="D874" s="2" t="n"/>
+      <c r="E874" s="2" t="n"/>
+      <c r="F874" s="2" t="n"/>
+      <c r="G874" s="2" t="n"/>
+      <c r="H874" s="2" t="n"/>
+      <c r="I874" s="2" t="n"/>
+      <c r="J874" s="2" t="n"/>
+    </row>
+    <row r="875">
+      <c r="A875" s="2" t="n"/>
+      <c r="B875" s="2" t="n"/>
+      <c r="C875" s="2" t="n"/>
+      <c r="D875" s="2" t="n"/>
+      <c r="E875" s="2" t="n"/>
+      <c r="F875" s="2" t="n"/>
+      <c r="G875" s="2" t="n"/>
+      <c r="H875" s="2" t="n"/>
+      <c r="I875" s="2" t="n"/>
+      <c r="J875" s="2" t="n"/>
+    </row>
+    <row r="876">
+      <c r="A876" s="2" t="n"/>
+      <c r="B876" s="2" t="n"/>
+      <c r="C876" s="2" t="n"/>
+      <c r="D876" s="2" t="n"/>
+      <c r="E876" s="2" t="n"/>
+      <c r="F876" s="2" t="n"/>
+      <c r="G876" s="2" t="n"/>
+      <c r="H876" s="2" t="n"/>
+      <c r="I876" s="2" t="n"/>
+      <c r="J876" s="2" t="n"/>
+    </row>
+    <row r="877">
+      <c r="A877" s="2" t="n"/>
+      <c r="B877" s="2" t="n"/>
+      <c r="C877" s="2" t="n"/>
+      <c r="D877" s="2" t="n"/>
+      <c r="E877" s="2" t="n"/>
+      <c r="F877" s="2" t="n"/>
+      <c r="G877" s="2" t="n"/>
+      <c r="H877" s="2" t="n"/>
+      <c r="I877" s="2" t="n"/>
+      <c r="J877" s="2" t="n"/>
+    </row>
+    <row r="878">
+      <c r="A878" s="2" t="n"/>
+      <c r="B878" s="2" t="n"/>
+      <c r="C878" s="2" t="n"/>
+      <c r="D878" s="2" t="n"/>
+      <c r="E878" s="2" t="n"/>
+      <c r="F878" s="2" t="n"/>
+      <c r="G878" s="2" t="n"/>
+      <c r="H878" s="2" t="n"/>
+      <c r="I878" s="2" t="n"/>
+      <c r="J878" s="2" t="n"/>
+    </row>
+    <row r="879">
+      <c r="A879" s="2" t="n"/>
+      <c r="B879" s="2" t="n"/>
+      <c r="C879" s="2" t="n"/>
+      <c r="D879" s="2" t="n"/>
+      <c r="E879" s="2" t="n"/>
+      <c r="F879" s="2" t="n"/>
+      <c r="G879" s="2" t="n"/>
+      <c r="H879" s="2" t="n"/>
+      <c r="I879" s="2" t="n"/>
+      <c r="J879" s="2" t="n"/>
+    </row>
+    <row r="880">
+      <c r="A880" s="2" t="n"/>
+      <c r="B880" s="2" t="n"/>
+      <c r="C880" s="2" t="n"/>
+      <c r="D880" s="2" t="n"/>
+      <c r="E880" s="2" t="n"/>
+      <c r="F880" s="2" t="n"/>
+      <c r="G880" s="2" t="n"/>
+      <c r="H880" s="2" t="n"/>
+      <c r="I880" s="2" t="n"/>
+      <c r="J880" s="2" t="n"/>
+    </row>
+    <row r="881">
+      <c r="A881" s="2" t="n"/>
+      <c r="B881" s="2" t="n"/>
+      <c r="C881" s="2" t="n"/>
+      <c r="D881" s="2" t="n"/>
+      <c r="E881" s="2" t="n"/>
+      <c r="F881" s="2" t="n"/>
+      <c r="G881" s="2" t="n"/>
+      <c r="H881" s="2" t="n"/>
+      <c r="I881" s="2" t="n"/>
+      <c r="J881" s="2" t="n"/>
+    </row>
+    <row r="882">
+      <c r="A882" s="2" t="n"/>
+      <c r="B882" s="2" t="n"/>
+      <c r="C882" s="2" t="n"/>
+      <c r="D882" s="2" t="n"/>
+      <c r="E882" s="2" t="n"/>
+      <c r="F882" s="2" t="n"/>
+      <c r="G882" s="2" t="n"/>
+      <c r="H882" s="2" t="n"/>
+      <c r="I882" s="2" t="n"/>
+      <c r="J882" s="2" t="n"/>
+    </row>
+    <row r="883">
+      <c r="A883" s="2" t="n"/>
+      <c r="B883" s="2" t="n"/>
+      <c r="C883" s="2" t="n"/>
+      <c r="D883" s="2" t="n"/>
+      <c r="E883" s="2" t="n"/>
+      <c r="F883" s="2" t="n"/>
+      <c r="G883" s="2" t="n"/>
+      <c r="H883" s="2" t="n"/>
+      <c r="I883" s="2" t="n"/>
+      <c r="J883" s="2" t="n"/>
+    </row>
+    <row r="884">
+      <c r="A884" s="2" t="n"/>
+      <c r="B884" s="2" t="n"/>
+      <c r="C884" s="2" t="n"/>
+      <c r="D884" s="2" t="n"/>
+      <c r="E884" s="2" t="n"/>
+      <c r="F884" s="2" t="n"/>
+      <c r="G884" s="2" t="n"/>
+      <c r="H884" s="2" t="n"/>
+      <c r="I884" s="2" t="n"/>
+      <c r="J884" s="2" t="n"/>
+    </row>
+    <row r="885">
+      <c r="A885" s="2" t="n"/>
+      <c r="B885" s="2" t="n"/>
+      <c r="C885" s="2" t="n"/>
+      <c r="D885" s="2" t="n"/>
+      <c r="E885" s="2" t="n"/>
+      <c r="F885" s="2" t="n"/>
+      <c r="G885" s="2" t="n"/>
+      <c r="H885" s="2" t="n"/>
+      <c r="I885" s="2" t="n"/>
+      <c r="J885" s="2" t="n"/>
+    </row>
+    <row r="886">
+      <c r="A886" s="2" t="n"/>
+      <c r="B886" s="2" t="n"/>
+      <c r="C886" s="2" t="n"/>
+      <c r="D886" s="2" t="n"/>
+      <c r="E886" s="2" t="n"/>
+      <c r="F886" s="2" t="n"/>
+      <c r="G886" s="2" t="n"/>
+      <c r="H886" s="2" t="n"/>
+      <c r="I886" s="2" t="n"/>
+      <c r="J886" s="2" t="n"/>
+    </row>
+    <row r="887">
+      <c r="A887" s="2" t="n"/>
+      <c r="B887" s="2" t="n"/>
+      <c r="C887" s="2" t="n"/>
+      <c r="D887" s="2" t="n"/>
+      <c r="E887" s="2" t="n"/>
+      <c r="F887" s="2" t="n"/>
+      <c r="G887" s="2" t="n"/>
+      <c r="H887" s="2" t="n"/>
+      <c r="I887" s="2" t="n"/>
+      <c r="J887" s="2" t="n"/>
+    </row>
+    <row r="888">
+      <c r="A888" s="2" t="n"/>
+      <c r="B888" s="2" t="n"/>
+      <c r="C888" s="2" t="n"/>
+      <c r="D888" s="2" t="n"/>
+      <c r="E888" s="2" t="n"/>
+      <c r="F888" s="2" t="n"/>
+      <c r="G888" s="2" t="n"/>
+      <c r="H888" s="2" t="n"/>
+      <c r="I888" s="2" t="n"/>
+      <c r="J888" s="2" t="n"/>
+    </row>
+    <row r="889">
+      <c r="A889" s="2" t="n"/>
+      <c r="B889" s="2" t="n"/>
+      <c r="C889" s="2" t="n"/>
+      <c r="D889" s="2" t="n"/>
+      <c r="E889" s="2" t="n"/>
+      <c r="F889" s="2" t="n"/>
+      <c r="G889" s="2" t="n"/>
+      <c r="H889" s="2" t="n"/>
+      <c r="I889" s="2" t="n"/>
+      <c r="J889" s="2" t="n"/>
+    </row>
+    <row r="890">
+      <c r="A890" s="2" t="n"/>
+      <c r="B890" s="2" t="n"/>
+      <c r="C890" s="2" t="n"/>
+      <c r="D890" s="2" t="n"/>
+      <c r="E890" s="2" t="n"/>
+      <c r="F890" s="2" t="n"/>
+      <c r="G890" s="2" t="n"/>
+      <c r="H890" s="2" t="n"/>
+      <c r="I890" s="2" t="n"/>
+      <c r="J890" s="2" t="n"/>
+    </row>
+    <row r="891">
+      <c r="A891" s="2" t="n"/>
+      <c r="B891" s="2" t="n"/>
+      <c r="C891" s="2" t="n"/>
+      <c r="D891" s="2" t="n"/>
+      <c r="E891" s="2" t="n"/>
+      <c r="F891" s="2" t="n"/>
+      <c r="G891" s="2" t="n"/>
+      <c r="H891" s="2" t="n"/>
+      <c r="I891" s="2" t="n"/>
+      <c r="J891" s="2" t="n"/>
+    </row>
+    <row r="892">
+      <c r="A892" s="2" t="n"/>
+      <c r="B892" s="2" t="n"/>
+      <c r="C892" s="2" t="n"/>
+      <c r="D892" s="2" t="n"/>
+      <c r="E892" s="2" t="n"/>
+      <c r="F892" s="2" t="n"/>
+      <c r="G892" s="2" t="n"/>
+      <c r="H892" s="2" t="n"/>
+      <c r="I892" s="2" t="n"/>
+      <c r="J892" s="2" t="n"/>
+    </row>
+    <row r="893">
+      <c r="A893" s="2" t="n"/>
+      <c r="B893" s="2" t="n"/>
+      <c r="C893" s="2" t="n"/>
+      <c r="D893" s="2" t="n"/>
+      <c r="E893" s="2" t="n"/>
+      <c r="F893" s="2" t="n"/>
+      <c r="G893" s="2" t="n"/>
+      <c r="H893" s="2" t="n"/>
+      <c r="I893" s="2" t="n"/>
+      <c r="J893" s="2" t="n"/>
+    </row>
+    <row r="894">
+      <c r="A894" s="2" t="n"/>
+      <c r="B894" s="2" t="n"/>
+      <c r="C894" s="2" t="n"/>
+      <c r="D894" s="2" t="n"/>
+      <c r="E894" s="2" t="n"/>
+      <c r="F894" s="2" t="n"/>
+      <c r="G894" s="2" t="n"/>
+      <c r="H894" s="2" t="n"/>
+      <c r="I894" s="2" t="n"/>
+      <c r="J894" s="2" t="n"/>
+    </row>
+    <row r="895">
+      <c r="A895" s="2" t="n"/>
+      <c r="B895" s="2" t="n"/>
+      <c r="C895" s="2" t="n"/>
+      <c r="D895" s="2" t="n"/>
+      <c r="E895" s="2" t="n"/>
+      <c r="F895" s="2" t="n"/>
+      <c r="G895" s="2" t="n"/>
+      <c r="H895" s="2" t="n"/>
+      <c r="I895" s="2" t="n"/>
+      <c r="J895" s="2" t="n"/>
+    </row>
+    <row r="896">
+      <c r="A896" s="2" t="n"/>
+      <c r="B896" s="2" t="n"/>
+      <c r="C896" s="2" t="n"/>
+      <c r="D896" s="2" t="n"/>
+      <c r="E896" s="2" t="n"/>
+      <c r="F896" s="2" t="n"/>
+      <c r="G896" s="2" t="n"/>
+      <c r="H896" s="2" t="n"/>
+      <c r="I896" s="2" t="n"/>
+      <c r="J896" s="2" t="n"/>
+    </row>
+    <row r="897">
+      <c r="A897" s="2" t="n"/>
+      <c r="B897" s="2" t="n"/>
+      <c r="C897" s="2" t="n"/>
+      <c r="D897" s="2" t="n"/>
+      <c r="E897" s="2" t="n"/>
+      <c r="F897" s="2" t="n"/>
+      <c r="G897" s="2" t="n"/>
+      <c r="H897" s="2" t="n"/>
+      <c r="I897" s="2" t="n"/>
+      <c r="J897" s="2" t="n"/>
+    </row>
+    <row r="898">
+      <c r="A898" s="2" t="n"/>
+      <c r="B898" s="2" t="n"/>
+      <c r="C898" s="2" t="n"/>
+      <c r="D898" s="2" t="n"/>
+      <c r="E898" s="2" t="n"/>
+      <c r="F898" s="2" t="n"/>
+      <c r="G898" s="2" t="n"/>
+      <c r="H898" s="2" t="n"/>
+      <c r="I898" s="2" t="n"/>
+      <c r="J898" s="2" t="n"/>
+    </row>
+    <row r="899">
+      <c r="A899" s="2" t="n"/>
+      <c r="B899" s="2" t="n"/>
+      <c r="C899" s="2" t="n"/>
+      <c r="D899" s="2" t="n"/>
+      <c r="E899" s="2" t="n"/>
+      <c r="F899" s="2" t="n"/>
+      <c r="G899" s="2" t="n"/>
+      <c r="H899" s="2" t="n"/>
+      <c r="I899" s="2" t="n"/>
+      <c r="J899" s="2" t="n"/>
+    </row>
+    <row r="900">
+      <c r="A900" s="2" t="n"/>
+      <c r="B900" s="2" t="n"/>
+      <c r="C900" s="2" t="n"/>
+      <c r="D900" s="2" t="n"/>
+      <c r="E900" s="2" t="n"/>
+      <c r="F900" s="2" t="n"/>
+      <c r="G900" s="2" t="n"/>
+      <c r="H900" s="2" t="n"/>
+      <c r="I900" s="2" t="n"/>
+      <c r="J900" s="2" t="n"/>
+    </row>
+    <row r="901">
+      <c r="A901" s="2" t="n"/>
+      <c r="B901" s="2" t="n"/>
+      <c r="C901" s="2" t="n"/>
+      <c r="D901" s="2" t="n"/>
+      <c r="E901" s="2" t="n"/>
+      <c r="F901" s="2" t="n"/>
+      <c r="G901" s="2" t="n"/>
+      <c r="H901" s="2" t="n"/>
+      <c r="I901" s="2" t="n"/>
+      <c r="J901" s="2" t="n"/>
+    </row>
+    <row r="902">
+      <c r="A902" s="2" t="n"/>
+      <c r="B902" s="2" t="n"/>
+      <c r="C902" s="2" t="n"/>
+      <c r="D902" s="2" t="n"/>
+      <c r="E902" s="2" t="n"/>
+      <c r="F902" s="2" t="n"/>
+      <c r="G902" s="2" t="n"/>
+      <c r="H902" s="2" t="n"/>
+      <c r="I902" s="2" t="n"/>
+      <c r="J902" s="2" t="n"/>
+    </row>
+    <row r="903">
+      <c r="A903" s="2" t="n"/>
+      <c r="B903" s="2" t="n"/>
+      <c r="C903" s="2" t="n"/>
+      <c r="D903" s="2" t="n"/>
+      <c r="E903" s="2" t="n"/>
+      <c r="F903" s="2" t="n"/>
+      <c r="G903" s="2" t="n"/>
+      <c r="H903" s="2" t="n"/>
+      <c r="I903" s="2" t="n"/>
+      <c r="J903" s="2" t="n"/>
+    </row>
+    <row r="904">
+      <c r="A904" s="2" t="n"/>
+      <c r="B904" s="2" t="n"/>
+      <c r="C904" s="2" t="n"/>
+      <c r="D904" s="2" t="n"/>
+      <c r="E904" s="2" t="n"/>
+      <c r="F904" s="2" t="n"/>
+      <c r="G904" s="2" t="n"/>
+      <c r="H904" s="2" t="n"/>
+      <c r="I904" s="2" t="n"/>
+      <c r="J904" s="2" t="n"/>
+    </row>
+    <row r="905">
+      <c r="A905" s="2" t="n"/>
+      <c r="B905" s="2" t="n"/>
+      <c r="C905" s="2" t="n"/>
+      <c r="D905" s="2" t="n"/>
+      <c r="E905" s="2" t="n"/>
+      <c r="F905" s="2" t="n"/>
+      <c r="G905" s="2" t="n"/>
+      <c r="H905" s="2" t="n"/>
+      <c r="I905" s="2" t="n"/>
+      <c r="J905" s="2" t="n"/>
+    </row>
+    <row r="906">
+      <c r="A906" s="2" t="n"/>
+      <c r="B906" s="2" t="n"/>
+      <c r="C906" s="2" t="n"/>
+      <c r="D906" s="2" t="n"/>
+      <c r="E906" s="2" t="n"/>
+      <c r="F906" s="2" t="n"/>
+      <c r="G906" s="2" t="n"/>
+      <c r="H906" s="2" t="n"/>
+      <c r="I906" s="2" t="n"/>
+      <c r="J906" s="2" t="n"/>
+    </row>
+    <row r="907">
+      <c r="A907" s="2" t="n"/>
+      <c r="B907" s="2" t="n"/>
+      <c r="C907" s="2" t="n"/>
+      <c r="D907" s="2" t="n"/>
+      <c r="E907" s="2" t="n"/>
+      <c r="F907" s="2" t="n"/>
+      <c r="G907" s="2" t="n"/>
+      <c r="H907" s="2" t="n"/>
+      <c r="I907" s="2" t="n"/>
+      <c r="J907" s="2" t="n"/>
+    </row>
+    <row r="908">
+      <c r="A908" s="2" t="n"/>
+      <c r="B908" s="2" t="n"/>
+      <c r="C908" s="2" t="n"/>
+      <c r="D908" s="2" t="n"/>
+      <c r="E908" s="2" t="n"/>
+      <c r="F908" s="2" t="n"/>
+      <c r="G908" s="2" t="n"/>
+      <c r="H908" s="2" t="n"/>
+      <c r="I908" s="2" t="n"/>
+      <c r="J908" s="2" t="n"/>
+    </row>
+    <row r="909">
+      <c r="A909" s="2" t="n"/>
+      <c r="B909" s="2" t="n"/>
+      <c r="C909" s="2" t="n"/>
+      <c r="D909" s="2" t="n"/>
+      <c r="E909" s="2" t="n"/>
+      <c r="F909" s="2" t="n"/>
+      <c r="G909" s="2" t="n"/>
+      <c r="H909" s="2" t="n"/>
+      <c r="I909" s="2" t="n"/>
+      <c r="J909" s="2" t="n"/>
+    </row>
+    <row r="910">
+      <c r="A910" s="2" t="n"/>
+      <c r="B910" s="2" t="n"/>
+      <c r="C910" s="2" t="n"/>
+      <c r="D910" s="2" t="n"/>
+      <c r="E910" s="2" t="n"/>
+      <c r="F910" s="2" t="n"/>
+      <c r="G910" s="2" t="n"/>
+      <c r="H910" s="2" t="n"/>
+      <c r="I910" s="2" t="n"/>
+      <c r="J910" s="2" t="n"/>
+    </row>
+    <row r="911">
+      <c r="A911" s="2" t="n"/>
+      <c r="B911" s="2" t="n"/>
+      <c r="C911" s="2" t="n"/>
+      <c r="D911" s="2" t="n"/>
+      <c r="E911" s="2" t="n"/>
+      <c r="F911" s="2" t="n"/>
+      <c r="G911" s="2" t="n"/>
+      <c r="H911" s="2" t="n"/>
+      <c r="I911" s="2" t="n"/>
+      <c r="J911" s="2" t="n"/>
+    </row>
+    <row r="912">
+      <c r="A912" s="2" t="n"/>
+      <c r="B912" s="2" t="n"/>
+      <c r="C912" s="2" t="n"/>
+      <c r="D912" s="2" t="n"/>
+      <c r="E912" s="2" t="n"/>
+      <c r="F912" s="2" t="n"/>
+      <c r="G912" s="2" t="n"/>
+      <c r="H912" s="2" t="n"/>
+      <c r="I912" s="2" t="n"/>
+      <c r="J912" s="2" t="n"/>
+    </row>
+    <row r="913">
+      <c r="A913" s="2" t="n"/>
+      <c r="B913" s="2" t="n"/>
+      <c r="C913" s="2" t="n"/>
+      <c r="D913" s="2" t="n"/>
+      <c r="E913" s="2" t="n"/>
+      <c r="F913" s="2" t="n"/>
+      <c r="G913" s="2" t="n"/>
+      <c r="H913" s="2" t="n"/>
+      <c r="I913" s="2" t="n"/>
+      <c r="J913" s="2" t="n"/>
+    </row>
+    <row r="914">
+      <c r="A914" s="2" t="n"/>
+      <c r="B914" s="2" t="n"/>
+      <c r="C914" s="2" t="n"/>
+      <c r="D914" s="2" t="n"/>
+      <c r="E914" s="2" t="n"/>
+      <c r="F914" s="2" t="n"/>
+      <c r="G914" s="2" t="n"/>
+      <c r="H914" s="2" t="n"/>
+      <c r="I914" s="2" t="n"/>
+      <c r="J914" s="2" t="n"/>
+    </row>
+    <row r="915">
+      <c r="A915" s="2" t="n"/>
+      <c r="B915" s="2" t="n"/>
+      <c r="C915" s="2" t="n"/>
+      <c r="D915" s="2" t="n"/>
+      <c r="E915" s="2" t="n"/>
+      <c r="F915" s="2" t="n"/>
+      <c r="G915" s="2" t="n"/>
+      <c r="H915" s="2" t="n"/>
+      <c r="I915" s="2" t="n"/>
+      <c r="J915" s="2" t="n"/>
+    </row>
+    <row r="916">
+      <c r="A916" s="2" t="n"/>
+      <c r="B916" s="2" t="n"/>
+      <c r="C916" s="2" t="n"/>
+      <c r="D916" s="2" t="n"/>
+      <c r="E916" s="2" t="n"/>
+      <c r="F916" s="2" t="n"/>
+      <c r="G916" s="2" t="n"/>
+      <c r="H916" s="2" t="n"/>
+      <c r="I916" s="2" t="n"/>
+      <c r="J916" s="2" t="n"/>
+    </row>
+    <row r="917">
+      <c r="A917" s="2" t="n"/>
+      <c r="B917" s="2" t="n"/>
+      <c r="C917" s="2" t="n"/>
+      <c r="D917" s="2" t="n"/>
+      <c r="E917" s="2" t="n"/>
+      <c r="F917" s="2" t="n"/>
+      <c r="G917" s="2" t="n"/>
+      <c r="H917" s="2" t="n"/>
+      <c r="I917" s="2" t="n"/>
+      <c r="J917" s="2" t="n"/>
+    </row>
+    <row r="918">
+      <c r="A918" s="2" t="n"/>
+      <c r="B918" s="2" t="n"/>
+      <c r="C918" s="2" t="n"/>
+      <c r="D918" s="2" t="n"/>
+      <c r="E918" s="2" t="n"/>
+      <c r="F918" s="2" t="n"/>
+      <c r="G918" s="2" t="n"/>
+      <c r="H918" s="2" t="n"/>
+      <c r="I918" s="2" t="n"/>
+      <c r="J918" s="2" t="n"/>
+    </row>
+    <row r="919">
+      <c r="A919" s="2" t="n"/>
+      <c r="B919" s="2" t="n"/>
+      <c r="C919" s="2" t="n"/>
+      <c r="D919" s="2" t="n"/>
+      <c r="E919" s="2" t="n"/>
+      <c r="F919" s="2" t="n"/>
+      <c r="G919" s="2" t="n"/>
+      <c r="H919" s="2" t="n"/>
+      <c r="I919" s="2" t="n"/>
+      <c r="J919" s="2" t="n"/>
+    </row>
+    <row r="920">
+      <c r="A920" s="2" t="n"/>
+      <c r="B920" s="2" t="n"/>
+      <c r="C920" s="2" t="n"/>
+      <c r="D920" s="2" t="n"/>
+      <c r="E920" s="2" t="n"/>
+      <c r="F920" s="2" t="n"/>
+      <c r="G920" s="2" t="n"/>
+      <c r="H920" s="2" t="n"/>
+      <c r="I920" s="2" t="n"/>
+      <c r="J920" s="2" t="n"/>
+    </row>
+    <row r="921">
+      <c r="A921" s="2" t="n"/>
+      <c r="B921" s="2" t="n"/>
+      <c r="C921" s="2" t="n"/>
+      <c r="D921" s="2" t="n"/>
+      <c r="E921" s="2" t="n"/>
+      <c r="F921" s="2" t="n"/>
+      <c r="G921" s="2" t="n"/>
+      <c r="H921" s="2" t="n"/>
+      <c r="I921" s="2" t="n"/>
+      <c r="J921" s="2" t="n"/>
+    </row>
+    <row r="922">
+      <c r="A922" s="2" t="n"/>
+      <c r="B922" s="2" t="n"/>
+      <c r="C922" s="2" t="n"/>
+      <c r="D922" s="2" t="n"/>
+      <c r="E922" s="2" t="n"/>
+      <c r="F922" s="2" t="n"/>
+      <c r="G922" s="2" t="n"/>
+      <c r="H922" s="2" t="n"/>
+      <c r="I922" s="2" t="n"/>
+      <c r="J922" s="2" t="n"/>
+    </row>
+    <row r="923">
+      <c r="A923" s="2" t="n"/>
+      <c r="B923" s="2" t="n"/>
+      <c r="C923" s="2" t="n"/>
+      <c r="D923" s="2" t="n"/>
+      <c r="E923" s="2" t="n"/>
+      <c r="F923" s="2" t="n"/>
+      <c r="G923" s="2" t="n"/>
+      <c r="H923" s="2" t="n"/>
+      <c r="I923" s="2" t="n"/>
+      <c r="J923" s="2" t="n"/>
+    </row>
+    <row r="924">
+      <c r="A924" s="2" t="n"/>
+      <c r="B924" s="2" t="n"/>
+      <c r="C924" s="2" t="n"/>
+      <c r="D924" s="2" t="n"/>
+      <c r="E924" s="2" t="n"/>
+      <c r="F924" s="2" t="n"/>
+      <c r="G924" s="2" t="n"/>
+      <c r="H924" s="2" t="n"/>
+      <c r="I924" s="2" t="n"/>
+      <c r="J924" s="2" t="n"/>
+    </row>
+    <row r="925">
+      <c r="A925" s="2" t="n"/>
+      <c r="B925" s="2" t="n"/>
+      <c r="C925" s="2" t="n"/>
+      <c r="D925" s="2" t="n"/>
+      <c r="E925" s="2" t="n"/>
+      <c r="F925" s="2" t="n"/>
+      <c r="G925" s="2" t="n"/>
+      <c r="H925" s="2" t="n"/>
+      <c r="I925" s="2" t="n"/>
+      <c r="J925" s="2" t="n"/>
+    </row>
+    <row r="926">
+      <c r="A926" s="2" t="n"/>
+      <c r="B926" s="2" t="n"/>
+      <c r="C926" s="2" t="n"/>
+      <c r="D926" s="2" t="n"/>
+      <c r="E926" s="2" t="n"/>
+      <c r="F926" s="2" t="n"/>
+      <c r="G926" s="2" t="n"/>
+      <c r="H926" s="2" t="n"/>
+      <c r="I926" s="2" t="n"/>
+      <c r="J926" s="2" t="n"/>
+    </row>
+    <row r="927">
+      <c r="A927" s="2" t="n"/>
+      <c r="B927" s="2" t="n"/>
+      <c r="C927" s="2" t="n"/>
+      <c r="D927" s="2" t="n"/>
+      <c r="E927" s="2" t="n"/>
+      <c r="F927" s="2" t="n"/>
+      <c r="G927" s="2" t="n"/>
+      <c r="H927" s="2" t="n"/>
+      <c r="I927" s="2" t="n"/>
+      <c r="J927" s="2" t="n"/>
+    </row>
+    <row r="928">
+      <c r="A928" s="2" t="n"/>
+      <c r="B928" s="2" t="n"/>
+      <c r="C928" s="2" t="n"/>
+      <c r="D928" s="2" t="n"/>
+      <c r="E928" s="2" t="n"/>
+      <c r="F928" s="2" t="n"/>
+      <c r="G928" s="2" t="n"/>
+      <c r="H928" s="2" t="n"/>
+      <c r="I928" s="2" t="n"/>
+      <c r="J928" s="2" t="n"/>
+    </row>
+    <row r="929">
+      <c r="A929" s="2" t="n"/>
+      <c r="B929" s="2" t="n"/>
+      <c r="C929" s="2" t="n"/>
+      <c r="D929" s="2" t="n"/>
+      <c r="E929" s="2" t="n"/>
+      <c r="F929" s="2" t="n"/>
+      <c r="G929" s="2" t="n"/>
+      <c r="H929" s="2" t="n"/>
+      <c r="I929" s="2" t="n"/>
+      <c r="J929" s="2" t="n"/>
+    </row>
+    <row r="930">
+      <c r="A930" s="2" t="n"/>
+      <c r="B930" s="2" t="n"/>
+      <c r="C930" s="2" t="n"/>
+      <c r="D930" s="2" t="n"/>
+      <c r="E930" s="2" t="n"/>
+      <c r="F930" s="2" t="n"/>
+      <c r="G930" s="2" t="n"/>
+      <c r="H930" s="2" t="n"/>
+      <c r="I930" s="2" t="n"/>
+      <c r="J930" s="2" t="n"/>
+    </row>
+    <row r="931">
+      <c r="A931" s="2" t="n"/>
+      <c r="B931" s="2" t="n"/>
+      <c r="C931" s="2" t="n"/>
+      <c r="D931" s="2" t="n"/>
+      <c r="E931" s="2" t="n"/>
+      <c r="F931" s="2" t="n"/>
+      <c r="G931" s="2" t="n"/>
+      <c r="H931" s="2" t="n"/>
+      <c r="I931" s="2" t="n"/>
+      <c r="J931" s="2" t="n"/>
+    </row>
+    <row r="932">
+      <c r="A932" s="2" t="n"/>
+      <c r="B932" s="2" t="n"/>
+      <c r="C932" s="2" t="n"/>
+      <c r="D932" s="2" t="n"/>
+      <c r="E932" s="2" t="n"/>
+      <c r="F932" s="2" t="n"/>
+      <c r="G932" s="2" t="n"/>
+      <c r="H932" s="2" t="n"/>
+      <c r="I932" s="2" t="n"/>
+      <c r="J932" s="2" t="n"/>
+    </row>
+    <row r="933">
+      <c r="A933" s="2" t="n"/>
+      <c r="B933" s="2" t="n"/>
+      <c r="C933" s="2" t="n"/>
+      <c r="D933" s="2" t="n"/>
+      <c r="E933" s="2" t="n"/>
+      <c r="F933" s="2" t="n"/>
+      <c r="G933" s="2" t="n"/>
+      <c r="H933" s="2" t="n"/>
+      <c r="I933" s="2" t="n"/>
+      <c r="J933" s="2" t="n"/>
+    </row>
+    <row r="934">
+      <c r="A934" s="2" t="n"/>
+      <c r="B934" s="2" t="n"/>
+      <c r="C934" s="2" t="n"/>
+      <c r="D934" s="2" t="n"/>
+      <c r="E934" s="2" t="n"/>
+      <c r="F934" s="2" t="n"/>
+      <c r="G934" s="2" t="n"/>
+      <c r="H934" s="2" t="n"/>
+      <c r="I934" s="2" t="n"/>
+      <c r="J934" s="2" t="n"/>
+    </row>
+    <row r="935">
+      <c r="A935" s="2" t="n"/>
+      <c r="B935" s="2" t="n"/>
+      <c r="C935" s="2" t="n"/>
+      <c r="D935" s="2" t="n"/>
+      <c r="E935" s="2" t="n"/>
+      <c r="F935" s="2" t="n"/>
+      <c r="G935" s="2" t="n"/>
+      <c r="H935" s="2" t="n"/>
+      <c r="I935" s="2" t="n"/>
+      <c r="J935" s="2" t="n"/>
+    </row>
+    <row r="936">
+      <c r="A936" s="2" t="n"/>
+      <c r="B936" s="2" t="n"/>
+      <c r="C936" s="2" t="n"/>
+      <c r="D936" s="2" t="n"/>
+      <c r="E936" s="2" t="n"/>
+      <c r="F936" s="2" t="n"/>
+      <c r="G936" s="2" t="n"/>
+      <c r="H936" s="2" t="n"/>
+      <c r="I936" s="2" t="n"/>
+      <c r="J936" s="2" t="n"/>
+    </row>
+    <row r="937">
+      <c r="A937" s="2" t="n"/>
+      <c r="B937" s="2" t="n"/>
+      <c r="C937" s="2" t="n"/>
+      <c r="D937" s="2" t="n"/>
+      <c r="E937" s="2" t="n"/>
+      <c r="F937" s="2" t="n"/>
+      <c r="G937" s="2" t="n"/>
+      <c r="H937" s="2" t="n"/>
+      <c r="I937" s="2" t="n"/>
+      <c r="J937" s="2" t="n"/>
+    </row>
+    <row r="938">
+      <c r="A938" s="2" t="n"/>
+      <c r="B938" s="2" t="n"/>
+      <c r="C938" s="2" t="n"/>
+      <c r="D938" s="2" t="n"/>
+      <c r="E938" s="2" t="n"/>
+      <c r="F938" s="2" t="n"/>
+      <c r="G938" s="2" t="n"/>
+      <c r="H938" s="2" t="n"/>
+      <c r="I938" s="2" t="n"/>
+      <c r="J938" s="2" t="n"/>
+    </row>
+    <row r="939">
+      <c r="A939" s="2" t="n"/>
+      <c r="B939" s="2" t="n"/>
+      <c r="C939" s="2" t="n"/>
+      <c r="D939" s="2" t="n"/>
+      <c r="E939" s="2" t="n"/>
+      <c r="F939" s="2" t="n"/>
+      <c r="G939" s="2" t="n"/>
+      <c r="H939" s="2" t="n"/>
+      <c r="I939" s="2" t="n"/>
+      <c r="J939" s="2" t="n"/>
+    </row>
+    <row r="940">
+      <c r="A940" s="2" t="n"/>
+      <c r="B940" s="2" t="n"/>
+      <c r="C940" s="2" t="n"/>
+      <c r="D940" s="2" t="n"/>
+      <c r="E940" s="2" t="n"/>
+      <c r="F940" s="2" t="n"/>
+      <c r="G940" s="2" t="n"/>
+      <c r="H940" s="2" t="n"/>
+      <c r="I940" s="2" t="n"/>
+      <c r="J940" s="2" t="n"/>
+    </row>
+    <row r="941">
+      <c r="A941" s="2" t="n"/>
+      <c r="B941" s="2" t="n"/>
+      <c r="C941" s="2" t="n"/>
+      <c r="D941" s="2" t="n"/>
+      <c r="E941" s="2" t="n"/>
+      <c r="F941" s="2" t="n"/>
+      <c r="G941" s="2" t="n"/>
+      <c r="H941" s="2" t="n"/>
+      <c r="I941" s="2" t="n"/>
+      <c r="J941" s="2" t="n"/>
+    </row>
+    <row r="942">
+      <c r="A942" s="2" t="n"/>
+      <c r="B942" s="2" t="n"/>
+      <c r="C942" s="2" t="n"/>
+      <c r="D942" s="2" t="n"/>
+      <c r="E942" s="2" t="n"/>
+      <c r="F942" s="2" t="n"/>
+      <c r="G942" s="2" t="n"/>
+      <c r="H942" s="2" t="n"/>
+      <c r="I942" s="2" t="n"/>
+      <c r="J942" s="2" t="n"/>
+    </row>
+    <row r="943">
+      <c r="A943" s="2" t="n"/>
+      <c r="B943" s="2" t="n"/>
+      <c r="C943" s="2" t="n"/>
+      <c r="D943" s="2" t="n"/>
+      <c r="E943" s="2" t="n"/>
+      <c r="F943" s="2" t="n"/>
+      <c r="G943" s="2" t="n"/>
+      <c r="H943" s="2" t="n"/>
+      <c r="I943" s="2" t="n"/>
+      <c r="J943" s="2" t="n"/>
+    </row>
+    <row r="944">
+      <c r="A944" s="2" t="n"/>
+      <c r="B944" s="2" t="n"/>
+      <c r="C944" s="2" t="n"/>
+      <c r="D944" s="2" t="n"/>
+      <c r="E944" s="2" t="n"/>
+      <c r="F944" s="2" t="n"/>
+      <c r="G944" s="2" t="n"/>
+      <c r="H944" s="2" t="n"/>
+      <c r="I944" s="2" t="n"/>
+      <c r="J944" s="2" t="n"/>
+    </row>
+    <row r="945">
+      <c r="A945" s="2" t="n"/>
+      <c r="B945" s="2" t="n"/>
+      <c r="C945" s="2" t="n"/>
+      <c r="D945" s="2" t="n"/>
+      <c r="E945" s="2" t="n"/>
+      <c r="F945" s="2" t="n"/>
+      <c r="G945" s="2" t="n"/>
+      <c r="H945" s="2" t="n"/>
+      <c r="I945" s="2" t="n"/>
+      <c r="J945" s="2" t="n"/>
+    </row>
+    <row r="946">
+      <c r="A946" s="2" t="n"/>
+      <c r="B946" s="2" t="n"/>
+      <c r="C946" s="2" t="n"/>
+      <c r="D946" s="2" t="n"/>
+      <c r="E946" s="2" t="n"/>
+      <c r="F946" s="2" t="n"/>
+      <c r="G946" s="2" t="n"/>
+      <c r="H946" s="2" t="n"/>
+      <c r="I946" s="2" t="n"/>
+      <c r="J946" s="2" t="n"/>
+    </row>
+    <row r="947">
+      <c r="A947" s="2" t="n"/>
+      <c r="B947" s="2" t="n"/>
+      <c r="C947" s="2" t="n"/>
+      <c r="D947" s="2" t="n"/>
+      <c r="E947" s="2" t="n"/>
+      <c r="F947" s="2" t="n"/>
+      <c r="G947" s="2" t="n"/>
+      <c r="H947" s="2" t="n"/>
+      <c r="I947" s="2" t="n"/>
+      <c r="J947" s="2" t="n"/>
+    </row>
+    <row r="948">
+      <c r="A948" s="2" t="n"/>
+      <c r="B948" s="2" t="n"/>
+      <c r="C948" s="2" t="n"/>
+      <c r="D948" s="2" t="n"/>
+      <c r="E948" s="2" t="n"/>
+      <c r="F948" s="2" t="n"/>
+      <c r="G948" s="2" t="n"/>
+      <c r="H948" s="2" t="n"/>
+      <c r="I948" s="2" t="n"/>
+      <c r="J948" s="2" t="n"/>
+    </row>
+    <row r="949">
+      <c r="A949" s="2" t="n"/>
+      <c r="B949" s="2" t="n"/>
+      <c r="C949" s="2" t="n"/>
+      <c r="D949" s="2" t="n"/>
+      <c r="E949" s="2" t="n"/>
+      <c r="F949" s="2" t="n"/>
+      <c r="G949" s="2" t="n"/>
+      <c r="H949" s="2" t="n"/>
+      <c r="I949" s="2" t="n"/>
+      <c r="J949" s="2" t="n"/>
+    </row>
+    <row r="950">
+      <c r="A950" s="2" t="n"/>
+      <c r="B950" s="2" t="n"/>
+      <c r="C950" s="2" t="n"/>
+      <c r="D950" s="2" t="n"/>
+      <c r="E950" s="2" t="n"/>
+      <c r="F950" s="2" t="n"/>
+      <c r="G950" s="2" t="n"/>
+      <c r="H950" s="2" t="n"/>
+      <c r="I950" s="2" t="n"/>
+      <c r="J950" s="2" t="n"/>
+    </row>
+    <row r="951">
+      <c r="A951" s="2" t="n"/>
+      <c r="B951" s="2" t="n"/>
+      <c r="C951" s="2" t="n"/>
+      <c r="D951" s="2" t="n"/>
+      <c r="E951" s="2" t="n"/>
+      <c r="F951" s="2" t="n"/>
+      <c r="G951" s="2" t="n"/>
+      <c r="H951" s="2" t="n"/>
+      <c r="I951" s="2" t="n"/>
+      <c r="J951" s="2" t="n"/>
+    </row>
+    <row r="952">
+      <c r="A952" s="2" t="n"/>
+      <c r="B952" s="2" t="n"/>
+      <c r="C952" s="2" t="n"/>
+      <c r="D952" s="2" t="n"/>
+      <c r="E952" s="2" t="n"/>
+      <c r="F952" s="2" t="n"/>
+      <c r="G952" s="2" t="n"/>
+      <c r="H952" s="2" t="n"/>
+      <c r="I952" s="2" t="n"/>
+      <c r="J952" s="2" t="n"/>
+    </row>
+    <row r="953">
+      <c r="A953" s="2" t="n"/>
+      <c r="B953" s="2" t="n"/>
+      <c r="C953" s="2" t="n"/>
+      <c r="D953" s="2" t="n"/>
+      <c r="E953" s="2" t="n"/>
+      <c r="F953" s="2" t="n"/>
+      <c r="G953" s="2" t="n"/>
+      <c r="H953" s="2" t="n"/>
+      <c r="I953" s="2" t="n"/>
+      <c r="J953" s="2" t="n"/>
+    </row>
+    <row r="954">
+      <c r="A954" s="2" t="n"/>
+      <c r="B954" s="2" t="n"/>
+      <c r="C954" s="2" t="n"/>
+      <c r="D954" s="2" t="n"/>
+      <c r="E954" s="2" t="n"/>
+      <c r="F954" s="2" t="n"/>
+      <c r="G954" s="2" t="n"/>
+      <c r="H954" s="2" t="n"/>
+      <c r="I954" s="2" t="n"/>
+      <c r="J954" s="2" t="n"/>
+    </row>
+    <row r="955">
+      <c r="A955" s="2" t="n"/>
+      <c r="B955" s="2" t="n"/>
+      <c r="C955" s="2" t="n"/>
+      <c r="D955" s="2" t="n"/>
+      <c r="E955" s="2" t="n"/>
+      <c r="F955" s="2" t="n"/>
+      <c r="G955" s="2" t="n"/>
+      <c r="H955" s="2" t="n"/>
+      <c r="I955" s="2" t="n"/>
+      <c r="J955" s="2" t="n"/>
+    </row>
+    <row r="956">
+      <c r="A956" s="2" t="n"/>
+      <c r="B956" s="2" t="n"/>
+      <c r="C956" s="2" t="n"/>
+      <c r="D956" s="2" t="n"/>
+      <c r="E956" s="2" t="n"/>
+      <c r="F956" s="2" t="n"/>
+      <c r="G956" s="2" t="n"/>
+      <c r="H956" s="2" t="n"/>
+      <c r="I956" s="2" t="n"/>
+      <c r="J956" s="2" t="n"/>
+    </row>
+    <row r="957">
+      <c r="A957" s="2" t="n"/>
+      <c r="B957" s="2" t="n"/>
+      <c r="C957" s="2" t="n"/>
+      <c r="D957" s="2" t="n"/>
+      <c r="E957" s="2" t="n"/>
+      <c r="F957" s="2" t="n"/>
+      <c r="G957" s="2" t="n"/>
+      <c r="H957" s="2" t="n"/>
+      <c r="I957" s="2" t="n"/>
+      <c r="J957" s="2" t="n"/>
+    </row>
+    <row r="958">
+      <c r="A958" s="2" t="n"/>
+      <c r="B958" s="2" t="n"/>
+      <c r="C958" s="2" t="n"/>
+      <c r="D958" s="2" t="n"/>
+      <c r="E958" s="2" t="n"/>
+      <c r="F958" s="2" t="n"/>
+      <c r="G958" s="2" t="n"/>
+      <c r="H958" s="2" t="n"/>
+      <c r="I958" s="2" t="n"/>
+      <c r="J958" s="2" t="n"/>
+    </row>
+    <row r="959">
+      <c r="A959" s="2" t="n"/>
+      <c r="B959" s="2" t="n"/>
+      <c r="C959" s="2" t="n"/>
+      <c r="D959" s="2" t="n"/>
+      <c r="E959" s="2" t="n"/>
+      <c r="F959" s="2" t="n"/>
+      <c r="G959" s="2" t="n"/>
+      <c r="H959" s="2" t="n"/>
+      <c r="I959" s="2" t="n"/>
+      <c r="J959" s="2" t="n"/>
+    </row>
+    <row r="960">
+      <c r="A960" s="2" t="n"/>
+      <c r="B960" s="2" t="n"/>
+      <c r="C960" s="2" t="n"/>
+      <c r="D960" s="2" t="n"/>
+      <c r="E960" s="2" t="n"/>
+      <c r="F960" s="2" t="n"/>
+      <c r="G960" s="2" t="n"/>
+      <c r="H960" s="2" t="n"/>
+      <c r="I960" s="2" t="n"/>
+      <c r="J960" s="2" t="n"/>
+    </row>
+    <row r="961">
+      <c r="A961" s="2" t="n"/>
+      <c r="B961" s="2" t="n"/>
+      <c r="C961" s="2" t="n"/>
+      <c r="D961" s="2" t="n"/>
+      <c r="E961" s="2" t="n"/>
+      <c r="F961" s="2" t="n"/>
+      <c r="G961" s="2" t="n"/>
+      <c r="H961" s="2" t="n"/>
+      <c r="I961" s="2" t="n"/>
+      <c r="J961" s="2" t="n"/>
+    </row>
+    <row r="962">
+      <c r="A962" s="2" t="n"/>
+      <c r="B962" s="2" t="n"/>
+      <c r="C962" s="2" t="n"/>
+      <c r="D962" s="2" t="n"/>
+      <c r="E962" s="2" t="n"/>
+      <c r="F962" s="2" t="n"/>
+      <c r="G962" s="2" t="n"/>
+      <c r="H962" s="2" t="n"/>
+      <c r="I962" s="2" t="n"/>
+      <c r="J962" s="2" t="n"/>
+    </row>
+    <row r="963">
+      <c r="A963" s="2" t="n"/>
+      <c r="B963" s="2" t="n"/>
+      <c r="C963" s="2" t="n"/>
+      <c r="D963" s="2" t="n"/>
+      <c r="E963" s="2" t="n"/>
+      <c r="F963" s="2" t="n"/>
+      <c r="G963" s="2" t="n"/>
+      <c r="H963" s="2" t="n"/>
+      <c r="I963" s="2" t="n"/>
+      <c r="J963" s="2" t="n"/>
+    </row>
+    <row r="964">
+      <c r="A964" s="2" t="n"/>
+      <c r="B964" s="2" t="n"/>
+      <c r="C964" s="2" t="n"/>
+      <c r="D964" s="2" t="n"/>
+      <c r="E964" s="2" t="n"/>
+      <c r="F964" s="2" t="n"/>
+      <c r="G964" s="2" t="n"/>
+      <c r="H964" s="2" t="n"/>
+      <c r="I964" s="2" t="n"/>
+      <c r="J964" s="2" t="n"/>
+    </row>
+    <row r="965">
+      <c r="A965" s="2" t="n"/>
+      <c r="B965" s="2" t="n"/>
+      <c r="C965" s="2" t="n"/>
+      <c r="D965" s="2" t="n"/>
+      <c r="E965" s="2" t="n"/>
+      <c r="F965" s="2" t="n"/>
+      <c r="G965" s="2" t="n"/>
+      <c r="H965" s="2" t="n"/>
+      <c r="I965" s="2" t="n"/>
+      <c r="J965" s="2" t="n"/>
+    </row>
+    <row r="966">
+      <c r="A966" s="2" t="n"/>
+      <c r="B966" s="2" t="n"/>
+      <c r="C966" s="2" t="n"/>
+      <c r="D966" s="2" t="n"/>
+      <c r="E966" s="2" t="n"/>
+      <c r="F966" s="2" t="n"/>
+      <c r="G966" s="2" t="n"/>
+      <c r="H966" s="2" t="n"/>
+      <c r="I966" s="2" t="n"/>
+      <c r="J966" s="2" t="n"/>
+    </row>
+    <row r="967">
+      <c r="A967" s="2" t="n"/>
+      <c r="B967" s="2" t="n"/>
+      <c r="C967" s="2" t="n"/>
+      <c r="D967" s="2" t="n"/>
+      <c r="E967" s="2" t="n"/>
+      <c r="F967" s="2" t="n"/>
+      <c r="G967" s="2" t="n"/>
+      <c r="H967" s="2" t="n"/>
+      <c r="I967" s="2" t="n"/>
+      <c r="J967" s="2" t="n"/>
+    </row>
+    <row r="968">
+      <c r="A968" s="2" t="n"/>
+      <c r="B968" s="2" t="n"/>
+      <c r="C968" s="2" t="n"/>
+      <c r="D968" s="2" t="n"/>
+      <c r="E968" s="2" t="n"/>
+      <c r="F968" s="2" t="n"/>
+      <c r="G968" s="2" t="n"/>
+      <c r="H968" s="2" t="n"/>
+      <c r="I968" s="2" t="n"/>
+      <c r="J968" s="2" t="n"/>
+    </row>
+    <row r="969">
+      <c r="A969" s="2" t="n"/>
+      <c r="B969" s="2" t="n"/>
+      <c r="C969" s="2" t="n"/>
+      <c r="D969" s="2" t="n"/>
+      <c r="E969" s="2" t="n"/>
+      <c r="F969" s="2" t="n"/>
+      <c r="G969" s="2" t="n"/>
+      <c r="H969" s="2" t="n"/>
+      <c r="I969" s="2" t="n"/>
+      <c r="J969" s="2" t="n"/>
+    </row>
+    <row r="970">
+      <c r="A970" s="2" t="n"/>
+      <c r="B970" s="2" t="n"/>
+      <c r="C970" s="2" t="n"/>
+      <c r="D970" s="2" t="n"/>
+      <c r="E970" s="2" t="n"/>
+      <c r="F970" s="2" t="n"/>
+      <c r="G970" s="2" t="n"/>
+      <c r="H970" s="2" t="n"/>
+      <c r="I970" s="2" t="n"/>
+      <c r="J970" s="2" t="n"/>
+    </row>
+    <row r="971">
+      <c r="A971" s="2" t="n"/>
+      <c r="B971" s="2" t="n"/>
+      <c r="C971" s="2" t="n"/>
+      <c r="D971" s="2" t="n"/>
+      <c r="E971" s="2" t="n"/>
+      <c r="F971" s="2" t="n"/>
+      <c r="G971" s="2" t="n"/>
+      <c r="H971" s="2" t="n"/>
+      <c r="I971" s="2" t="n"/>
+      <c r="J971" s="2" t="n"/>
+    </row>
+    <row r="972">
+      <c r="A972" s="2" t="n"/>
+      <c r="B972" s="2" t="n"/>
+      <c r="C972" s="2" t="n"/>
+      <c r="D972" s="2" t="n"/>
+      <c r="E972" s="2" t="n"/>
+      <c r="F972" s="2" t="n"/>
+      <c r="G972" s="2" t="n"/>
+      <c r="H972" s="2" t="n"/>
+      <c r="I972" s="2" t="n"/>
+      <c r="J972" s="2" t="n"/>
+    </row>
+    <row r="973">
+      <c r="A973" s="2" t="n"/>
+      <c r="B973" s="2" t="n"/>
+      <c r="C973" s="2" t="n"/>
+      <c r="D973" s="2" t="n"/>
+      <c r="E973" s="2" t="n"/>
+      <c r="F973" s="2" t="n"/>
+      <c r="G973" s="2" t="n"/>
+      <c r="H973" s="2" t="n"/>
+      <c r="I973" s="2" t="n"/>
+      <c r="J973" s="2" t="n"/>
+    </row>
+    <row r="974">
+      <c r="A974" s="2" t="n"/>
+      <c r="B974" s="2" t="n"/>
+      <c r="C974" s="2" t="n"/>
+      <c r="D974" s="2" t="n"/>
+      <c r="E974" s="2" t="n"/>
+      <c r="F974" s="2" t="n"/>
+      <c r="G974" s="2" t="n"/>
+      <c r="H974" s="2" t="n"/>
+      <c r="I974" s="2" t="n"/>
+      <c r="J974" s="2" t="n"/>
+    </row>
+    <row r="975">
+      <c r="A975" s="2" t="n"/>
+      <c r="B975" s="2" t="n"/>
+      <c r="C975" s="2" t="n"/>
+      <c r="D975" s="2" t="n"/>
+      <c r="E975" s="2" t="n"/>
+      <c r="F975" s="2" t="n"/>
+      <c r="G975" s="2" t="n"/>
+      <c r="H975" s="2" t="n"/>
+      <c r="I975" s="2" t="n"/>
+      <c r="J975" s="2" t="n"/>
+    </row>
+    <row r="976">
+      <c r="A976" s="2" t="n"/>
+      <c r="B976" s="2" t="n"/>
+      <c r="C976" s="2" t="n"/>
+      <c r="D976" s="2" t="n"/>
+      <c r="E976" s="2" t="n"/>
+      <c r="F976" s="2" t="n"/>
+      <c r="G976" s="2" t="n"/>
+      <c r="H976" s="2" t="n"/>
+      <c r="I976" s="2" t="n"/>
+      <c r="J976" s="2" t="n"/>
+    </row>
+    <row r="977">
+      <c r="A977" s="2" t="n"/>
+      <c r="B977" s="2" t="n"/>
+      <c r="C977" s="2" t="n"/>
+      <c r="D977" s="2" t="n"/>
+      <c r="E977" s="2" t="n"/>
+      <c r="F977" s="2" t="n"/>
+      <c r="G977" s="2" t="n"/>
+      <c r="H977" s="2" t="n"/>
+      <c r="I977" s="2" t="n"/>
+      <c r="J977" s="2" t="n"/>
+    </row>
+    <row r="978">
+      <c r="A978" s="2" t="n"/>
+      <c r="B978" s="2" t="n"/>
+      <c r="C978" s="2" t="n"/>
+      <c r="D978" s="2" t="n"/>
+      <c r="E978" s="2" t="n"/>
+      <c r="F978" s="2" t="n"/>
+      <c r="G978" s="2" t="n"/>
+      <c r="H978" s="2" t="n"/>
+      <c r="I978" s="2" t="n"/>
+      <c r="J978" s="2" t="n"/>
+    </row>
+    <row r="979">
+      <c r="A979" s="2" t="n"/>
+      <c r="B979" s="2" t="n"/>
+      <c r="C979" s="2" t="n"/>
+      <c r="D979" s="2" t="n"/>
+      <c r="E979" s="2" t="n"/>
+      <c r="F979" s="2" t="n"/>
+      <c r="G979" s="2" t="n"/>
+      <c r="H979" s="2" t="n"/>
+      <c r="I979" s="2" t="n"/>
+      <c r="J979" s="2" t="n"/>
+    </row>
+    <row r="980">
+      <c r="A980" s="2" t="n"/>
+      <c r="B980" s="2" t="n"/>
+      <c r="C980" s="2" t="n"/>
+      <c r="D980" s="2" t="n"/>
+      <c r="E980" s="2" t="n"/>
+      <c r="F980" s="2" t="n"/>
+      <c r="G980" s="2" t="n"/>
+      <c r="H980" s="2" t="n"/>
+      <c r="I980" s="2" t="n"/>
+      <c r="J980" s="2" t="n"/>
+    </row>
+    <row r="981">
+      <c r="A981" s="2" t="n"/>
+      <c r="B981" s="2" t="n"/>
+      <c r="C981" s="2" t="n"/>
+      <c r="D981" s="2" t="n"/>
+      <c r="E981" s="2" t="n"/>
+      <c r="F981" s="2" t="n"/>
+      <c r="G981" s="2" t="n"/>
+      <c r="H981" s="2" t="n"/>
+      <c r="I981" s="2" t="n"/>
+      <c r="J981" s="2" t="n"/>
+    </row>
+    <row r="982">
+      <c r="A982" s="2" t="n"/>
+      <c r="B982" s="2" t="n"/>
+      <c r="C982" s="2" t="n"/>
+      <c r="D982" s="2" t="n"/>
+      <c r="E982" s="2" t="n"/>
+      <c r="F982" s="2" t="n"/>
+      <c r="G982" s="2" t="n"/>
+      <c r="H982" s="2" t="n"/>
+      <c r="I982" s="2" t="n"/>
+      <c r="J982" s="2" t="n"/>
+    </row>
+    <row r="983">
+      <c r="A983" s="2" t="n"/>
+      <c r="B983" s="2" t="n"/>
+      <c r="C983" s="2" t="n"/>
+      <c r="D983" s="2" t="n"/>
+      <c r="E983" s="2" t="n"/>
+      <c r="F983" s="2" t="n"/>
+      <c r="G983" s="2" t="n"/>
+      <c r="H983" s="2" t="n"/>
+      <c r="I983" s="2" t="n"/>
+      <c r="J983" s="2" t="n"/>
+    </row>
+    <row r="984">
+      <c r="A984" s="2" t="n"/>
+      <c r="B984" s="2" t="n"/>
+      <c r="C984" s="2" t="n"/>
+      <c r="D984" s="2" t="n"/>
+      <c r="E984" s="2" t="n"/>
+      <c r="F984" s="2" t="n"/>
+      <c r="G984" s="2" t="n"/>
+      <c r="H984" s="2" t="n"/>
+      <c r="I984" s="2" t="n"/>
+      <c r="J984" s="2" t="n"/>
+    </row>
+    <row r="985">
+      <c r="A985" s="2" t="n"/>
+      <c r="B985" s="2" t="n"/>
+      <c r="C985" s="2" t="n"/>
+      <c r="D985" s="2" t="n"/>
+      <c r="E985" s="2" t="n"/>
+      <c r="F985" s="2" t="n"/>
+      <c r="G985" s="2" t="n"/>
+      <c r="H985" s="2" t="n"/>
+      <c r="I985" s="2" t="n"/>
+      <c r="J985" s="2" t="n"/>
+    </row>
+    <row r="986">
+      <c r="A986" s="2" t="n"/>
+      <c r="B986" s="2" t="n"/>
+      <c r="C986" s="2" t="n"/>
+      <c r="D986" s="2" t="n"/>
+      <c r="E986" s="2" t="n"/>
+      <c r="F986" s="2" t="n"/>
+      <c r="G986" s="2" t="n"/>
+      <c r="H986" s="2" t="n"/>
+      <c r="I986" s="2" t="n"/>
+      <c r="J986" s="2" t="n"/>
+    </row>
+    <row r="987">
+      <c r="A987" s="2" t="n"/>
+      <c r="B987" s="2" t="n"/>
+      <c r="C987" s="2" t="n"/>
+      <c r="D987" s="2" t="n"/>
+      <c r="E987" s="2" t="n"/>
+      <c r="F987" s="2" t="n"/>
+      <c r="G987" s="2" t="n"/>
+      <c r="H987" s="2" t="n"/>
+      <c r="I987" s="2" t="n"/>
+      <c r="J987" s="2" t="n"/>
+    </row>
+    <row r="988">
+      <c r="A988" s="2" t="n"/>
+      <c r="B988" s="2" t="n"/>
+      <c r="C988" s="2" t="n"/>
+      <c r="D988" s="2" t="n"/>
+      <c r="E988" s="2" t="n"/>
+      <c r="F988" s="2" t="n"/>
+      <c r="G988" s="2" t="n"/>
+      <c r="H988" s="2" t="n"/>
+      <c r="I988" s="2" t="n"/>
+      <c r="J988" s="2" t="n"/>
+    </row>
+    <row r="989">
+      <c r="A989" s="2" t="n"/>
+      <c r="B989" s="2" t="n"/>
+      <c r="C989" s="2" t="n"/>
+      <c r="D989" s="2" t="n"/>
+      <c r="E989" s="2" t="n"/>
+      <c r="F989" s="2" t="n"/>
+      <c r="G989" s="2" t="n"/>
+      <c r="H989" s="2" t="n"/>
+      <c r="I989" s="2" t="n"/>
+      <c r="J989" s="2" t="n"/>
+    </row>
+    <row r="990">
+      <c r="A990" s="2" t="n"/>
+      <c r="B990" s="2" t="n"/>
+      <c r="C990" s="2" t="n"/>
+      <c r="D990" s="2" t="n"/>
+      <c r="E990" s="2" t="n"/>
+      <c r="F990" s="2" t="n"/>
+      <c r="G990" s="2" t="n"/>
+      <c r="H990" s="2" t="n"/>
+      <c r="I990" s="2" t="n"/>
+      <c r="J990" s="2" t="n"/>
+    </row>
+    <row r="991">
+      <c r="A991" s="2" t="n"/>
+      <c r="B991" s="2" t="n"/>
+      <c r="C991" s="2" t="n"/>
+      <c r="D991" s="2" t="n"/>
+      <c r="E991" s="2" t="n"/>
+      <c r="F991" s="2" t="n"/>
+      <c r="G991" s="2" t="n"/>
+      <c r="H991" s="2" t="n"/>
+      <c r="I991" s="2" t="n"/>
+      <c r="J991" s="2" t="n"/>
+    </row>
+    <row r="992">
+      <c r="A992" s="2" t="n"/>
+      <c r="B992" s="2" t="n"/>
+      <c r="C992" s="2" t="n"/>
+      <c r="D992" s="2" t="n"/>
+      <c r="E992" s="2" t="n"/>
+      <c r="F992" s="2" t="n"/>
+      <c r="G992" s="2" t="n"/>
+      <c r="H992" s="2" t="n"/>
+      <c r="I992" s="2" t="n"/>
+      <c r="J992" s="2" t="n"/>
+    </row>
+    <row r="993">
+      <c r="A993" s="2" t="n"/>
+      <c r="B993" s="2" t="n"/>
+      <c r="C993" s="2" t="n"/>
+      <c r="D993" s="2" t="n"/>
+      <c r="E993" s="2" t="n"/>
+      <c r="F993" s="2" t="n"/>
+      <c r="G993" s="2" t="n"/>
+      <c r="H993" s="2" t="n"/>
+      <c r="I993" s="2" t="n"/>
+      <c r="J993" s="2" t="n"/>
+    </row>
+    <row r="994">
+      <c r="A994" s="2" t="n"/>
+      <c r="B994" s="2" t="n"/>
+      <c r="C994" s="2" t="n"/>
+      <c r="D994" s="2" t="n"/>
+      <c r="E994" s="2" t="n"/>
+      <c r="F994" s="2" t="n"/>
+      <c r="G994" s="2" t="n"/>
+      <c r="H994" s="2" t="n"/>
+      <c r="I994" s="2" t="n"/>
+      <c r="J994" s="2" t="n"/>
+    </row>
+    <row r="995">
+      <c r="A995" s="2" t="n"/>
+      <c r="B995" s="2" t="n"/>
+      <c r="C995" s="2" t="n"/>
+      <c r="D995" s="2" t="n"/>
+      <c r="E995" s="2" t="n"/>
+      <c r="F995" s="2" t="n"/>
+      <c r="G995" s="2" t="n"/>
+      <c r="H995" s="2" t="n"/>
+      <c r="I995" s="2" t="n"/>
+      <c r="J995" s="2" t="n"/>
+    </row>
+    <row r="996">
+      <c r="A996" s="2" t="n"/>
+      <c r="B996" s="2" t="n"/>
+      <c r="C996" s="2" t="n"/>
+      <c r="D996" s="2" t="n"/>
+      <c r="E996" s="2" t="n"/>
+      <c r="F996" s="2" t="n"/>
+      <c r="G996" s="2" t="n"/>
+      <c r="H996" s="2" t="n"/>
+      <c r="I996" s="2" t="n"/>
+      <c r="J996" s="2" t="n"/>
+    </row>
+    <row r="997">
+      <c r="A997" s="2" t="n"/>
+      <c r="B997" s="2" t="n"/>
+      <c r="C997" s="2" t="n"/>
+      <c r="D997" s="2" t="n"/>
+      <c r="E997" s="2" t="n"/>
+      <c r="F997" s="2" t="n"/>
+      <c r="G997" s="2" t="n"/>
+      <c r="H997" s="2" t="n"/>
+      <c r="I997" s="2" t="n"/>
+      <c r="J997" s="2" t="n"/>
+    </row>
+    <row r="998">
+      <c r="A998" s="2" t="n"/>
+      <c r="B998" s="2" t="n"/>
+      <c r="C998" s="2" t="n"/>
+      <c r="D998" s="2" t="n"/>
+      <c r="E998" s="2" t="n"/>
+      <c r="F998" s="2" t="n"/>
+      <c r="G998" s="2" t="n"/>
+      <c r="H998" s="2" t="n"/>
+      <c r="I998" s="2" t="n"/>
+      <c r="J998" s="2" t="n"/>
+    </row>
+    <row r="999">
+      <c r="A999" s="2" t="n"/>
+      <c r="B999" s="2" t="n"/>
+      <c r="C999" s="2" t="n"/>
+      <c r="D999" s="2" t="n"/>
+      <c r="E999" s="2" t="n"/>
+      <c r="F999" s="2" t="n"/>
+      <c r="G999" s="2" t="n"/>
+      <c r="H999" s="2" t="n"/>
+      <c r="I999" s="2" t="n"/>
+      <c r="J999" s="2" t="n"/>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="2" t="n"/>
+      <c r="B1000" s="2" t="n"/>
+      <c r="C1000" s="2" t="n"/>
+      <c r="D1000" s="2" t="n"/>
+      <c r="E1000" s="2" t="n"/>
+      <c r="F1000" s="2" t="n"/>
+      <c r="G1000" s="2" t="n"/>
+      <c r="H1000" s="2" t="n"/>
+      <c r="I1000" s="2" t="n"/>
+      <c r="J1000" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Cube_finish.xlsx
+++ b/Cube_finish.xlsx
@@ -13644,10 +13644,8 @@
           <t>10/03/2022</t>
         </is>
       </c>
-      <c r="E413" s="2" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="E413" s="2" t="n">
+        <v>2360</v>
       </c>
       <c r="F413" s="2" t="inlineStr"/>
       <c r="G413" s="2" t="inlineStr"/>
@@ -13762,10 +13760,8 @@
           <t>11/03/2022</t>
         </is>
       </c>
-      <c r="E417" s="2" t="inlineStr">
-        <is>
-          <t>2350</t>
-        </is>
+      <c r="E417" s="2" t="n">
+        <v>2350</v>
       </c>
       <c r="F417" s="2" t="inlineStr"/>
       <c r="G417" s="2" t="inlineStr"/>
@@ -13882,10 +13878,8 @@
           <t>14/03/2022</t>
         </is>
       </c>
-      <c r="E421" s="2" t="inlineStr">
-        <is>
-          <t>2380</t>
-        </is>
+      <c r="E421" s="2" t="n">
+        <v>2380</v>
       </c>
       <c r="F421" s="2" t="inlineStr"/>
       <c r="G421" s="2" t="inlineStr"/>
@@ -13996,10 +13990,8 @@
           <t>14/03/2022</t>
         </is>
       </c>
-      <c r="E425" s="2" t="inlineStr">
-        <is>
-          <t>2370</t>
-        </is>
+      <c r="E425" s="2" t="n">
+        <v>2370</v>
       </c>
       <c r="F425" s="2" t="inlineStr"/>
       <c r="G425" s="2" t="inlineStr"/>
@@ -14200,10 +14192,8 @@
           <t>16/03/2022</t>
         </is>
       </c>
-      <c r="E432" s="2" t="inlineStr">
-        <is>
-          <t>2380</t>
-        </is>
+      <c r="E432" s="2" t="n">
+        <v>2380</v>
       </c>
       <c r="F432" s="2" t="inlineStr"/>
       <c r="G432" s="2" t="inlineStr"/>
@@ -14346,10 +14336,8 @@
           <t>17/03/2022</t>
         </is>
       </c>
-      <c r="E437" s="2" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="E437" s="2" t="n">
+        <v>2360</v>
       </c>
       <c r="F437" s="2" t="inlineStr"/>
       <c r="G437" s="2" t="inlineStr"/>
@@ -14380,10 +14368,8 @@
           <t>17/03/2022</t>
         </is>
       </c>
-      <c r="E438" s="2" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="E438" s="2" t="n">
+        <v>2330</v>
       </c>
       <c r="F438" s="2" t="inlineStr"/>
       <c r="G438" s="2" t="inlineStr"/>
@@ -14498,10 +14484,8 @@
           <t>18/03/2022</t>
         </is>
       </c>
-      <c r="E442" s="2" t="inlineStr">
-        <is>
-          <t>2420</t>
-        </is>
+      <c r="E442" s="2" t="n">
+        <v>2420</v>
       </c>
       <c r="F442" s="2" t="inlineStr"/>
       <c r="G442" s="2" t="inlineStr"/>
@@ -14618,10 +14602,8 @@
           <t>21/03/2022</t>
         </is>
       </c>
-      <c r="E446" s="2" t="inlineStr">
-        <is>
-          <t>2370</t>
-        </is>
+      <c r="E446" s="2" t="n">
+        <v>2370</v>
       </c>
       <c r="F446" s="2" t="inlineStr"/>
       <c r="G446" s="2" t="inlineStr"/>
@@ -14738,10 +14720,8 @@
           <t>22/03/2022</t>
         </is>
       </c>
-      <c r="E450" s="2" t="inlineStr">
-        <is>
-          <t>2370</t>
-        </is>
+      <c r="E450" s="2" t="n">
+        <v>2370</v>
       </c>
       <c r="F450" s="2" t="inlineStr"/>
       <c r="G450" s="2" t="inlineStr"/>
@@ -14844,10 +14824,8 @@
           <t>23/03/2022</t>
         </is>
       </c>
-      <c r="E454" s="2" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
+      <c r="E454" s="2" t="n">
+        <v>2340</v>
       </c>
       <c r="F454" s="2" t="inlineStr"/>
       <c r="G454" s="2" t="inlineStr"/>
@@ -14962,10 +14940,8 @@
           <t>24/03/2022</t>
         </is>
       </c>
-      <c r="E458" s="2" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
+      <c r="E458" s="2" t="n">
+        <v>2400</v>
       </c>
       <c r="F458" s="2" t="inlineStr"/>
       <c r="G458" s="2" t="inlineStr"/>
@@ -15103,12 +15079,22 @@
           <t xml:space="preserve">First Floor Wall (32-45)(A-Z) </t>
         </is>
       </c>
-      <c r="D463" s="2" t="inlineStr"/>
-      <c r="E463" s="2" t="inlineStr"/>
+      <c r="D463" s="2" t="inlineStr">
+        <is>
+          <t>25/03/2022</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="n">
+        <v>2390</v>
+      </c>
       <c r="F463" s="2" t="inlineStr"/>
       <c r="G463" s="2" t="inlineStr"/>
       <c r="H463" s="2" t="inlineStr"/>
-      <c r="I463" s="2" t="inlineStr"/>
+      <c r="I463" s="2" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
       <c r="J463" s="2" t="inlineStr"/>
     </row>
     <row r="464">
@@ -15199,12 +15185,24 @@
           <t>First Floor Wall (30-45)(B-Z)</t>
         </is>
       </c>
-      <c r="D467" s="2" t="inlineStr"/>
-      <c r="E467" s="2" t="inlineStr"/>
+      <c r="D467" s="2" t="inlineStr">
+        <is>
+          <t>28/03/2022</t>
+        </is>
+      </c>
+      <c r="E467" s="2" t="inlineStr">
+        <is>
+          <t>2380</t>
+        </is>
+      </c>
       <c r="F467" s="2" t="inlineStr"/>
       <c r="G467" s="2" t="inlineStr"/>
       <c r="H467" s="2" t="inlineStr"/>
-      <c r="I467" s="2" t="inlineStr"/>
+      <c r="I467" s="2" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
       <c r="J467" s="2" t="inlineStr"/>
     </row>
     <row r="468">
@@ -15325,12 +15323,24 @@
           <t>Second Floor Slab - Area 1</t>
         </is>
       </c>
-      <c r="D472" s="2" t="inlineStr"/>
-      <c r="E472" s="2" t="inlineStr"/>
+      <c r="D472" s="2" t="inlineStr">
+        <is>
+          <t>28/03/2022</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>2350</t>
+        </is>
+      </c>
       <c r="F472" s="2" t="inlineStr"/>
       <c r="G472" s="2" t="inlineStr"/>
       <c r="H472" s="2" t="inlineStr"/>
-      <c r="I472" s="2" t="inlineStr"/>
+      <c r="I472" s="2" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
       <c r="J472" s="2" t="inlineStr"/>
     </row>
     <row r="473">
@@ -16018,17 +16028,13 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E498" s="2" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
+      <c r="E498" s="2" t="n">
+        <v>2400</v>
       </c>
       <c r="F498" s="2" t="inlineStr"/>
       <c r="G498" s="2" t="inlineStr"/>
-      <c r="H498" s="2" t="inlineStr">
-        <is>
-          <t>51.0</t>
-        </is>
+      <c r="H498" s="2" t="n">
+        <v>51</v>
       </c>
       <c r="I498" s="2" t="inlineStr"/>
       <c r="J498" s="2" t="inlineStr"/>
@@ -16053,17 +16059,13 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E499" s="2" t="inlineStr">
-        <is>
-          <t>2430</t>
-        </is>
+      <c r="E499" s="2" t="n">
+        <v>2430</v>
       </c>
       <c r="F499" s="2" t="inlineStr"/>
       <c r="G499" s="2" t="inlineStr"/>
-      <c r="H499" s="2" t="inlineStr">
-        <is>
-          <t>50.1</t>
-        </is>
+      <c r="H499" s="2" t="n">
+        <v>50.1</v>
       </c>
       <c r="I499" s="2" t="inlineStr"/>
       <c r="J499" s="2" t="inlineStr"/>
@@ -16138,17 +16140,13 @@
           <t>10/03/2022</t>
         </is>
       </c>
-      <c r="E502" s="2" t="inlineStr">
-        <is>
-          <t>2380</t>
-        </is>
+      <c r="E502" s="2" t="n">
+        <v>2380</v>
       </c>
       <c r="F502" s="2" t="inlineStr"/>
       <c r="G502" s="2" t="inlineStr"/>
-      <c r="H502" s="2" t="inlineStr">
-        <is>
-          <t>45.5</t>
-        </is>
+      <c r="H502" s="2" t="n">
+        <v>45.5</v>
       </c>
       <c r="I502" s="2" t="inlineStr"/>
       <c r="J502" s="2" t="inlineStr"/>
@@ -16172,17 +16170,13 @@
           <t>10/03/2022</t>
         </is>
       </c>
-      <c r="E503" s="2" t="inlineStr">
-        <is>
-          <t>2380</t>
-        </is>
+      <c r="E503" s="2" t="n">
+        <v>2380</v>
       </c>
       <c r="F503" s="2" t="inlineStr"/>
       <c r="G503" s="2" t="inlineStr"/>
-      <c r="H503" s="2" t="inlineStr">
-        <is>
-          <t>39.3</t>
-        </is>
+      <c r="H503" s="2" t="n">
+        <v>39.3</v>
       </c>
       <c r="I503" s="2" t="inlineStr"/>
       <c r="J503" s="2" t="inlineStr"/>
@@ -16284,17 +16278,13 @@
           <t>11/03/2022</t>
         </is>
       </c>
-      <c r="E507" s="2" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="E507" s="2" t="n">
+        <v>2360</v>
       </c>
       <c r="F507" s="2" t="inlineStr"/>
       <c r="G507" s="2" t="inlineStr"/>
-      <c r="H507" s="2" t="inlineStr">
-        <is>
-          <t>43.0</t>
-        </is>
+      <c r="H507" s="2" t="n">
+        <v>43</v>
       </c>
       <c r="I507" s="2" t="inlineStr"/>
       <c r="J507" s="2" t="inlineStr"/>
@@ -16318,17 +16308,13 @@
           <t>11/03/2022</t>
         </is>
       </c>
-      <c r="E508" s="2" t="inlineStr">
-        <is>
-          <t>2370</t>
-        </is>
+      <c r="E508" s="2" t="n">
+        <v>2370</v>
       </c>
       <c r="F508" s="2" t="inlineStr"/>
       <c r="G508" s="2" t="inlineStr"/>
-      <c r="H508" s="2" t="inlineStr">
-        <is>
-          <t>44.5</t>
-        </is>
+      <c r="H508" s="2" t="n">
+        <v>44.5</v>
       </c>
       <c r="I508" s="2" t="inlineStr"/>
       <c r="J508" s="2" t="inlineStr"/>
@@ -16402,17 +16388,13 @@
           <t>14/03/2022</t>
         </is>
       </c>
-      <c r="E511" s="2" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="E511" s="2" t="n">
+        <v>2330</v>
       </c>
       <c r="F511" s="2" t="inlineStr"/>
       <c r="G511" s="2" t="inlineStr"/>
-      <c r="H511" s="2" t="inlineStr">
-        <is>
-          <t>39.6</t>
-        </is>
+      <c r="H511" s="2" t="n">
+        <v>39.6</v>
       </c>
       <c r="I511" s="2" t="inlineStr"/>
       <c r="J511" s="2" t="inlineStr"/>
@@ -16436,17 +16418,13 @@
           <t>14/03/2022</t>
         </is>
       </c>
-      <c r="E512" s="2" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
+      <c r="E512" s="2" t="n">
+        <v>2330</v>
       </c>
       <c r="F512" s="2" t="inlineStr"/>
       <c r="G512" s="2" t="inlineStr"/>
-      <c r="H512" s="2" t="inlineStr">
-        <is>
-          <t>39.0</t>
-        </is>
+      <c r="H512" s="2" t="n">
+        <v>39</v>
       </c>
       <c r="I512" s="2" t="inlineStr"/>
       <c r="J512" s="2" t="inlineStr"/>
@@ -16514,17 +16492,13 @@
           <t>14/03/2022</t>
         </is>
       </c>
-      <c r="E515" s="2" t="inlineStr">
-        <is>
-          <t>2380</t>
-        </is>
+      <c r="E515" s="2" t="n">
+        <v>2380</v>
       </c>
       <c r="F515" s="2" t="inlineStr"/>
       <c r="G515" s="2" t="inlineStr"/>
-      <c r="H515" s="2" t="inlineStr">
-        <is>
-          <t>52.9</t>
-        </is>
+      <c r="H515" s="2" t="n">
+        <v>52.9</v>
       </c>
       <c r="I515" s="2" t="inlineStr"/>
       <c r="J515" s="2" t="inlineStr"/>
@@ -16548,17 +16522,13 @@
           <t>14/03/2022</t>
         </is>
       </c>
-      <c r="E516" s="2" t="inlineStr">
-        <is>
-          <t>2380</t>
-        </is>
+      <c r="E516" s="2" t="n">
+        <v>2380</v>
       </c>
       <c r="F516" s="2" t="inlineStr"/>
       <c r="G516" s="2" t="inlineStr"/>
-      <c r="H516" s="2" t="inlineStr">
-        <is>
-          <t>51.8</t>
-        </is>
+      <c r="H516" s="2" t="n">
+        <v>51.8</v>
       </c>
       <c r="I516" s="2" t="inlineStr"/>
       <c r="J516" s="2" t="inlineStr"/>
@@ -16604,10 +16574,8 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E518" s="2" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="E518" s="2" t="n">
+        <v>2360</v>
       </c>
       <c r="F518" s="2" t="inlineStr">
         <is>
@@ -16638,17 +16606,13 @@
           <t>15/03/2022</t>
         </is>
       </c>
-      <c r="E519" s="2" t="inlineStr">
-        <is>
-          <t>2350</t>
-        </is>
+      <c r="E519" s="2" t="n">
+        <v>2350</v>
       </c>
       <c r="F519" s="2" t="inlineStr"/>
       <c r="G519" s="2" t="inlineStr"/>
-      <c r="H519" s="2" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
+      <c r="H519" s="2" t="n">
+        <v>45.6</v>
       </c>
       <c r="I519" s="2" t="inlineStr"/>
       <c r="J519" s="2" t="inlineStr"/>
@@ -16672,17 +16636,13 @@
           <t>15/03/2022</t>
         </is>
       </c>
-      <c r="E520" s="2" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="E520" s="2" t="n">
+        <v>2360</v>
       </c>
       <c r="F520" s="2" t="inlineStr"/>
       <c r="G520" s="2" t="inlineStr"/>
-      <c r="H520" s="2" t="inlineStr">
-        <is>
-          <t>41.9</t>
-        </is>
+      <c r="H520" s="2" t="n">
+        <v>41.9</v>
       </c>
       <c r="I520" s="2" t="inlineStr"/>
       <c r="J520" s="2" t="inlineStr"/>
@@ -16728,10 +16688,8 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E522" s="2" t="inlineStr">
-        <is>
-          <t>2380</t>
-        </is>
+      <c r="E522" s="2" t="n">
+        <v>2380</v>
       </c>
       <c r="F522" s="2" t="inlineStr">
         <is>
@@ -16762,17 +16720,13 @@
           <t>16/03/2022</t>
         </is>
       </c>
-      <c r="E523" s="2" t="inlineStr">
-        <is>
-          <t>2370</t>
-        </is>
+      <c r="E523" s="2" t="n">
+        <v>2370</v>
       </c>
       <c r="F523" s="2" t="inlineStr"/>
       <c r="G523" s="2" t="inlineStr"/>
-      <c r="H523" s="2" t="inlineStr">
-        <is>
-          <t>50.4</t>
-        </is>
+      <c r="H523" s="2" t="n">
+        <v>50.4</v>
       </c>
       <c r="I523" s="2" t="inlineStr"/>
       <c r="J523" s="2" t="inlineStr"/>
@@ -16796,17 +16750,13 @@
           <t>16/03/2022</t>
         </is>
       </c>
-      <c r="E524" s="2" t="inlineStr">
-        <is>
-          <t>2370</t>
-        </is>
+      <c r="E524" s="2" t="n">
+        <v>2370</v>
       </c>
       <c r="F524" s="2" t="inlineStr"/>
       <c r="G524" s="2" t="inlineStr"/>
-      <c r="H524" s="2" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
+      <c r="H524" s="2" t="n">
+        <v>49.7</v>
       </c>
       <c r="I524" s="2" t="inlineStr"/>
       <c r="J524" s="2" t="inlineStr"/>
@@ -16852,10 +16802,8 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E526" s="2" t="inlineStr">
-        <is>
-          <t>2380</t>
-        </is>
+      <c r="E526" s="2" t="n">
+        <v>2380</v>
       </c>
       <c r="F526" s="2" t="inlineStr">
         <is>
@@ -16886,17 +16834,13 @@
           <t>17/03/2022</t>
         </is>
       </c>
-      <c r="E527" s="2" t="inlineStr">
-        <is>
-          <t>2380</t>
-        </is>
+      <c r="E527" s="2" t="n">
+        <v>2380</v>
       </c>
       <c r="F527" s="2" t="inlineStr"/>
       <c r="G527" s="2" t="inlineStr"/>
-      <c r="H527" s="2" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
+      <c r="H527" s="2" t="n">
+        <v>49.7</v>
       </c>
       <c r="I527" s="2" t="inlineStr"/>
       <c r="J527" s="2" t="inlineStr"/>
@@ -16920,17 +16864,13 @@
           <t>17/03/2022</t>
         </is>
       </c>
-      <c r="E528" s="2" t="inlineStr">
-        <is>
-          <t>2390</t>
-        </is>
+      <c r="E528" s="2" t="n">
+        <v>2390</v>
       </c>
       <c r="F528" s="2" t="inlineStr"/>
       <c r="G528" s="2" t="inlineStr"/>
-      <c r="H528" s="2" t="inlineStr">
-        <is>
-          <t>48.6</t>
-        </is>
+      <c r="H528" s="2" t="n">
+        <v>48.6</v>
       </c>
       <c r="I528" s="2" t="inlineStr"/>
       <c r="J528" s="2" t="inlineStr"/>
@@ -16976,10 +16916,8 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E530" s="2" t="inlineStr">
-        <is>
-          <t>2380</t>
-        </is>
+      <c r="E530" s="2" t="n">
+        <v>2380</v>
       </c>
       <c r="F530" s="2" t="inlineStr">
         <is>
@@ -17010,17 +16948,13 @@
           <t>18/03/2022</t>
         </is>
       </c>
-      <c r="E531" s="2" t="inlineStr">
-        <is>
-          <t>2390</t>
-        </is>
+      <c r="E531" s="2" t="n">
+        <v>2390</v>
       </c>
       <c r="F531" s="2" t="inlineStr"/>
       <c r="G531" s="2" t="inlineStr"/>
-      <c r="H531" s="2" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
+      <c r="H531" s="2" t="n">
+        <v>45.6</v>
       </c>
       <c r="I531" s="2" t="inlineStr"/>
       <c r="J531" s="2" t="inlineStr"/>
@@ -17044,17 +16978,13 @@
           <t>18/03/2022</t>
         </is>
       </c>
-      <c r="E532" s="2" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
+      <c r="E532" s="2" t="n">
+        <v>2400</v>
       </c>
       <c r="F532" s="2" t="inlineStr"/>
       <c r="G532" s="2" t="inlineStr"/>
-      <c r="H532" s="2" t="inlineStr">
-        <is>
-          <t>46.8</t>
-        </is>
+      <c r="H532" s="2" t="n">
+        <v>46.8</v>
       </c>
       <c r="I532" s="2" t="inlineStr"/>
       <c r="J532" s="2" t="inlineStr"/>
@@ -17100,10 +17030,8 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E534" s="2" t="inlineStr">
-        <is>
-          <t>2370</t>
-        </is>
+      <c r="E534" s="2" t="n">
+        <v>2370</v>
       </c>
       <c r="F534" s="2" t="inlineStr">
         <is>
@@ -17134,17 +17062,13 @@
           <t>21/03/2022</t>
         </is>
       </c>
-      <c r="E535" s="2" t="inlineStr">
-        <is>
-          <t>2370</t>
-        </is>
+      <c r="E535" s="2" t="n">
+        <v>2370</v>
       </c>
       <c r="F535" s="2" t="inlineStr"/>
       <c r="G535" s="2" t="inlineStr"/>
-      <c r="H535" s="2" t="inlineStr">
-        <is>
-          <t>44.4</t>
-        </is>
+      <c r="H535" s="2" t="n">
+        <v>44.4</v>
       </c>
       <c r="I535" s="2" t="inlineStr"/>
       <c r="J535" s="2" t="inlineStr"/>
@@ -17168,17 +17092,13 @@
           <t>21/03/2022</t>
         </is>
       </c>
-      <c r="E536" s="2" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="E536" s="2" t="n">
+        <v>2360</v>
       </c>
       <c r="F536" s="2" t="inlineStr"/>
       <c r="G536" s="2" t="inlineStr"/>
-      <c r="H536" s="2" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
+      <c r="H536" s="2" t="n">
+        <v>45.3</v>
       </c>
       <c r="I536" s="2" t="inlineStr"/>
       <c r="J536" s="2" t="inlineStr"/>
@@ -17224,10 +17144,8 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E538" s="2" t="inlineStr">
-        <is>
-          <t>2310</t>
-        </is>
+      <c r="E538" s="2" t="n">
+        <v>2310</v>
       </c>
       <c r="F538" s="2" t="inlineStr">
         <is>
@@ -17258,17 +17176,13 @@
           <t>22/03/2022</t>
         </is>
       </c>
-      <c r="E539" s="2" t="inlineStr">
-        <is>
-          <t>2290</t>
-        </is>
+      <c r="E539" s="2" t="n">
+        <v>2290</v>
       </c>
       <c r="F539" s="2" t="inlineStr"/>
       <c r="G539" s="2" t="inlineStr"/>
-      <c r="H539" s="2" t="inlineStr">
-        <is>
-          <t>51.6</t>
-        </is>
+      <c r="H539" s="2" t="n">
+        <v>51.6</v>
       </c>
       <c r="I539" s="2" t="inlineStr"/>
       <c r="J539" s="2" t="inlineStr"/>
@@ -17292,17 +17206,13 @@
           <t>22/03/2022</t>
         </is>
       </c>
-      <c r="E540" s="2" t="inlineStr">
-        <is>
-          <t>2310</t>
-        </is>
+      <c r="E540" s="2" t="n">
+        <v>2310</v>
       </c>
       <c r="F540" s="2" t="inlineStr"/>
       <c r="G540" s="2" t="inlineStr"/>
-      <c r="H540" s="2" t="inlineStr">
-        <is>
-          <t>40.2</t>
-        </is>
+      <c r="H540" s="2" t="n">
+        <v>40.2</v>
       </c>
       <c r="I540" s="2" t="inlineStr"/>
       <c r="J540" s="2" t="inlineStr"/>
@@ -17348,10 +17258,8 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E542" s="2" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
+      <c r="E542" s="2" t="n">
+        <v>2400</v>
       </c>
       <c r="F542" s="2" t="inlineStr">
         <is>
@@ -17382,17 +17290,13 @@
           <t>22/03/2022</t>
         </is>
       </c>
-      <c r="E543" s="2" t="inlineStr">
-        <is>
-          <t>2390</t>
-        </is>
+      <c r="E543" s="2" t="n">
+        <v>2390</v>
       </c>
       <c r="F543" s="2" t="inlineStr"/>
       <c r="G543" s="2" t="inlineStr"/>
-      <c r="H543" s="2" t="inlineStr">
-        <is>
-          <t>40.8</t>
-        </is>
+      <c r="H543" s="2" t="n">
+        <v>40.8</v>
       </c>
       <c r="I543" s="2" t="inlineStr"/>
       <c r="J543" s="2" t="inlineStr"/>
@@ -17416,17 +17320,13 @@
           <t>22/03/2022</t>
         </is>
       </c>
-      <c r="E544" s="2" t="inlineStr">
-        <is>
-          <t>2370</t>
-        </is>
+      <c r="E544" s="2" t="n">
+        <v>2370</v>
       </c>
       <c r="F544" s="2" t="inlineStr"/>
       <c r="G544" s="2" t="inlineStr"/>
-      <c r="H544" s="2" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
+      <c r="H544" s="2" t="n">
+        <v>40</v>
       </c>
       <c r="I544" s="2" t="inlineStr"/>
       <c r="J544" s="2" t="inlineStr"/>
@@ -17472,10 +17372,8 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E546" s="2" t="inlineStr">
-        <is>
-          <t>2370</t>
-        </is>
+      <c r="E546" s="2" t="n">
+        <v>2370</v>
       </c>
       <c r="F546" s="2" t="inlineStr"/>
       <c r="G546" s="2" t="inlineStr">
@@ -17506,17 +17404,13 @@
           <t>23/03/2022</t>
         </is>
       </c>
-      <c r="E547" s="2" t="inlineStr">
-        <is>
-          <t>2390</t>
-        </is>
+      <c r="E547" s="2" t="n">
+        <v>2390</v>
       </c>
       <c r="F547" s="2" t="inlineStr"/>
       <c r="G547" s="2" t="inlineStr"/>
-      <c r="H547" s="2" t="inlineStr">
-        <is>
-          <t>40.2</t>
-        </is>
+      <c r="H547" s="2" t="n">
+        <v>40.2</v>
       </c>
       <c r="I547" s="2" t="inlineStr"/>
       <c r="J547" s="2" t="inlineStr"/>
@@ -17540,17 +17434,13 @@
           <t>23/03/2022</t>
         </is>
       </c>
-      <c r="E548" s="2" t="inlineStr">
-        <is>
-          <t>2410</t>
-        </is>
+      <c r="E548" s="2" t="n">
+        <v>2410</v>
       </c>
       <c r="F548" s="2" t="inlineStr"/>
       <c r="G548" s="2" t="inlineStr"/>
-      <c r="H548" s="2" t="inlineStr">
-        <is>
-          <t>44.6</t>
-        </is>
+      <c r="H548" s="2" t="n">
+        <v>44.6</v>
       </c>
       <c r="I548" s="2" t="inlineStr"/>
       <c r="J548" s="2" t="inlineStr"/>
@@ -17596,10 +17486,8 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E550" s="2" t="inlineStr">
-        <is>
-          <t>2350</t>
-        </is>
+      <c r="E550" s="2" t="n">
+        <v>2350</v>
       </c>
       <c r="F550" s="2" t="inlineStr">
         <is>
@@ -17630,17 +17518,13 @@
           <t>24/03/2022</t>
         </is>
       </c>
-      <c r="E551" s="2" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="E551" s="2" t="n">
+        <v>2360</v>
       </c>
       <c r="F551" s="2" t="inlineStr"/>
       <c r="G551" s="2" t="inlineStr"/>
-      <c r="H551" s="2" t="inlineStr">
-        <is>
-          <t>45.2</t>
-        </is>
+      <c r="H551" s="2" t="n">
+        <v>45.2</v>
       </c>
       <c r="I551" s="2" t="inlineStr"/>
       <c r="J551" s="2" t="inlineStr"/>
@@ -17664,17 +17548,13 @@
           <t>14/03/2022</t>
         </is>
       </c>
-      <c r="E552" s="2" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
+      <c r="E552" s="2" t="n">
+        <v>2340</v>
       </c>
       <c r="F552" s="2" t="inlineStr"/>
       <c r="G552" s="2" t="inlineStr"/>
-      <c r="H552" s="2" t="inlineStr">
-        <is>
-          <t>38.2</t>
-        </is>
+      <c r="H552" s="2" t="n">
+        <v>38.2</v>
       </c>
       <c r="I552" s="2" t="inlineStr"/>
       <c r="J552" s="2" t="inlineStr"/>
@@ -17720,10 +17600,8 @@
           <t>11/03/2022</t>
         </is>
       </c>
-      <c r="E554" s="2" t="inlineStr">
-        <is>
-          <t>2320</t>
-        </is>
+      <c r="E554" s="2" t="n">
+        <v>2320</v>
       </c>
       <c r="F554" s="2" t="inlineStr"/>
       <c r="G554" s="2" t="inlineStr">
@@ -17749,11 +17627,19 @@
           <t>2nd Floor Walls (39)(B-J),W1 (31-36)(G), W1(35-36)(Z-DD)</t>
         </is>
       </c>
-      <c r="D555" s="2" t="inlineStr"/>
-      <c r="E555" s="2" t="inlineStr"/>
+      <c r="D555" s="2" t="inlineStr">
+        <is>
+          <t>25/03/2022</t>
+        </is>
+      </c>
+      <c r="E555" s="2" t="n">
+        <v>2340</v>
+      </c>
       <c r="F555" s="2" t="inlineStr"/>
       <c r="G555" s="2" t="inlineStr"/>
-      <c r="H555" s="2" t="inlineStr"/>
+      <c r="H555" s="2" t="n">
+        <v>45.5</v>
+      </c>
       <c r="I555" s="2" t="inlineStr"/>
       <c r="J555" s="2" t="inlineStr"/>
     </row>
@@ -17771,11 +17657,19 @@
           <t>2nd Floor Walls (39)(B-J),W1 (31-36)(G), W1(35-36)(Z-DD)</t>
         </is>
       </c>
-      <c r="D556" s="2" t="inlineStr"/>
-      <c r="E556" s="2" t="inlineStr"/>
+      <c r="D556" s="2" t="inlineStr">
+        <is>
+          <t>25/03/2022</t>
+        </is>
+      </c>
+      <c r="E556" s="2" t="n">
+        <v>2330</v>
+      </c>
       <c r="F556" s="2" t="inlineStr"/>
       <c r="G556" s="2" t="inlineStr"/>
-      <c r="H556" s="2" t="inlineStr"/>
+      <c r="H556" s="2" t="n">
+        <v>43</v>
+      </c>
       <c r="I556" s="2" t="inlineStr"/>
       <c r="J556" s="2" t="inlineStr"/>
     </row>
@@ -17820,10 +17714,8 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E558" s="2" t="inlineStr">
-        <is>
-          <t>2350</t>
-        </is>
+      <c r="E558" s="2" t="n">
+        <v>2350</v>
       </c>
       <c r="F558" s="2" t="inlineStr">
         <is>
@@ -17849,11 +17741,23 @@
           <t>3rd Floor (U-LL)(10-19)</t>
         </is>
       </c>
-      <c r="D559" s="2" t="inlineStr"/>
-      <c r="E559" s="2" t="inlineStr"/>
+      <c r="D559" s="2" t="inlineStr">
+        <is>
+          <t>28/03/2022</t>
+        </is>
+      </c>
+      <c r="E559" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
       <c r="F559" s="2" t="inlineStr"/>
       <c r="G559" s="2" t="inlineStr"/>
-      <c r="H559" s="2" t="inlineStr"/>
+      <c r="H559" s="2" t="inlineStr">
+        <is>
+          <t>40.5</t>
+        </is>
+      </c>
       <c r="I559" s="2" t="inlineStr"/>
       <c r="J559" s="2" t="inlineStr"/>
     </row>
@@ -17871,11 +17775,23 @@
           <t>3rd Floor (U-LL)(10-19)</t>
         </is>
       </c>
-      <c r="D560" s="2" t="inlineStr"/>
-      <c r="E560" s="2" t="inlineStr"/>
+      <c r="D560" s="2" t="inlineStr">
+        <is>
+          <t>28/03/2022</t>
+        </is>
+      </c>
+      <c r="E560" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
       <c r="F560" s="2" t="inlineStr"/>
       <c r="G560" s="2" t="inlineStr"/>
-      <c r="H560" s="2" t="inlineStr"/>
+      <c r="H560" s="2" t="inlineStr">
+        <is>
+          <t>41.3</t>
+        </is>
+      </c>
       <c r="I560" s="2" t="inlineStr"/>
       <c r="J560" s="2" t="inlineStr"/>
     </row>
@@ -17920,10 +17836,8 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E562" s="2" t="inlineStr">
-        <is>
-          <t>2370</t>
-        </is>
+      <c r="E562" s="2" t="n">
+        <v>2370</v>
       </c>
       <c r="F562" s="2" t="inlineStr">
         <is>
@@ -17949,11 +17863,23 @@
           <t>3rd Floor Walls (2-6)(L-DD)</t>
         </is>
       </c>
-      <c r="D563" s="2" t="inlineStr"/>
-      <c r="E563" s="2" t="inlineStr"/>
+      <c r="D563" s="2" t="inlineStr">
+        <is>
+          <t>28/03/2022</t>
+        </is>
+      </c>
+      <c r="E563" s="2" t="inlineStr">
+        <is>
+          <t>2370</t>
+        </is>
+      </c>
       <c r="F563" s="2" t="inlineStr"/>
       <c r="G563" s="2" t="inlineStr"/>
-      <c r="H563" s="2" t="inlineStr"/>
+      <c r="H563" s="2" t="inlineStr">
+        <is>
+          <t>42.4</t>
+        </is>
+      </c>
       <c r="I563" s="2" t="inlineStr"/>
       <c r="J563" s="2" t="inlineStr"/>
     </row>
@@ -17971,11 +17897,23 @@
           <t>3rd Floor Walls (2-6)(L-DD)</t>
         </is>
       </c>
-      <c r="D564" s="2" t="inlineStr"/>
-      <c r="E564" s="2" t="inlineStr"/>
+      <c r="D564" s="2" t="inlineStr">
+        <is>
+          <t>28/03/2022</t>
+        </is>
+      </c>
+      <c r="E564" s="2" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
       <c r="F564" s="2" t="inlineStr"/>
       <c r="G564" s="2" t="inlineStr"/>
-      <c r="H564" s="2" t="inlineStr"/>
+      <c r="H564" s="2" t="inlineStr">
+        <is>
+          <t>40.9</t>
+        </is>
+      </c>
       <c r="I564" s="2" t="inlineStr"/>
       <c r="J564" s="2" t="inlineStr"/>
     </row>
@@ -18020,10 +17958,8 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E566" s="2" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="E566" s="2" t="n">
+        <v>2360</v>
       </c>
       <c r="F566" s="2" t="inlineStr">
         <is>
@@ -18120,10 +18056,8 @@
           <t>09/03/2022</t>
         </is>
       </c>
-      <c r="E570" s="2" t="inlineStr">
-        <is>
-          <t>2350</t>
-        </is>
+      <c r="E570" s="2" t="n">
+        <v>2350</v>
       </c>
       <c r="F570" s="2" t="inlineStr">
         <is>
@@ -18220,10 +18154,8 @@
           <t>10/03/2022</t>
         </is>
       </c>
-      <c r="E574" s="2" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="E574" s="2" t="n">
+        <v>2360</v>
       </c>
       <c r="F574" s="2" t="inlineStr">
         <is>
@@ -18320,10 +18252,8 @@
           <t>11/03/2022</t>
         </is>
       </c>
-      <c r="E578" s="2" t="inlineStr">
-        <is>
-          <t>2380</t>
-        </is>
+      <c r="E578" s="2" t="n">
+        <v>2380</v>
       </c>
       <c r="F578" s="2" t="inlineStr">
         <is>
@@ -18407,17 +18337,21 @@
           <t>111A</t>
         </is>
       </c>
-      <c r="B582" s="2" t="inlineStr"/>
-      <c r="C582" s="2" t="inlineStr"/>
+      <c r="B582" s="3" t="n">
+        <v>44627</v>
+      </c>
+      <c r="C582" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Slab (19-33)(U-JJ)</t>
+        </is>
+      </c>
       <c r="D582" s="2" t="inlineStr">
         <is>
           <t>23/03/2022</t>
         </is>
       </c>
-      <c r="E582" s="2" t="inlineStr">
-        <is>
-          <t>2320</t>
-        </is>
+      <c r="E582" s="2" t="n">
+        <v>2320</v>
       </c>
       <c r="F582" s="2" t="inlineStr">
         <is>
@@ -18435,8 +18369,14 @@
           <t>111B</t>
         </is>
       </c>
-      <c r="B583" s="2" t="inlineStr"/>
-      <c r="C583" s="2" t="inlineStr"/>
+      <c r="B583" s="3" t="n">
+        <v>44627</v>
+      </c>
+      <c r="C583" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Slab (19-33)(U-JJ)</t>
+        </is>
+      </c>
       <c r="D583" s="2" t="inlineStr"/>
       <c r="E583" s="2" t="inlineStr"/>
       <c r="F583" s="2" t="inlineStr"/>
@@ -18451,8 +18391,14 @@
           <t>111C</t>
         </is>
       </c>
-      <c r="B584" s="2" t="inlineStr"/>
-      <c r="C584" s="2" t="inlineStr"/>
+      <c r="B584" s="3" t="n">
+        <v>44627</v>
+      </c>
+      <c r="C584" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Slab (19-33)(U-JJ)</t>
+        </is>
+      </c>
       <c r="D584" s="2" t="inlineStr"/>
       <c r="E584" s="2" t="inlineStr"/>
       <c r="F584" s="2" t="inlineStr"/>
@@ -18467,8 +18413,14 @@
           <t>111D</t>
         </is>
       </c>
-      <c r="B585" s="2" t="inlineStr"/>
-      <c r="C585" s="2" t="inlineStr"/>
+      <c r="B585" s="3" t="n">
+        <v>44627</v>
+      </c>
+      <c r="C585" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Slab (19-33)(U-JJ)</t>
+        </is>
+      </c>
       <c r="D585" s="2" t="inlineStr"/>
       <c r="E585" s="2" t="inlineStr"/>
       <c r="F585" s="2" t="inlineStr"/>
@@ -18483,17 +18435,21 @@
           <t>112A</t>
         </is>
       </c>
-      <c r="B586" s="2" t="inlineStr"/>
-      <c r="C586" s="2" t="inlineStr"/>
+      <c r="B586" s="3" t="n">
+        <v>44627</v>
+      </c>
+      <c r="C586" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Wall (U)(13-14), w1(U-Z)(16-19),W1(U-GG)(18),W1(DD-GG)(15-16),W1(12-17)(Z-GG)</t>
+        </is>
+      </c>
       <c r="D586" s="2" t="inlineStr">
         <is>
           <t>23/03/2022</t>
         </is>
       </c>
-      <c r="E586" s="2" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="E586" s="2" t="n">
+        <v>2360</v>
       </c>
       <c r="F586" s="2" t="inlineStr">
         <is>
@@ -18511,8 +18467,14 @@
           <t>112B</t>
         </is>
       </c>
-      <c r="B587" s="2" t="inlineStr"/>
-      <c r="C587" s="2" t="inlineStr"/>
+      <c r="B587" s="3" t="n">
+        <v>44627</v>
+      </c>
+      <c r="C587" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Wall (U)(13-14), w1(U-Z)(16-19),W1(U-GG)(18),W1(DD-GG)(15-16),W1(12-17)(Z-GG)</t>
+        </is>
+      </c>
       <c r="D587" s="2" t="inlineStr"/>
       <c r="E587" s="2" t="inlineStr"/>
       <c r="F587" s="2" t="inlineStr"/>
@@ -18527,8 +18489,14 @@
           <t>112C</t>
         </is>
       </c>
-      <c r="B588" s="2" t="inlineStr"/>
-      <c r="C588" s="2" t="inlineStr"/>
+      <c r="B588" s="3" t="n">
+        <v>44627</v>
+      </c>
+      <c r="C588" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Wall (U)(13-14), w1(U-Z)(16-19),W1(U-GG)(18),W1(DD-GG)(15-16),W1(12-17)(Z-GG)</t>
+        </is>
+      </c>
       <c r="D588" s="2" t="inlineStr"/>
       <c r="E588" s="2" t="inlineStr"/>
       <c r="F588" s="2" t="inlineStr"/>
@@ -18543,8 +18511,14 @@
           <t>112D</t>
         </is>
       </c>
-      <c r="B589" s="2" t="inlineStr"/>
-      <c r="C589" s="2" t="inlineStr"/>
+      <c r="B589" s="3" t="n">
+        <v>44627</v>
+      </c>
+      <c r="C589" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Wall (U)(13-14), w1(U-Z)(16-19),W1(U-GG)(18),W1(DD-GG)(15-16),W1(12-17)(Z-GG)</t>
+        </is>
+      </c>
       <c r="D589" s="2" t="inlineStr"/>
       <c r="E589" s="2" t="inlineStr"/>
       <c r="F589" s="2" t="inlineStr"/>
@@ -18559,17 +18533,21 @@
           <t>113A</t>
         </is>
       </c>
-      <c r="B590" s="2" t="inlineStr"/>
-      <c r="C590" s="2" t="inlineStr"/>
+      <c r="B590" s="3" t="n">
+        <v>44629</v>
+      </c>
+      <c r="C590" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Walls (19)(U-GG),W1 (18)(Z-DD),W1(16)(Z-DD),W1(13)(U-GG), W1(11)(DD-EE), W1( 5-7)(EE), W1(24-29)(Z-GG)</t>
+        </is>
+      </c>
       <c r="D590" s="2" t="inlineStr">
         <is>
           <t>23/03/2022</t>
         </is>
       </c>
-      <c r="E590" s="2" t="inlineStr">
-        <is>
-          <t>2350</t>
-        </is>
+      <c r="E590" s="2" t="n">
+        <v>2350</v>
       </c>
       <c r="F590" s="2" t="inlineStr"/>
       <c r="G590" s="2" t="inlineStr">
@@ -18587,8 +18565,14 @@
           <t>113B</t>
         </is>
       </c>
-      <c r="B591" s="2" t="inlineStr"/>
-      <c r="C591" s="2" t="inlineStr"/>
+      <c r="B591" s="3" t="n">
+        <v>44629</v>
+      </c>
+      <c r="C591" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Walls (19)(U-GG),W1 (18)(Z-DD),W1(16)(Z-DD),W1(13)(U-GG), W1(11)(DD-EE), W1( 5-7)(EE), W1(24-29)(Z-GG)</t>
+        </is>
+      </c>
       <c r="D591" s="2" t="inlineStr"/>
       <c r="E591" s="2" t="inlineStr"/>
       <c r="F591" s="2" t="inlineStr"/>
@@ -18603,8 +18587,14 @@
           <t>113C</t>
         </is>
       </c>
-      <c r="B592" s="2" t="inlineStr"/>
-      <c r="C592" s="2" t="inlineStr"/>
+      <c r="B592" s="3" t="n">
+        <v>44629</v>
+      </c>
+      <c r="C592" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Walls (19)(U-GG),W1 (18)(Z-DD),W1(16)(Z-DD),W1(13)(U-GG), W1(11)(DD-EE), W1( 5-7)(EE), W1(24-29)(Z-GG)</t>
+        </is>
+      </c>
       <c r="D592" s="2" t="inlineStr"/>
       <c r="E592" s="2" t="inlineStr"/>
       <c r="F592" s="2" t="inlineStr"/>
@@ -18619,8 +18609,14 @@
           <t>113D</t>
         </is>
       </c>
-      <c r="B593" s="2" t="inlineStr"/>
-      <c r="C593" s="2" t="inlineStr"/>
+      <c r="B593" s="3" t="n">
+        <v>44629</v>
+      </c>
+      <c r="C593" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Walls (19)(U-GG),W1 (18)(Z-DD),W1(16)(Z-DD),W1(13)(U-GG), W1(11)(DD-EE), W1( 5-7)(EE), W1(24-29)(Z-GG)</t>
+        </is>
+      </c>
       <c r="D593" s="2" t="inlineStr"/>
       <c r="E593" s="2" t="inlineStr"/>
       <c r="F593" s="2" t="inlineStr"/>
@@ -18635,17 +18631,21 @@
           <t>114A</t>
         </is>
       </c>
-      <c r="B594" s="2" t="inlineStr"/>
-      <c r="C594" s="2" t="inlineStr"/>
+      <c r="B594" s="3" t="n">
+        <v>44630</v>
+      </c>
+      <c r="C594" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Slab (A-GG)(31-45), Half Landing Core A 03-03,04-04</t>
+        </is>
+      </c>
       <c r="D594" s="2" t="inlineStr">
         <is>
           <t>24/03/2022</t>
         </is>
       </c>
-      <c r="E594" s="2" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
+      <c r="E594" s="2" t="n">
+        <v>2340</v>
       </c>
       <c r="F594" s="2" t="inlineStr"/>
       <c r="G594" s="2" t="inlineStr">
@@ -18663,8 +18663,14 @@
           <t>114B</t>
         </is>
       </c>
-      <c r="B595" s="2" t="inlineStr"/>
-      <c r="C595" s="2" t="inlineStr"/>
+      <c r="B595" s="3" t="n">
+        <v>44630</v>
+      </c>
+      <c r="C595" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Slab (A-GG)(31-45), Half Landing Core A 03-03,04-04</t>
+        </is>
+      </c>
       <c r="D595" s="2" t="inlineStr"/>
       <c r="E595" s="2" t="inlineStr"/>
       <c r="F595" s="2" t="inlineStr"/>
@@ -18679,8 +18685,14 @@
           <t>114C</t>
         </is>
       </c>
-      <c r="B596" s="2" t="inlineStr"/>
-      <c r="C596" s="2" t="inlineStr"/>
+      <c r="B596" s="3" t="n">
+        <v>44630</v>
+      </c>
+      <c r="C596" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Slab (A-GG)(31-45), Half Landing Core A 03-03,04-04</t>
+        </is>
+      </c>
       <c r="D596" s="2" t="inlineStr"/>
       <c r="E596" s="2" t="inlineStr"/>
       <c r="F596" s="2" t="inlineStr"/>
@@ -18695,8 +18707,14 @@
           <t>114D</t>
         </is>
       </c>
-      <c r="B597" s="2" t="inlineStr"/>
-      <c r="C597" s="2" t="inlineStr"/>
+      <c r="B597" s="3" t="n">
+        <v>44630</v>
+      </c>
+      <c r="C597" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Slab (A-GG)(31-45), Half Landing Core A 03-03,04-04</t>
+        </is>
+      </c>
       <c r="D597" s="2" t="inlineStr"/>
       <c r="E597" s="2" t="inlineStr"/>
       <c r="F597" s="2" t="inlineStr"/>
@@ -18711,17 +18729,21 @@
           <t>115A</t>
         </is>
       </c>
-      <c r="B598" s="2" t="inlineStr"/>
-      <c r="C598" s="2" t="inlineStr"/>
+      <c r="B598" s="3" t="n">
+        <v>44630</v>
+      </c>
+      <c r="C598" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Slab (A-GG)(31-45), Half Landing Core A 03-03,04-04</t>
+        </is>
+      </c>
       <c r="D598" s="2" t="inlineStr">
         <is>
           <t>24/03/2022</t>
         </is>
       </c>
-      <c r="E598" s="2" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="E598" s="2" t="n">
+        <v>2360</v>
       </c>
       <c r="F598" s="2" t="inlineStr"/>
       <c r="G598" s="2" t="inlineStr">
@@ -18739,8 +18761,14 @@
           <t>115B</t>
         </is>
       </c>
-      <c r="B599" s="2" t="inlineStr"/>
-      <c r="C599" s="2" t="inlineStr"/>
+      <c r="B599" s="3" t="n">
+        <v>44630</v>
+      </c>
+      <c r="C599" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Slab (A-GG)(31-45), Half Landing Core A 03-03,04-04</t>
+        </is>
+      </c>
       <c r="D599" s="2" t="inlineStr"/>
       <c r="E599" s="2" t="inlineStr"/>
       <c r="F599" s="2" t="inlineStr"/>
@@ -18755,8 +18783,14 @@
           <t>115C</t>
         </is>
       </c>
-      <c r="B600" s="2" t="inlineStr"/>
-      <c r="C600" s="2" t="inlineStr"/>
+      <c r="B600" s="3" t="n">
+        <v>44630</v>
+      </c>
+      <c r="C600" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Slab (A-GG)(31-45), Half Landing Core A 03-03,04-04</t>
+        </is>
+      </c>
       <c r="D600" s="2" t="inlineStr"/>
       <c r="E600" s="2" t="inlineStr"/>
       <c r="F600" s="2" t="inlineStr"/>
@@ -18771,8 +18805,14 @@
           <t>115D</t>
         </is>
       </c>
-      <c r="B601" s="2" t="inlineStr"/>
-      <c r="C601" s="2" t="inlineStr"/>
+      <c r="B601" s="3" t="n">
+        <v>44630</v>
+      </c>
+      <c r="C601" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Slab (A-GG)(31-45), Half Landing Core A 03-03,04-04</t>
+        </is>
+      </c>
       <c r="D601" s="2" t="inlineStr"/>
       <c r="E601" s="2" t="inlineStr"/>
       <c r="F601" s="2" t="inlineStr"/>
@@ -18787,12 +18827,28 @@
           <t>116A</t>
         </is>
       </c>
-      <c r="B602" s="2" t="inlineStr"/>
-      <c r="C602" s="2" t="inlineStr"/>
-      <c r="D602" s="2" t="inlineStr"/>
-      <c r="E602" s="2" t="inlineStr"/>
+      <c r="B602" s="3" t="n">
+        <v>44631</v>
+      </c>
+      <c r="C602" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Slab (28-35)(U-Z),W1(27-34)(GG-JJ), W1(30)(U-GG)</t>
+        </is>
+      </c>
+      <c r="D602" s="2" t="inlineStr">
+        <is>
+          <t>25/03/2022</t>
+        </is>
+      </c>
+      <c r="E602" s="2" t="n">
+        <v>2360</v>
+      </c>
       <c r="F602" s="2" t="inlineStr"/>
-      <c r="G602" s="2" t="inlineStr"/>
+      <c r="G602" s="2" t="inlineStr">
+        <is>
+          <t>36.3</t>
+        </is>
+      </c>
       <c r="H602" s="2" t="inlineStr"/>
       <c r="I602" s="2" t="inlineStr"/>
       <c r="J602" s="2" t="inlineStr"/>
@@ -18803,8 +18859,14 @@
           <t>116B</t>
         </is>
       </c>
-      <c r="B603" s="2" t="inlineStr"/>
-      <c r="C603" s="2" t="inlineStr"/>
+      <c r="B603" s="3" t="n">
+        <v>44631</v>
+      </c>
+      <c r="C603" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Slab (28-35)(U-Z),W1(27-34)(GG-JJ), W1(30)(U-GG)</t>
+        </is>
+      </c>
       <c r="D603" s="2" t="inlineStr"/>
       <c r="E603" s="2" t="inlineStr"/>
       <c r="F603" s="2" t="inlineStr"/>
@@ -18819,8 +18881,14 @@
           <t>116C</t>
         </is>
       </c>
-      <c r="B604" s="2" t="inlineStr"/>
-      <c r="C604" s="2" t="inlineStr"/>
+      <c r="B604" s="3" t="n">
+        <v>44631</v>
+      </c>
+      <c r="C604" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Slab (28-35)(U-Z),W1(27-34)(GG-JJ), W1(30)(U-GG)</t>
+        </is>
+      </c>
       <c r="D604" s="2" t="inlineStr"/>
       <c r="E604" s="2" t="inlineStr"/>
       <c r="F604" s="2" t="inlineStr"/>
@@ -18835,8 +18903,14 @@
           <t>116D</t>
         </is>
       </c>
-      <c r="B605" s="2" t="inlineStr"/>
-      <c r="C605" s="2" t="inlineStr"/>
+      <c r="B605" s="3" t="n">
+        <v>44631</v>
+      </c>
+      <c r="C605" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Slab (28-35)(U-Z),W1(27-34)(GG-JJ), W1(30)(U-GG)</t>
+        </is>
+      </c>
       <c r="D605" s="2" t="inlineStr"/>
       <c r="E605" s="2" t="inlineStr"/>
       <c r="F605" s="2" t="inlineStr"/>
@@ -18851,17 +18925,21 @@
           <t>117A</t>
         </is>
       </c>
-      <c r="B606" s="2" t="inlineStr"/>
-      <c r="C606" s="2" t="inlineStr"/>
+      <c r="B606" s="3" t="n">
+        <v>44634</v>
+      </c>
+      <c r="C606" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Walls (19-20)(U), W1(22-25)(U-Z), W1(25-27)(P-Z), W1(27-28)(DD-GG), W1(23)(Z-GG), W1 (19-22)(Z-JJ)</t>
+        </is>
+      </c>
       <c r="D606" s="2" t="inlineStr">
         <is>
           <t>23/03/2022</t>
         </is>
       </c>
-      <c r="E606" s="2" t="inlineStr">
-        <is>
-          <t>2350</t>
-        </is>
+      <c r="E606" s="2" t="n">
+        <v>2350</v>
       </c>
       <c r="F606" s="2" t="inlineStr">
         <is>
@@ -18876,11 +18954,17 @@
     <row r="607">
       <c r="A607" s="2" t="inlineStr">
         <is>
-          <t>11B</t>
-        </is>
-      </c>
-      <c r="B607" s="2" t="inlineStr"/>
-      <c r="C607" s="2" t="inlineStr"/>
+          <t>117B</t>
+        </is>
+      </c>
+      <c r="B607" s="3" t="n">
+        <v>44634</v>
+      </c>
+      <c r="C607" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Walls (19-20)(U), W1(22-25)(U-Z), W1(25-27)(P-Z), W1(27-28)(DD-GG), W1(23)(Z-GG), W1 (19-22)(Z-JJ)</t>
+        </is>
+      </c>
       <c r="D607" s="2" t="inlineStr"/>
       <c r="E607" s="2" t="inlineStr"/>
       <c r="F607" s="2" t="inlineStr"/>
@@ -18895,8 +18979,14 @@
           <t>117C</t>
         </is>
       </c>
-      <c r="B608" s="2" t="inlineStr"/>
-      <c r="C608" s="2" t="inlineStr"/>
+      <c r="B608" s="3" t="n">
+        <v>44634</v>
+      </c>
+      <c r="C608" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Walls (19-20)(U), W1(22-25)(U-Z), W1(25-27)(P-Z), W1(27-28)(DD-GG), W1(23)(Z-GG), W1 (19-22)(Z-JJ)</t>
+        </is>
+      </c>
       <c r="D608" s="2" t="inlineStr"/>
       <c r="E608" s="2" t="inlineStr"/>
       <c r="F608" s="2" t="inlineStr"/>
@@ -18911,8 +19001,14 @@
           <t>117D</t>
         </is>
       </c>
-      <c r="B609" s="2" t="inlineStr"/>
-      <c r="C609" s="2" t="inlineStr"/>
+      <c r="B609" s="3" t="n">
+        <v>44634</v>
+      </c>
+      <c r="C609" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Walls (19-20)(U), W1(22-25)(U-Z), W1(25-27)(P-Z), W1(27-28)(DD-GG), W1(23)(Z-GG), W1 (19-22)(Z-JJ)</t>
+        </is>
+      </c>
       <c r="D609" s="2" t="inlineStr"/>
       <c r="E609" s="2" t="inlineStr"/>
       <c r="F609" s="2" t="inlineStr"/>
@@ -18927,17 +19023,21 @@
           <t>118A</t>
         </is>
       </c>
-      <c r="B610" s="2" t="inlineStr"/>
-      <c r="C610" s="2" t="inlineStr"/>
+      <c r="B610" s="3" t="n">
+        <v>44635</v>
+      </c>
+      <c r="C610" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Walls (44-45)(K-GG), W1 (34-45)(EE-GG), W1(28)(U-DD)</t>
+        </is>
+      </c>
       <c r="D610" s="2" t="inlineStr">
         <is>
           <t>23/03/2022</t>
         </is>
       </c>
-      <c r="E610" s="2" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
+      <c r="E610" s="2" t="n">
+        <v>2360</v>
       </c>
       <c r="F610" s="2" t="inlineStr">
         <is>
@@ -18955,8 +19055,14 @@
           <t>118B</t>
         </is>
       </c>
-      <c r="B611" s="2" t="inlineStr"/>
-      <c r="C611" s="2" t="inlineStr"/>
+      <c r="B611" s="3" t="n">
+        <v>44635</v>
+      </c>
+      <c r="C611" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Walls (44-45)(K-GG), W1 (34-45)(EE-GG), W1(28)(U-DD)</t>
+        </is>
+      </c>
       <c r="D611" s="2" t="inlineStr"/>
       <c r="E611" s="2" t="inlineStr"/>
       <c r="F611" s="2" t="inlineStr"/>
@@ -18971,8 +19077,14 @@
           <t>118C</t>
         </is>
       </c>
-      <c r="B612" s="2" t="inlineStr"/>
-      <c r="C612" s="2" t="inlineStr"/>
+      <c r="B612" s="3" t="n">
+        <v>44635</v>
+      </c>
+      <c r="C612" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Walls (44-45)(K-GG), W1 (34-45)(EE-GG), W1(28)(U-DD)</t>
+        </is>
+      </c>
       <c r="D612" s="2" t="inlineStr"/>
       <c r="E612" s="2" t="inlineStr"/>
       <c r="F612" s="2" t="inlineStr"/>
@@ -18987,8 +19099,14 @@
           <t>118D</t>
         </is>
       </c>
-      <c r="B613" s="2" t="inlineStr"/>
-      <c r="C613" s="2" t="inlineStr"/>
+      <c r="B613" s="3" t="n">
+        <v>44635</v>
+      </c>
+      <c r="C613" s="2" t="inlineStr">
+        <is>
+          <t>3rd Floor Walls (44-45)(K-GG), W1 (34-45)(EE-GG), W1(28)(U-DD)</t>
+        </is>
+      </c>
       <c r="D613" s="2" t="inlineStr"/>
       <c r="E613" s="2" t="inlineStr"/>
       <c r="F613" s="2" t="inlineStr"/>
